--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A606C-DB42-478A-B13A-6FA766E1C1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B07B2ED-D9AF-420A-A259-F4A169FCE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1156,10 +1156,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ES2812_LED</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Pin17</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1359,6 +1355,10 @@
   </si>
   <si>
     <t>DIO6</t>
+  </si>
+  <si>
+    <t>srom_cs_n</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1675,7 +1675,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1855,6 +1855,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6967,13 +6970,13 @@
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
@@ -7025,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F8" s="53"/>
       <c r="G8" s="12"/>
@@ -7040,7 +7043,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N8" s="53"/>
       <c r="O8" s="12"/>
@@ -7076,7 +7079,7 @@
         <v>4</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N9" s="53"/>
       <c r="O9" s="12"/>
@@ -7112,16 +7115,16 @@
         <v>3</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7135,7 +7138,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F11" s="53"/>
       <c r="G11" s="12"/>
@@ -7150,10 +7153,10 @@
         <v>3</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O11" s="12" t="s">
         <v>48</v>
@@ -7171,7 +7174,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F12" s="53"/>
       <c r="G12" s="12"/>
@@ -7186,13 +7189,13 @@
         <v>3</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P12" s="33"/>
     </row>
@@ -7207,7 +7210,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F13" s="53"/>
       <c r="G13" s="12"/>
@@ -7222,7 +7225,7 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N13" s="53"/>
       <c r="O13" s="12"/>
@@ -7239,7 +7242,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F14" s="53"/>
       <c r="G14" s="12"/>
@@ -7254,16 +7257,16 @@
         <v>3</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
@@ -7277,7 +7280,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F15" s="53"/>
       <c r="G15" s="12"/>
@@ -7292,7 +7295,7 @@
         <v>3</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N15" s="53"/>
       <c r="O15" s="12"/>
@@ -7309,7 +7312,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F16" s="53"/>
       <c r="G16" s="12"/>
@@ -7339,7 +7342,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="12"/>
@@ -7356,18 +7359,18 @@
       <c r="M17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N17" s="43" t="s">
-        <v>282</v>
+      <c r="N17" s="19" t="s">
+        <v>328</v>
       </c>
       <c r="O17" s="12"/>
-      <c r="P17" s="50"/>
+      <c r="P17" s="60"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D18" s="1">
         <v>6</v>
@@ -7382,7 +7385,7 @@
         <v>48</v>
       </c>
       <c r="H18" s="55" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J18" s="8">
         <v>26</v>
@@ -7408,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D19" s="1">
         <v>6</v>
@@ -7427,7 +7430,7 @@
         <v>25</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>36</v>
@@ -7447,7 +7450,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -7466,7 +7469,7 @@
         <v>24</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L20" s="1">
         <v>1</v>
@@ -7481,7 +7484,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -7500,7 +7503,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
@@ -7515,7 +7518,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>36</v>
@@ -7533,13 +7536,13 @@
         <v>22</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L22" s="1">
         <v>3</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N22" s="41"/>
       <c r="O22" s="12"/>
@@ -7567,20 +7570,20 @@
         <v>21</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L23" s="37">
         <v>3</v>
       </c>
       <c r="M23" s="37" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N23" s="42"/>
       <c r="O23" s="38"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.15">
       <c r="E25" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.15">
@@ -7776,13 +7779,13 @@
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
@@ -7835,13 +7838,13 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>210</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J8" s="11">
         <v>36</v>
@@ -7889,13 +7892,13 @@
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7928,16 +7931,16 @@
         <v>3</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7952,13 +7955,13 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J11" s="11">
         <v>33</v>
@@ -7970,10 +7973,10 @@
         <v>3</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O11" s="12" t="s">
         <v>45</v>
@@ -7992,7 +7995,7 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>210</v>
@@ -8008,13 +8011,13 @@
         <v>3</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N12" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="O12" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="P12" s="33"/>
     </row>
@@ -8030,7 +8033,7 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>210</v>
@@ -8047,13 +8050,13 @@
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.15">
@@ -8068,7 +8071,7 @@
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>210</v>
@@ -8084,10 +8087,10 @@
         <v>3</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>45</v>
@@ -8106,7 +8109,7 @@
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>210</v>
@@ -8123,13 +8126,13 @@
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
@@ -8144,7 +8147,7 @@
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>210</v>
@@ -8161,7 +8164,7 @@
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>48</v>
@@ -8180,7 +8183,7 @@
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>210</v>
@@ -8198,18 +8201,18 @@
       <c r="M17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N17" s="43" t="s">
-        <v>282</v>
+      <c r="N17" s="19" t="s">
+        <v>328</v>
       </c>
       <c r="O17" s="12"/>
-      <c r="P17" s="50"/>
+      <c r="P17" s="60"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D18" s="1">
         <v>6</v>
@@ -8224,7 +8227,7 @@
         <v>48</v>
       </c>
       <c r="H18" s="55" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J18" s="8">
         <v>26</v>
@@ -8250,7 +8253,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D19" s="1">
         <v>6</v>
@@ -8269,7 +8272,7 @@
         <v>25</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>36</v>
@@ -8289,7 +8292,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D20" s="1">
         <v>6</v>
@@ -8308,20 +8311,20 @@
         <v>24</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L20" s="1">
         <v>1</v>
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="45" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
       <c r="P20" s="58" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.15">
@@ -8329,7 +8332,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -8348,14 +8351,14 @@
         <v>23</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="45" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>48</v>
@@ -8367,7 +8370,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>36</v>
@@ -8385,13 +8388,13 @@
         <v>22</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L22" s="1">
         <v>3</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N22" s="41"/>
       <c r="O22" s="12"/>
@@ -8419,20 +8422,20 @@
         <v>21</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L23" s="37">
         <v>3</v>
       </c>
       <c r="M23" s="37" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N23" s="42"/>
       <c r="O23" s="38"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.15">
       <c r="E25" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.15">
@@ -8440,30 +8443,30 @@
     </row>
     <row r="36" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M37" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M38" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M39" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B07B2ED-D9AF-420A-A259-F4A169FCE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A689FBB-DD22-40AC-9446-46221BC4DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="337">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1358,6 +1358,38 @@
   </si>
   <si>
     <t>srom_cs_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>spi_clk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>smem_sio1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>smem_clk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sram_cs_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>smem_sio0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>smem_sio2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>smem_sio3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ROM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1838,6 +1870,9 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1855,9 +1890,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3140,7 +3172,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="54" t="s">
+      <c r="AC9" s="55" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3201,7 +3233,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="54"/>
+      <c r="AC10" s="55"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -3264,7 +3296,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="54"/>
+      <c r="AC11" s="55"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -3325,7 +3357,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="54"/>
+      <c r="AC12" s="55"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -3390,7 +3422,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="54"/>
+      <c r="AC13" s="55"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -3459,7 +3491,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="54"/>
+      <c r="AC14" s="55"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -3722,7 +3754,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="55" t="s">
+      <c r="AC18" s="56" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3787,7 +3819,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="55"/>
+      <c r="AC19" s="56"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -3846,7 +3878,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="55"/>
+      <c r="AC20" s="56"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -3909,7 +3941,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="55"/>
+      <c r="AC21" s="56"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -3970,7 +4002,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="54" t="s">
+      <c r="AC22" s="55" t="s">
         <v>244</v>
       </c>
     </row>
@@ -4033,7 +4065,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="54"/>
+      <c r="AC23" s="55"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -4094,7 +4126,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="54"/>
+      <c r="AC24" s="55"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -4153,7 +4185,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="54"/>
+      <c r="AC25" s="55"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -4216,7 +4248,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="54"/>
+      <c r="AC26" s="55"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -4277,7 +4309,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="54"/>
+      <c r="AC27" s="55"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -5161,7 +5193,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="54" t="s">
+      <c r="AC9" s="55" t="s">
         <v>245</v>
       </c>
     </row>
@@ -5230,7 +5262,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="54"/>
+      <c r="AC10" s="55"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -5297,7 +5329,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="54"/>
+      <c r="AC11" s="55"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -5364,7 +5396,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="54"/>
+      <c r="AC12" s="55"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -5433,7 +5465,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="54"/>
+      <c r="AC13" s="55"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -5506,7 +5538,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="54"/>
+      <c r="AC14" s="55"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -5791,7 +5823,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="55" t="s">
+      <c r="AC18" s="56" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5860,7 +5892,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="55"/>
+      <c r="AC19" s="56"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -5927,7 +5959,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="55"/>
+      <c r="AC20" s="56"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -5998,7 +6030,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="55"/>
+      <c r="AC21" s="56"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -6063,7 +6095,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="54" t="s">
+      <c r="AC22" s="55" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6130,7 +6162,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="54"/>
+      <c r="AC23" s="55"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -6195,7 +6227,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="54"/>
+      <c r="AC24" s="55"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -6258,7 +6290,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="54"/>
+      <c r="AC25" s="55"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -6321,7 +6353,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="54"/>
+      <c r="AC26" s="55"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -6386,7 +6418,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="54"/>
+      <c r="AC27" s="55"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -6515,7 +6547,7 @@
       <c r="AB29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AC29" s="56" t="s">
+      <c r="AC29" s="57" t="s">
         <v>243</v>
       </c>
     </row>
@@ -6586,7 +6618,7 @@
       <c r="AB30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC30" s="56"/>
+      <c r="AC30" s="57"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="21">
@@ -6651,7 +6683,7 @@
       <c r="AB31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC31" s="56"/>
+      <c r="AC31" s="57"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
@@ -6714,7 +6746,7 @@
       <c r="AB32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC32" s="56"/>
+      <c r="AC32" s="57"/>
     </row>
     <row r="33" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
@@ -6818,14 +6850,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="58" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -6968,16 +7000,16 @@
       <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="24" t="s">
-        <v>313</v>
+      <c r="M6" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>259</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>317</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P6" s="50"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B7" s="11">
@@ -7009,13 +7041,15 @@
       <c r="M7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="43" t="s">
-        <v>259</v>
+      <c r="N7" s="24" t="s">
+        <v>313</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="50"/>
+        <v>48</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
@@ -7123,7 +7157,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="56" t="s">
+      <c r="P10" s="57" t="s">
         <v>305</v>
       </c>
     </row>
@@ -7161,7 +7195,7 @@
       <c r="O11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P11" s="56"/>
+      <c r="P11" s="57"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -7363,7 +7397,7 @@
         <v>328</v>
       </c>
       <c r="O17" s="12"/>
-      <c r="P17" s="60"/>
+      <c r="P17" s="54"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -7384,7 +7418,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="56" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -7425,7 +7459,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="55"/>
+      <c r="H19" s="56"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -7464,7 +7498,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="55"/>
+      <c r="H20" s="56"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -7498,7 +7532,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="55"/>
+      <c r="H21" s="56"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -7625,14 +7659,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="58" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -7686,12 +7720,12 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="55" t="s">
         <v>244</v>
       </c>
       <c r="J4" s="8">
@@ -7725,12 +7759,12 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19" t="s">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="54"/>
+      <c r="H5" s="55"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -7762,12 +7796,12 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19" t="s">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="54"/>
+      <c r="H6" s="55"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -7777,16 +7811,16 @@
       <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="24" t="s">
-        <v>313</v>
+      <c r="M6" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>259</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>317</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P6" s="50"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B7" s="11">
@@ -7800,12 +7834,12 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="19" t="s">
-        <v>220</v>
+        <v>333</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="54"/>
+      <c r="H7" s="55"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -7818,13 +7852,15 @@
       <c r="M7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="43" t="s">
-        <v>259</v>
+      <c r="N7" s="24" t="s">
+        <v>313</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="50"/>
+        <v>48</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
@@ -7873,12 +7909,12 @@
         <v>263</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="55" t="s">
         <v>244</v>
       </c>
       <c r="J9" s="11">
@@ -7915,12 +7951,12 @@
         <v>263</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>222</v>
+        <v>335</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="54"/>
+      <c r="H10" s="55"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -7939,7 +7975,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="56" t="s">
+      <c r="P10" s="57" t="s">
         <v>305</v>
       </c>
     </row>
@@ -7960,7 +7996,7 @@
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="60" t="s">
         <v>315</v>
       </c>
       <c r="J11" s="11">
@@ -7981,7 +8017,7 @@
       <c r="O11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="56"/>
+      <c r="P11" s="57"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -8000,7 +8036,7 @@
       <c r="G12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="59"/>
+      <c r="H12" s="60"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -8038,7 +8074,7 @@
       <c r="G13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H13" s="59"/>
+      <c r="H13" s="60"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -8055,7 +8091,7 @@
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="56" t="s">
+      <c r="P13" s="57" t="s">
         <v>305</v>
       </c>
     </row>
@@ -8076,7 +8112,7 @@
       <c r="G14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="59"/>
+      <c r="H14" s="60"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -8095,7 +8131,7 @@
       <c r="O14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="56"/>
+      <c r="P14" s="57"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
@@ -8114,7 +8150,7 @@
       <c r="G15" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H15" s="59"/>
+      <c r="H15" s="60"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -8131,7 +8167,7 @@
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="59" t="s">
+      <c r="P15" s="60" t="s">
         <v>316</v>
       </c>
     </row>
@@ -8152,7 +8188,7 @@
       <c r="G16" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="59"/>
+      <c r="H16" s="60"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -8169,7 +8205,7 @@
       <c r="O16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="59"/>
+      <c r="P16" s="60"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -8188,7 +8224,7 @@
       <c r="G17" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H17" s="59"/>
+      <c r="H17" s="60"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -8205,7 +8241,9 @@
         <v>328</v>
       </c>
       <c r="O17" s="12"/>
-      <c r="P17" s="60"/>
+      <c r="P17" s="54" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -8221,12 +8259,12 @@
         <v>263</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>229</v>
+        <v>329</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="56" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -8267,7 +8305,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="55"/>
+      <c r="H19" s="56"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -8306,7 +8344,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="55"/>
+      <c r="H20" s="56"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -8323,7 +8361,7 @@
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="58" t="s">
+      <c r="P20" s="59" t="s">
         <v>316</v>
       </c>
     </row>
@@ -8346,7 +8384,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="55"/>
+      <c r="H21" s="56"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -8363,7 +8401,7 @@
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="58"/>
+      <c r="P21" s="59"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">

--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A689FBB-DD22-40AC-9446-46221BC4DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BF0BD1-4BAA-44C7-BCF4-71F8854FEAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangPrimer25K (SLOT無し版)" sheetId="3" r:id="rId1"/>
     <sheet name="TangPrimer25K(SLOTあり版)" sheetId="2" r:id="rId2"/>
     <sheet name="TangNano20K(SLOT無し版)" sheetId="5" r:id="rId3"/>
     <sheet name="TangNano20K(SLOTあり版)" sheetId="4" r:id="rId4"/>
+    <sheet name="IO Expander" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="414">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1390,6 +1391,290 @@
   </si>
   <si>
     <t>ROM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DIO DIR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Decoder</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_sel[2]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_sel[1]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_sel[0]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_clk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.579545MHz</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_dio[7]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_dio[6]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_dio[5]</t>
+  </si>
+  <si>
+    <t>ioe_dio[4]</t>
+  </si>
+  <si>
+    <t>ioe_dio[3]</t>
+  </si>
+  <si>
+    <t>ioe_dio[2]</t>
+  </si>
+  <si>
+    <t>ioe_dio[1]</t>
+  </si>
+  <si>
+    <t>ioe_dio[0]</t>
+  </si>
+  <si>
+    <t>a15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a13</t>
+  </si>
+  <si>
+    <t>a12</t>
+  </si>
+  <si>
+    <t>a11</t>
+  </si>
+  <si>
+    <t>a10</t>
+  </si>
+  <si>
+    <t>a9</t>
+  </si>
+  <si>
+    <t>a8</t>
+  </si>
+  <si>
+    <t>74LCX138</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a5</t>
+  </si>
+  <si>
+    <t>a4</t>
+  </si>
+  <si>
+    <t>a3</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>a0</t>
+  </si>
+  <si>
+    <t>a6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>d7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>d5</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>d0</t>
+  </si>
+  <si>
+    <t>d6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/wr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/rd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/reset</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ioe_reset_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/merq</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/iorq</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/m1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/rfsh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/sltsl1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/slt1_cs12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/slt1_cs2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/slt1_cs1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/sltsl2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/slt2_cs12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/slt2_cs2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/slt2_cs1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>busdir</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/int</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/wait</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RESERVE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_l</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_r</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_l</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_r</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy1_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>joy2_d</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1431,7 +1716,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1522,8 +1807,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1701,13 +1992,271 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1890,6 +2439,141 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2451,6 +3135,347 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5121" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3B5420C-E479-CEDE-E85A-8C1ED909791D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2057400" y="5657850"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5122" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DBAEF9B-2834-1148-F151-A283DDA67876}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="5486400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5123" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C94784-B933-EEC1-DD4B-14F7930C3CC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="5486400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5124" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{483C20CC-0C5F-857E-C66A-837C0B9B9D4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="6343650"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5125" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{142C68C3-2DB7-322C-A0DF-51E8C1D1432F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="6343650"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5126" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75E28A6B-0069-7DE4-62DC-83B3D2478967}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="6343650"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5127" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64EED7F3-BCAD-0140-267D-C5199C8B6D39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2057400" y="6172200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -8523,4 +9548,491 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A67668-6EEE-4108-B879-B877CE3F1C10}">
+  <dimension ref="B1:K17"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="9" style="61"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B2" s="68"/>
+      <c r="C2" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="70">
+        <v>0</v>
+      </c>
+      <c r="E2" s="71">
+        <v>1</v>
+      </c>
+      <c r="F2" s="71">
+        <v>2</v>
+      </c>
+      <c r="G2" s="71">
+        <v>3</v>
+      </c>
+      <c r="H2" s="71">
+        <v>4</v>
+      </c>
+      <c r="I2" s="71">
+        <v>5</v>
+      </c>
+      <c r="J2" s="71">
+        <v>6</v>
+      </c>
+      <c r="K2" s="69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="72"/>
+      <c r="C3" s="73" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>339</v>
+      </c>
+      <c r="E3" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="G3" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="I3" s="76" t="s">
+        <v>340</v>
+      </c>
+      <c r="J3" s="76" t="s">
+        <v>340</v>
+      </c>
+      <c r="K3" s="77" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B4" s="78">
+        <v>1</v>
+      </c>
+      <c r="C4" s="79" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" s="80" t="s">
+        <v>355</v>
+      </c>
+      <c r="E4" s="81" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="81" t="s">
+        <v>372</v>
+      </c>
+      <c r="G4" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="H4" s="81" t="s">
+        <v>390</v>
+      </c>
+      <c r="I4" s="81" t="s">
+        <v>372</v>
+      </c>
+      <c r="J4" s="81" t="s">
+        <v>398</v>
+      </c>
+      <c r="K4" s="82" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B5" s="83">
+        <v>2</v>
+      </c>
+      <c r="C5" s="84" t="s">
+        <v>348</v>
+      </c>
+      <c r="D5" s="85" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="86" t="s">
+        <v>379</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>381</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>391</v>
+      </c>
+      <c r="I5" s="86" t="s">
+        <v>379</v>
+      </c>
+      <c r="J5" s="86" t="s">
+        <v>399</v>
+      </c>
+      <c r="K5" s="87" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B6" s="83">
+        <v>3</v>
+      </c>
+      <c r="C6" s="84" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="85" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" s="86" t="s">
+        <v>365</v>
+      </c>
+      <c r="F6" s="86" t="s">
+        <v>373</v>
+      </c>
+      <c r="G6" s="86" t="s">
+        <v>384</v>
+      </c>
+      <c r="H6" s="86" t="s">
+        <v>392</v>
+      </c>
+      <c r="I6" s="86" t="s">
+        <v>373</v>
+      </c>
+      <c r="J6" s="86" t="s">
+        <v>400</v>
+      </c>
+      <c r="K6" s="87" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B7" s="83">
+        <v>4</v>
+      </c>
+      <c r="C7" s="84" t="s">
+        <v>350</v>
+      </c>
+      <c r="D7" s="85" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="86" t="s">
+        <v>366</v>
+      </c>
+      <c r="F7" s="86" t="s">
+        <v>374</v>
+      </c>
+      <c r="G7" s="86" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="86" t="s">
+        <v>393</v>
+      </c>
+      <c r="I7" s="86" t="s">
+        <v>374</v>
+      </c>
+      <c r="J7" s="86" t="s">
+        <v>401</v>
+      </c>
+      <c r="K7" s="87" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B8" s="83">
+        <v>5</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>351</v>
+      </c>
+      <c r="D8" s="85" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>367</v>
+      </c>
+      <c r="F8" s="86" t="s">
+        <v>375</v>
+      </c>
+      <c r="G8" s="86" t="s">
+        <v>386</v>
+      </c>
+      <c r="H8" s="86" t="s">
+        <v>394</v>
+      </c>
+      <c r="I8" s="86" t="s">
+        <v>375</v>
+      </c>
+      <c r="J8" s="86" t="s">
+        <v>402</v>
+      </c>
+      <c r="K8" s="87" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B9" s="83">
+        <v>6</v>
+      </c>
+      <c r="C9" s="84" t="s">
+        <v>352</v>
+      </c>
+      <c r="D9" s="85" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="F9" s="86" t="s">
+        <v>376</v>
+      </c>
+      <c r="G9" s="86" t="s">
+        <v>387</v>
+      </c>
+      <c r="H9" s="86" t="s">
+        <v>395</v>
+      </c>
+      <c r="I9" s="86" t="s">
+        <v>376</v>
+      </c>
+      <c r="J9" s="86" t="s">
+        <v>403</v>
+      </c>
+      <c r="K9" s="87" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B10" s="83">
+        <v>7</v>
+      </c>
+      <c r="C10" s="84" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>361</v>
+      </c>
+      <c r="E10" s="86" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="G10" s="86" t="s">
+        <v>388</v>
+      </c>
+      <c r="H10" s="86" t="s">
+        <v>396</v>
+      </c>
+      <c r="I10" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="J10" s="86" t="s">
+        <v>404</v>
+      </c>
+      <c r="K10" s="87" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="88">
+        <v>8</v>
+      </c>
+      <c r="C11" s="89" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>362</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>370</v>
+      </c>
+      <c r="F11" s="91" t="s">
+        <v>378</v>
+      </c>
+      <c r="G11" s="91" t="s">
+        <v>389</v>
+      </c>
+      <c r="H11" s="91" t="s">
+        <v>397</v>
+      </c>
+      <c r="I11" s="91" t="s">
+        <v>378</v>
+      </c>
+      <c r="J11" s="91" t="s">
+        <v>405</v>
+      </c>
+      <c r="K11" s="92" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B12" s="68">
+        <v>9</v>
+      </c>
+      <c r="C12" s="93" t="s">
+        <v>342</v>
+      </c>
+      <c r="D12" s="70">
+        <v>0</v>
+      </c>
+      <c r="E12" s="71">
+        <v>0</v>
+      </c>
+      <c r="F12" s="71">
+        <v>0</v>
+      </c>
+      <c r="G12" s="71">
+        <v>0</v>
+      </c>
+      <c r="H12" s="71">
+        <v>1</v>
+      </c>
+      <c r="I12" s="71">
+        <v>1</v>
+      </c>
+      <c r="J12" s="71">
+        <v>1</v>
+      </c>
+      <c r="K12" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B13" s="83">
+        <v>10</v>
+      </c>
+      <c r="C13" s="94" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="85">
+        <v>0</v>
+      </c>
+      <c r="E13" s="86">
+        <v>0</v>
+      </c>
+      <c r="F13" s="86">
+        <v>1</v>
+      </c>
+      <c r="G13" s="86">
+        <v>1</v>
+      </c>
+      <c r="H13" s="86">
+        <v>0</v>
+      </c>
+      <c r="I13" s="86">
+        <v>0</v>
+      </c>
+      <c r="J13" s="86">
+        <v>1</v>
+      </c>
+      <c r="K13" s="87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="72">
+        <v>11</v>
+      </c>
+      <c r="C14" s="95" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" s="96">
+        <v>0</v>
+      </c>
+      <c r="E14" s="97">
+        <v>1</v>
+      </c>
+      <c r="F14" s="97">
+        <v>0</v>
+      </c>
+      <c r="G14" s="97">
+        <v>1</v>
+      </c>
+      <c r="H14" s="97">
+        <v>0</v>
+      </c>
+      <c r="I14" s="97">
+        <v>1</v>
+      </c>
+      <c r="J14" s="97">
+        <v>0</v>
+      </c>
+      <c r="K14" s="73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="98">
+        <v>12</v>
+      </c>
+      <c r="C15" s="99" t="s">
+        <v>383</v>
+      </c>
+      <c r="D15" s="66" t="s">
+        <v>382</v>
+      </c>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="65"/>
+    </row>
+    <row r="16" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="100">
+        <v>13</v>
+      </c>
+      <c r="C16" s="101" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" s="67" t="s">
+        <v>346</v>
+      </c>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="63"/>
+    </row>
+    <row r="17" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="100"/>
+      <c r="C17" s="102" t="s">
+        <v>341</v>
+      </c>
+      <c r="D17" s="103" t="s">
+        <v>363</v>
+      </c>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="105"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D16:K16"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="D17:K17"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BF0BD1-4BAA-44C7-BCF4-71F8854FEAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A19011B-88C9-4B65-A037-D8DE3A0653BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangPrimer25K (SLOT無し版)" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="TangNano20K(SLOT無し版)" sheetId="5" r:id="rId3"/>
     <sheet name="TangNano20K(SLOTあり版)" sheetId="4" r:id="rId4"/>
     <sheet name="IO Expander" sheetId="6" r:id="rId5"/>
+    <sheet name="IO Expander Timing_x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009__x0009_" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="458">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1677,12 +1678,172 @@
     <t>joy2_d</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>74LCX238</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IN CLOCK (3.54x8x3=85.96MHz)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FPGA DIN/DOUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOUT0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOUT1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOUT2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOUT3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOUT4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DIN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DOUT0</t>
+  </si>
+  <si>
+    <t>DOUT1</t>
+  </si>
+  <si>
+    <t>DOUT2</t>
+  </si>
+  <si>
+    <t>DOUT3</t>
+  </si>
+  <si>
+    <t>DOUT4</t>
+  </si>
+  <si>
+    <t>DIN</t>
+  </si>
+  <si>
+    <t>FPGA DadaDir</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OUTPUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INPUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OUTPUT</t>
+  </si>
+  <si>
+    <t>INPUT</t>
+  </si>
+  <si>
+    <t>FPGA Cycle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cycle1</t>
+  </si>
+  <si>
+    <t>Cycle2</t>
+  </si>
+  <si>
+    <t>Cycle3</t>
+  </si>
+  <si>
+    <t>Cycle4</t>
+  </si>
+  <si>
+    <t>Cycle5</t>
+  </si>
+  <si>
+    <t>Cycle6</t>
+  </si>
+  <si>
+    <t>Cycle7</t>
+  </si>
+  <si>
+    <t>Cycle0</t>
+  </si>
+  <si>
+    <t>FPGA 3.54MHz</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SLOT DOUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SLOT DATA OUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SLOT DATA IN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JOYSTICK1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JOYSTICK2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STATE</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1715,8 +1876,16 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1813,8 +1982,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF747474"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -2250,13 +2461,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2422,6 +2712,114 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2440,7 +2838,7 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2449,123 +2847,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2574,6 +2864,159 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="35" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3139,13 +3582,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -3187,13 +3630,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -3235,13 +3678,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -3283,13 +3726,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>133349</xdr:rowOff>
@@ -3331,13 +3774,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>133349</xdr:rowOff>
@@ -3379,13 +3822,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>133349</xdr:rowOff>
@@ -3427,13 +3870,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>133351</xdr:rowOff>
@@ -4197,7 +4640,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="55" t="s">
+      <c r="AC9" s="91" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4258,7 +4701,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="55"/>
+      <c r="AC10" s="91"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -4321,7 +4764,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="55"/>
+      <c r="AC11" s="91"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -4382,7 +4825,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="55"/>
+      <c r="AC12" s="91"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -4447,7 +4890,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="55"/>
+      <c r="AC13" s="91"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -4516,7 +4959,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="55"/>
+      <c r="AC14" s="91"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -4779,7 +5222,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="56" t="s">
+      <c r="AC18" s="92" t="s">
         <v>246</v>
       </c>
     </row>
@@ -4844,7 +5287,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="56"/>
+      <c r="AC19" s="92"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -4903,7 +5346,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="56"/>
+      <c r="AC20" s="92"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -4966,7 +5409,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="56"/>
+      <c r="AC21" s="92"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -5027,7 +5470,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="55" t="s">
+      <c r="AC22" s="91" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5090,7 +5533,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="55"/>
+      <c r="AC23" s="91"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -5151,7 +5594,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="55"/>
+      <c r="AC24" s="91"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -5210,7 +5653,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="55"/>
+      <c r="AC25" s="91"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -5273,7 +5716,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="55"/>
+      <c r="AC26" s="91"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -5334,7 +5777,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="55"/>
+      <c r="AC27" s="91"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -6218,7 +6661,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="55" t="s">
+      <c r="AC9" s="91" t="s">
         <v>245</v>
       </c>
     </row>
@@ -6287,7 +6730,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="55"/>
+      <c r="AC10" s="91"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -6354,7 +6797,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="55"/>
+      <c r="AC11" s="91"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -6421,7 +6864,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="55"/>
+      <c r="AC12" s="91"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -6490,7 +6933,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="55"/>
+      <c r="AC13" s="91"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -6563,7 +7006,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="55"/>
+      <c r="AC14" s="91"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -6848,7 +7291,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="56" t="s">
+      <c r="AC18" s="92" t="s">
         <v>246</v>
       </c>
     </row>
@@ -6917,7 +7360,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="56"/>
+      <c r="AC19" s="92"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -6984,7 +7427,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="56"/>
+      <c r="AC20" s="92"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -7055,7 +7498,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="56"/>
+      <c r="AC21" s="92"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -7120,7 +7563,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="55" t="s">
+      <c r="AC22" s="91" t="s">
         <v>244</v>
       </c>
     </row>
@@ -7187,7 +7630,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="55"/>
+      <c r="AC23" s="91"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -7252,7 +7695,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="55"/>
+      <c r="AC24" s="91"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -7315,7 +7758,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="55"/>
+      <c r="AC25" s="91"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -7378,7 +7821,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="55"/>
+      <c r="AC26" s="91"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -7443,7 +7886,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="55"/>
+      <c r="AC27" s="91"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -7572,7 +8015,7 @@
       <c r="AB29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AC29" s="57" t="s">
+      <c r="AC29" s="93" t="s">
         <v>243</v>
       </c>
     </row>
@@ -7643,7 +8086,7 @@
       <c r="AB30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC30" s="57"/>
+      <c r="AC30" s="93"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="21">
@@ -7708,7 +8151,7 @@
       <c r="AB31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC31" s="57"/>
+      <c r="AC31" s="93"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
@@ -7771,7 +8214,7 @@
       <c r="AB32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC32" s="57"/>
+      <c r="AC32" s="93"/>
     </row>
     <row r="33" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
@@ -7875,14 +8318,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -8182,7 +8625,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="57" t="s">
+      <c r="P10" s="93" t="s">
         <v>305</v>
       </c>
     </row>
@@ -8220,7 +8663,7 @@
       <c r="O11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P11" s="57"/>
+      <c r="P11" s="93"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -8443,7 +8886,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="56" t="s">
+      <c r="H18" s="92" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -8484,7 +8927,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="56"/>
+      <c r="H19" s="92"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -8523,7 +8966,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="56"/>
+      <c r="H20" s="92"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -8557,7 +9000,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="56"/>
+      <c r="H21" s="92"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -8684,14 +9127,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -8750,7 +9193,7 @@
       <c r="G4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="55" t="s">
+      <c r="H4" s="91" t="s">
         <v>244</v>
       </c>
       <c r="J4" s="8">
@@ -8789,7 +9232,7 @@
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="55"/>
+      <c r="H5" s="91"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -8826,7 +9269,7 @@
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="55"/>
+      <c r="H6" s="91"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -8864,7 +9307,7 @@
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="55"/>
+      <c r="H7" s="91"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -8939,7 +9382,7 @@
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="91" t="s">
         <v>244</v>
       </c>
       <c r="J9" s="11">
@@ -8981,7 +9424,7 @@
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="55"/>
+      <c r="H10" s="91"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -9000,7 +9443,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="57" t="s">
+      <c r="P10" s="93" t="s">
         <v>305</v>
       </c>
     </row>
@@ -9021,7 +9464,7 @@
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="60" t="s">
+      <c r="H11" s="96" t="s">
         <v>315</v>
       </c>
       <c r="J11" s="11">
@@ -9042,7 +9485,7 @@
       <c r="O11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="57"/>
+      <c r="P11" s="93"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -9061,7 +9504,7 @@
       <c r="G12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="96"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -9099,7 +9542,7 @@
       <c r="G13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H13" s="60"/>
+      <c r="H13" s="96"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -9116,7 +9559,7 @@
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="93" t="s">
         <v>305</v>
       </c>
     </row>
@@ -9137,7 +9580,7 @@
       <c r="G14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="60"/>
+      <c r="H14" s="96"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -9156,7 +9599,7 @@
       <c r="O14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="57"/>
+      <c r="P14" s="93"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
@@ -9175,7 +9618,7 @@
       <c r="G15" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="96"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -9192,7 +9635,7 @@
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="60" t="s">
+      <c r="P15" s="96" t="s">
         <v>316</v>
       </c>
     </row>
@@ -9213,7 +9656,7 @@
       <c r="G16" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="60"/>
+      <c r="H16" s="96"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -9230,7 +9673,7 @@
       <c r="O16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="60"/>
+      <c r="P16" s="96"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -9249,7 +9692,7 @@
       <c r="G17" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H17" s="60"/>
+      <c r="H17" s="96"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -9289,7 +9732,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="56" t="s">
+      <c r="H18" s="92" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -9330,7 +9773,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="56"/>
+      <c r="H19" s="92"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -9369,7 +9812,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="56"/>
+      <c r="H20" s="92"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -9386,7 +9829,7 @@
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="59" t="s">
+      <c r="P20" s="95" t="s">
         <v>316</v>
       </c>
     </row>
@@ -9409,7 +9852,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="56"/>
+      <c r="H21" s="92"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -9426,7 +9869,7 @@
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="59"/>
+      <c r="P21" s="95"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -9552,487 +9995,1445 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A67668-6EEE-4108-B879-B877CE3F1C10}">
-  <dimension ref="B1:K17"/>
+  <dimension ref="C1:L17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="9" style="61"/>
+    <col min="1" max="2" width="3" customWidth="1"/>
+    <col min="3" max="3" width="3.5" style="55" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="9" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B2" s="68"/>
-      <c r="C2" s="69" t="s">
+    <row r="1" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C2" s="57"/>
+      <c r="D2" s="58" t="s">
         <v>337</v>
       </c>
-      <c r="D2" s="70">
+      <c r="E2" s="59">
         <v>0</v>
       </c>
-      <c r="E2" s="71">
+      <c r="F2" s="60">
         <v>1</v>
       </c>
-      <c r="F2" s="71">
+      <c r="G2" s="60">
         <v>2</v>
       </c>
-      <c r="G2" s="71">
+      <c r="H2" s="60">
         <v>3</v>
       </c>
-      <c r="H2" s="71">
+      <c r="I2" s="60">
         <v>4</v>
       </c>
-      <c r="I2" s="71">
+      <c r="J2" s="60">
         <v>5</v>
       </c>
-      <c r="J2" s="71">
+      <c r="K2" s="60">
         <v>6</v>
       </c>
-      <c r="K2" s="69">
+      <c r="L2" s="58">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="72"/>
-      <c r="C3" s="73" t="s">
+    <row r="3" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="61"/>
+      <c r="D3" s="62" t="s">
         <v>338</v>
       </c>
-      <c r="D3" s="74" t="s">
+      <c r="E3" s="63" t="s">
         <v>339</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="F3" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="G3" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="H3" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="75" t="s">
+      <c r="I3" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="J3" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="J3" s="76" t="s">
+      <c r="K3" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="K3" s="77" t="s">
+      <c r="L3" s="66" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B4" s="78">
+    <row r="4" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C4" s="67">
         <v>1</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="D4" s="68" t="s">
         <v>347</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="E4" s="69" t="s">
         <v>355</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="F4" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="F4" s="81" t="s">
+      <c r="G4" s="70" t="s">
+        <v>380</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="I4" s="70" t="s">
         <v>372</v>
       </c>
-      <c r="G4" s="81" t="s">
-        <v>380</v>
-      </c>
-      <c r="H4" s="81" t="s">
-        <v>390</v>
-      </c>
-      <c r="I4" s="81" t="s">
+      <c r="J4" s="70" t="s">
         <v>372</v>
       </c>
-      <c r="J4" s="81" t="s">
+      <c r="K4" s="70" t="s">
         <v>398</v>
       </c>
-      <c r="K4" s="82" t="s">
+      <c r="L4" s="71" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B5" s="83">
+    <row r="5" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C5" s="72">
         <v>2</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="D5" s="73" t="s">
         <v>348</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="E5" s="74" t="s">
         <v>356</v>
       </c>
-      <c r="E5" s="86" t="s">
+      <c r="F5" s="75" t="s">
         <v>371</v>
       </c>
-      <c r="F5" s="86" t="s">
+      <c r="G5" s="75" t="s">
+        <v>381</v>
+      </c>
+      <c r="H5" s="75" t="s">
+        <v>391</v>
+      </c>
+      <c r="I5" s="75" t="s">
         <v>379</v>
       </c>
-      <c r="G5" s="86" t="s">
-        <v>381</v>
-      </c>
-      <c r="H5" s="86" t="s">
-        <v>391</v>
-      </c>
-      <c r="I5" s="86" t="s">
+      <c r="J5" s="75" t="s">
         <v>379</v>
       </c>
-      <c r="J5" s="86" t="s">
+      <c r="K5" s="75" t="s">
         <v>399</v>
       </c>
-      <c r="K5" s="87" t="s">
+      <c r="L5" s="76" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B6" s="83">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C6" s="72">
         <v>3</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="D6" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="E6" s="74" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="86" t="s">
+      <c r="F6" s="75" t="s">
         <v>365</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="G6" s="75" t="s">
+        <v>384</v>
+      </c>
+      <c r="H6" s="75" t="s">
+        <v>392</v>
+      </c>
+      <c r="I6" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="G6" s="86" t="s">
-        <v>384</v>
-      </c>
-      <c r="H6" s="86" t="s">
-        <v>392</v>
-      </c>
-      <c r="I6" s="86" t="s">
+      <c r="J6" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="J6" s="86" t="s">
+      <c r="K6" s="75" t="s">
         <v>400</v>
       </c>
-      <c r="K6" s="87" t="s">
+      <c r="L6" s="76" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B7" s="83">
+    <row r="7" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C7" s="72">
         <v>4</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="D7" s="73" t="s">
         <v>350</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="E7" s="74" t="s">
         <v>358</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="F7" s="75" t="s">
         <v>366</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="G7" s="75" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="75" t="s">
+        <v>393</v>
+      </c>
+      <c r="I7" s="75" t="s">
         <v>374</v>
       </c>
-      <c r="G7" s="86" t="s">
-        <v>385</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>393</v>
-      </c>
-      <c r="I7" s="86" t="s">
+      <c r="J7" s="75" t="s">
         <v>374</v>
       </c>
-      <c r="J7" s="86" t="s">
+      <c r="K7" s="75" t="s">
         <v>401</v>
       </c>
-      <c r="K7" s="87" t="s">
+      <c r="L7" s="76" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B8" s="83">
+    <row r="8" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C8" s="72">
         <v>5</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="D8" s="73" t="s">
         <v>351</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="E8" s="74" t="s">
         <v>359</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="F8" s="75" t="s">
         <v>367</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="G8" s="75" t="s">
+        <v>386</v>
+      </c>
+      <c r="H8" s="75" t="s">
+        <v>394</v>
+      </c>
+      <c r="I8" s="75" t="s">
         <v>375</v>
       </c>
-      <c r="G8" s="86" t="s">
-        <v>386</v>
-      </c>
-      <c r="H8" s="86" t="s">
-        <v>394</v>
-      </c>
-      <c r="I8" s="86" t="s">
+      <c r="J8" s="75" t="s">
         <v>375</v>
       </c>
-      <c r="J8" s="86" t="s">
+      <c r="K8" s="75" t="s">
         <v>402</v>
       </c>
-      <c r="K8" s="87" t="s">
+      <c r="L8" s="76" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B9" s="83">
+    <row r="9" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C9" s="72">
         <v>6</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="D9" s="73" t="s">
         <v>352</v>
       </c>
-      <c r="D9" s="85" t="s">
+      <c r="E9" s="74" t="s">
         <v>360</v>
       </c>
-      <c r="E9" s="86" t="s">
+      <c r="F9" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="F9" s="86" t="s">
+      <c r="G9" s="75" t="s">
+        <v>387</v>
+      </c>
+      <c r="H9" s="75" t="s">
+        <v>395</v>
+      </c>
+      <c r="I9" s="75" t="s">
         <v>376</v>
       </c>
-      <c r="G9" s="86" t="s">
-        <v>387</v>
-      </c>
-      <c r="H9" s="86" t="s">
-        <v>395</v>
-      </c>
-      <c r="I9" s="86" t="s">
+      <c r="J9" s="75" t="s">
         <v>376</v>
       </c>
-      <c r="J9" s="86" t="s">
+      <c r="K9" s="75" t="s">
         <v>403</v>
       </c>
-      <c r="K9" s="87" t="s">
+      <c r="L9" s="76" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B10" s="83">
+    <row r="10" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C10" s="72">
         <v>7</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="D10" s="73" t="s">
         <v>353</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="E10" s="74" t="s">
         <v>361</v>
       </c>
-      <c r="E10" s="86" t="s">
+      <c r="F10" s="75" t="s">
         <v>369</v>
       </c>
-      <c r="F10" s="86" t="s">
+      <c r="G10" s="75" t="s">
+        <v>388</v>
+      </c>
+      <c r="H10" s="75" t="s">
+        <v>396</v>
+      </c>
+      <c r="I10" s="75" t="s">
         <v>377</v>
       </c>
-      <c r="G10" s="86" t="s">
-        <v>388</v>
-      </c>
-      <c r="H10" s="86" t="s">
-        <v>396</v>
-      </c>
-      <c r="I10" s="86" t="s">
+      <c r="J10" s="75" t="s">
         <v>377</v>
       </c>
-      <c r="J10" s="86" t="s">
+      <c r="K10" s="75" t="s">
         <v>404</v>
       </c>
-      <c r="K10" s="87" t="s">
+      <c r="L10" s="76" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="88">
+    <row r="11" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="77">
         <v>8</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="D11" s="78" t="s">
         <v>354</v>
       </c>
-      <c r="D11" s="90" t="s">
+      <c r="E11" s="79" t="s">
         <v>362</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="F11" s="80" t="s">
         <v>370</v>
       </c>
-      <c r="F11" s="91" t="s">
+      <c r="G11" s="80" t="s">
+        <v>389</v>
+      </c>
+      <c r="H11" s="80" t="s">
+        <v>397</v>
+      </c>
+      <c r="I11" s="80" t="s">
         <v>378</v>
       </c>
-      <c r="G11" s="91" t="s">
-        <v>389</v>
-      </c>
-      <c r="H11" s="91" t="s">
-        <v>397</v>
-      </c>
-      <c r="I11" s="91" t="s">
+      <c r="J11" s="80" t="s">
         <v>378</v>
       </c>
-      <c r="J11" s="91" t="s">
+      <c r="K11" s="80" t="s">
         <v>405</v>
       </c>
-      <c r="K11" s="92" t="s">
+      <c r="L11" s="81" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B12" s="68">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C12" s="57">
         <v>9</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="D12" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="D12" s="70">
+      <c r="E12" s="59">
         <v>0</v>
       </c>
-      <c r="E12" s="71">
+      <c r="F12" s="60">
         <v>0</v>
       </c>
-      <c r="F12" s="71">
+      <c r="G12" s="60">
         <v>0</v>
       </c>
-      <c r="G12" s="71">
+      <c r="H12" s="60">
         <v>0</v>
       </c>
-      <c r="H12" s="71">
+      <c r="I12" s="60">
         <v>1</v>
       </c>
-      <c r="I12" s="71">
+      <c r="J12" s="60">
         <v>1</v>
       </c>
-      <c r="J12" s="71">
+      <c r="K12" s="60">
         <v>1</v>
       </c>
-      <c r="K12" s="69">
+      <c r="L12" s="58">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B13" s="83">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C13" s="72">
         <v>10</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="D13" s="83" t="s">
         <v>343</v>
       </c>
-      <c r="D13" s="85">
+      <c r="E13" s="74">
         <v>0</v>
       </c>
-      <c r="E13" s="86">
+      <c r="F13" s="75">
         <v>0</v>
       </c>
-      <c r="F13" s="86">
+      <c r="G13" s="75">
         <v>1</v>
       </c>
-      <c r="G13" s="86">
+      <c r="H13" s="75">
         <v>1</v>
       </c>
-      <c r="H13" s="86">
+      <c r="I13" s="75">
         <v>0</v>
       </c>
-      <c r="I13" s="86">
+      <c r="J13" s="75">
         <v>0</v>
       </c>
-      <c r="J13" s="86">
+      <c r="K13" s="75">
         <v>1</v>
       </c>
-      <c r="K13" s="87">
+      <c r="L13" s="76">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="72">
+    <row r="14" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="61">
         <v>11</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="D14" s="84" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="96">
+      <c r="E14" s="85">
         <v>0</v>
       </c>
-      <c r="E14" s="97">
+      <c r="F14" s="86">
         <v>1</v>
       </c>
-      <c r="F14" s="97">
+      <c r="G14" s="86">
         <v>0</v>
       </c>
-      <c r="G14" s="97">
+      <c r="H14" s="86">
         <v>1</v>
       </c>
-      <c r="H14" s="97">
+      <c r="I14" s="86">
         <v>0</v>
       </c>
-      <c r="I14" s="97">
+      <c r="J14" s="86">
         <v>1</v>
       </c>
-      <c r="J14" s="97">
+      <c r="K14" s="86">
         <v>0</v>
       </c>
-      <c r="K14" s="73">
+      <c r="L14" s="62">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="98">
+    <row r="15" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="87">
         <v>12</v>
       </c>
-      <c r="C15" s="99" t="s">
+      <c r="D15" s="88" t="s">
         <v>383</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="E15" s="100" t="s">
         <v>382</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
-    </row>
-    <row r="16" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="100">
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="102"/>
+    </row>
+    <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="89">
         <v>13</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="D16" s="90" t="s">
         <v>345</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="E16" s="97" t="s">
         <v>346</v>
       </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="63"/>
-    </row>
-    <row r="17" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="100"/>
-      <c r="C17" s="102" t="s">
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="99"/>
+    </row>
+    <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="89"/>
+      <c r="D17" s="56" t="s">
         <v>341</v>
       </c>
-      <c r="D17" s="103" t="s">
-        <v>363</v>
-      </c>
-      <c r="E17" s="104"/>
+      <c r="E17" s="103" t="s">
+        <v>414</v>
+      </c>
       <c r="F17" s="104"/>
       <c r="G17" s="104"/>
       <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="105"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="103" t="s">
+        <v>363</v>
+      </c>
+      <c r="K17" s="104"/>
+      <c r="L17" s="105"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="D17:K17"/>
+  <mergeCells count="4">
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="E15:L15"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="E17:I17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5560DAE5-66A8-4B9C-9E5B-C6113045F168}">
+  <dimension ref="A1:BS19"/>
+  <sheetFormatPr defaultColWidth="4.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="4.25" style="106"/>
+    <col min="9" max="11" width="4.25" style="106"/>
+    <col min="15" max="17" width="4.25" style="106"/>
+    <col min="21" max="23" width="4.25" style="106"/>
+    <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.25" style="106"/>
+    <col min="33" max="35" width="4.25" style="106"/>
+    <col min="39" max="41" width="4.25" style="106"/>
+    <col min="45" max="47" width="4.25" style="106"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:62" x14ac:dyDescent="0.15">
+      <c r="AK1">
+        <v>11.6402131183339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="155" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="106">
+        <v>1</v>
+      </c>
+      <c r="D2" s="106">
+        <v>2</v>
+      </c>
+      <c r="E2" s="106">
+        <v>3</v>
+      </c>
+      <c r="F2" s="156">
+        <v>4</v>
+      </c>
+      <c r="G2" s="156">
+        <v>5</v>
+      </c>
+      <c r="H2" s="156">
+        <v>6</v>
+      </c>
+      <c r="I2" s="106">
+        <v>7</v>
+      </c>
+      <c r="J2" s="106">
+        <v>8</v>
+      </c>
+      <c r="K2" s="106">
+        <v>9</v>
+      </c>
+      <c r="L2" s="156">
+        <v>10</v>
+      </c>
+      <c r="M2" s="156">
+        <v>11</v>
+      </c>
+      <c r="N2" s="156">
+        <v>12</v>
+      </c>
+      <c r="O2" s="106">
+        <v>13</v>
+      </c>
+      <c r="P2" s="106">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="106">
+        <v>15</v>
+      </c>
+      <c r="R2" s="156">
+        <v>16</v>
+      </c>
+      <c r="S2" s="156">
+        <v>17</v>
+      </c>
+      <c r="T2" s="156">
+        <v>18</v>
+      </c>
+      <c r="U2" s="106">
+        <v>19</v>
+      </c>
+      <c r="V2" s="106">
+        <v>20</v>
+      </c>
+      <c r="W2" s="106">
+        <v>21</v>
+      </c>
+      <c r="X2" s="156">
+        <v>22</v>
+      </c>
+      <c r="Y2" s="156">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B3" s="107"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="109"/>
+      <c r="Y3" s="109"/>
+      <c r="Z3" s="109"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="109"/>
+      <c r="AE3" s="109"/>
+      <c r="AF3" s="109"/>
+      <c r="AG3" s="108"/>
+      <c r="AH3" s="108"/>
+      <c r="AI3" s="108"/>
+      <c r="AJ3" s="109"/>
+      <c r="AK3" s="109"/>
+      <c r="AL3" s="109"/>
+      <c r="AM3" s="108"/>
+      <c r="AN3" s="108"/>
+      <c r="AO3" s="108"/>
+      <c r="AP3" s="109"/>
+      <c r="AQ3" s="109"/>
+      <c r="AR3" s="109"/>
+      <c r="AS3" s="108"/>
+      <c r="AT3" s="108"/>
+      <c r="AU3" s="108"/>
+      <c r="AV3" s="109"/>
+      <c r="AW3" s="109"/>
+      <c r="AX3" s="109"/>
+    </row>
+    <row r="4" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B5" s="107"/>
+      <c r="C5" s="110" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="111"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="113" t="s">
+        <v>418</v>
+      </c>
+      <c r="G5" s="114"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="110" t="s">
+        <v>419</v>
+      </c>
+      <c r="J5" s="111"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="113" t="s">
+        <v>420</v>
+      </c>
+      <c r="M5" s="114"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="115" t="s">
+        <v>421</v>
+      </c>
+      <c r="P5" s="116"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="119" t="s">
+        <v>422</v>
+      </c>
+      <c r="T5" s="118"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="120" t="s">
+        <v>422</v>
+      </c>
+      <c r="W5" s="118"/>
+      <c r="X5" s="118"/>
+      <c r="Y5" s="119" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z5" s="118"/>
+      <c r="AA5" s="115" t="s">
+        <v>423</v>
+      </c>
+      <c r="AB5" s="116"/>
+      <c r="AC5" s="117"/>
+      <c r="AD5" s="121" t="s">
+        <v>424</v>
+      </c>
+      <c r="AE5" s="122"/>
+      <c r="AF5" s="123"/>
+      <c r="AG5" s="124" t="s">
+        <v>425</v>
+      </c>
+      <c r="AH5" s="125"/>
+      <c r="AI5" s="126"/>
+      <c r="AJ5" s="121" t="s">
+        <v>426</v>
+      </c>
+      <c r="AK5" s="122"/>
+      <c r="AL5" s="123"/>
+      <c r="AM5" s="124" t="s">
+        <v>427</v>
+      </c>
+      <c r="AN5" s="125"/>
+      <c r="AO5" s="126"/>
+      <c r="AP5" s="127"/>
+      <c r="AQ5" s="128" t="s">
+        <v>428</v>
+      </c>
+      <c r="AR5" s="127"/>
+      <c r="AS5" s="127"/>
+      <c r="AT5" s="129" t="s">
+        <v>428</v>
+      </c>
+      <c r="AU5" s="127"/>
+      <c r="AV5" s="127"/>
+      <c r="AW5" s="128" t="s">
+        <v>428</v>
+      </c>
+      <c r="AX5" s="127"/>
+    </row>
+    <row r="6" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="107"/>
+      <c r="C6" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="116"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="116"/>
+      <c r="P6" s="116"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="121" t="s">
+        <v>431</v>
+      </c>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="116"/>
+      <c r="W6" s="116"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="122"/>
+      <c r="Z6" s="123"/>
+      <c r="AA6" s="115" t="s">
+        <v>432</v>
+      </c>
+      <c r="AB6" s="116"/>
+      <c r="AC6" s="116"/>
+      <c r="AD6" s="122"/>
+      <c r="AE6" s="122"/>
+      <c r="AF6" s="122"/>
+      <c r="AG6" s="116"/>
+      <c r="AH6" s="116"/>
+      <c r="AI6" s="116"/>
+      <c r="AJ6" s="122"/>
+      <c r="AK6" s="122"/>
+      <c r="AL6" s="122"/>
+      <c r="AM6" s="116"/>
+      <c r="AN6" s="116"/>
+      <c r="AO6" s="117"/>
+      <c r="AP6" s="121" t="s">
+        <v>433</v>
+      </c>
+      <c r="AQ6" s="122"/>
+      <c r="AR6" s="122"/>
+      <c r="AS6" s="116"/>
+      <c r="AT6" s="116"/>
+      <c r="AU6" s="116"/>
+      <c r="AV6" s="122"/>
+      <c r="AW6" s="122"/>
+      <c r="AX6" s="123"/>
+    </row>
+    <row r="7" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" s="113" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="111"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="110" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" s="114"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="113" t="s">
+        <v>437</v>
+      </c>
+      <c r="I7" s="111"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="110" t="s">
+        <v>438</v>
+      </c>
+      <c r="L7" s="114"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="113" t="s">
+        <v>439</v>
+      </c>
+      <c r="O7" s="111"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="110" t="s">
+        <v>440</v>
+      </c>
+      <c r="R7" s="114"/>
+      <c r="S7" s="107"/>
+      <c r="T7" s="113" t="s">
+        <v>441</v>
+      </c>
+      <c r="U7" s="111"/>
+      <c r="V7" s="112"/>
+      <c r="W7" s="110" t="s">
+        <v>442</v>
+      </c>
+      <c r="X7" s="114"/>
+      <c r="Y7" s="107"/>
+      <c r="Z7" s="113" t="s">
+        <v>435</v>
+      </c>
+      <c r="AA7" s="116"/>
+      <c r="AB7" s="117"/>
+      <c r="AC7" s="116" t="s">
+        <v>443</v>
+      </c>
+      <c r="AD7" s="122"/>
+      <c r="AE7" s="123"/>
+      <c r="AF7" s="122" t="s">
+        <v>444</v>
+      </c>
+      <c r="AG7" s="125"/>
+      <c r="AH7" s="126"/>
+      <c r="AI7" s="125" t="s">
+        <v>445</v>
+      </c>
+      <c r="AJ7" s="122"/>
+      <c r="AK7" s="123"/>
+      <c r="AL7" s="122" t="s">
+        <v>446</v>
+      </c>
+      <c r="AM7" s="125"/>
+      <c r="AN7" s="126"/>
+      <c r="AO7" s="125" t="s">
+        <v>447</v>
+      </c>
+      <c r="AP7" s="122"/>
+      <c r="AQ7" s="123"/>
+      <c r="AR7" s="122" t="s">
+        <v>448</v>
+      </c>
+      <c r="AS7" s="125"/>
+      <c r="AT7" s="126"/>
+      <c r="AU7" s="125" t="s">
+        <v>449</v>
+      </c>
+      <c r="AV7" s="122"/>
+      <c r="AW7" s="123"/>
+      <c r="AX7" s="122" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="114"/>
+      <c r="S8" s="114"/>
+      <c r="T8" s="114"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="114"/>
+      <c r="Y8" s="114"/>
+      <c r="Z8" s="114"/>
+      <c r="AM8" s="111"/>
+      <c r="AN8" s="111"/>
+      <c r="AO8" s="111"/>
+      <c r="AP8" s="114"/>
+      <c r="AQ8" s="114"/>
+      <c r="AR8" s="114"/>
+      <c r="AS8" s="111"/>
+      <c r="AT8" s="111"/>
+      <c r="AU8" s="111"/>
+      <c r="AV8" s="114"/>
+      <c r="AW8" s="114"/>
+    </row>
+    <row r="9" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B9" s="130"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="134"/>
+      <c r="Z9" s="130"/>
+      <c r="AA9" s="131"/>
+      <c r="AB9" s="132"/>
+      <c r="AC9" s="132"/>
+      <c r="AD9" s="133"/>
+      <c r="AE9" s="133"/>
+      <c r="AF9" s="133"/>
+      <c r="AG9" s="132"/>
+      <c r="AH9" s="132"/>
+      <c r="AI9" s="132"/>
+      <c r="AJ9" s="133"/>
+      <c r="AK9" s="133"/>
+      <c r="AL9" s="134"/>
+      <c r="AW9" s="130"/>
+    </row>
+    <row r="11" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="133"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+    </row>
+    <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="94" t="s">
+        <v>452</v>
+      </c>
+      <c r="B12" s="114"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="113" t="s">
+        <v>417</v>
+      </c>
+      <c r="G12" s="114"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="135"/>
+      <c r="M12" s="135"/>
+      <c r="N12" s="135"/>
+      <c r="O12" s="136"/>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="136"/>
+      <c r="R12" s="135"/>
+      <c r="S12" s="135"/>
+      <c r="T12" s="135"/>
+      <c r="U12" s="136"/>
+      <c r="V12" s="136"/>
+      <c r="W12" s="136"/>
+      <c r="X12" s="135"/>
+      <c r="Y12" s="135"/>
+      <c r="Z12" s="135"/>
+      <c r="AA12" s="136"/>
+      <c r="AB12" s="136"/>
+      <c r="AC12" s="137"/>
+      <c r="AD12" s="113" t="s">
+        <v>417</v>
+      </c>
+      <c r="AE12" s="114"/>
+      <c r="AF12" s="114"/>
+      <c r="AG12" s="111"/>
+      <c r="AH12" s="111"/>
+      <c r="AI12" s="111"/>
+      <c r="AJ12" s="135"/>
+      <c r="AK12" s="135"/>
+      <c r="AL12" s="135"/>
+      <c r="AM12" s="136"/>
+      <c r="AN12" s="136"/>
+      <c r="AO12" s="136"/>
+      <c r="AP12" s="135"/>
+      <c r="AQ12" s="135"/>
+      <c r="AR12" s="135"/>
+      <c r="AS12" s="136"/>
+      <c r="AT12" s="136"/>
+      <c r="AU12" s="136"/>
+      <c r="AV12" s="135"/>
+      <c r="AW12" s="135"/>
+      <c r="AX12" s="135"/>
+      <c r="AY12" s="136"/>
+      <c r="AZ12" s="136"/>
+      <c r="BA12" s="137"/>
+    </row>
+    <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="94"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="115" t="s">
+        <v>418</v>
+      </c>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="111"/>
+      <c r="V13" s="111"/>
+      <c r="W13" s="111"/>
+      <c r="X13" s="114"/>
+      <c r="Y13" s="114"/>
+      <c r="Z13" s="114"/>
+      <c r="AA13" s="111"/>
+      <c r="AB13" s="111"/>
+      <c r="AC13" s="111"/>
+      <c r="AD13" s="114"/>
+      <c r="AE13" s="114"/>
+      <c r="AF13" s="107"/>
+      <c r="AG13" s="115" t="s">
+        <v>424</v>
+      </c>
+      <c r="AH13" s="116"/>
+      <c r="AI13" s="116"/>
+      <c r="AJ13" s="122"/>
+      <c r="AK13" s="122"/>
+      <c r="AL13" s="122"/>
+      <c r="AM13" s="116"/>
+      <c r="AN13" s="116"/>
+      <c r="AO13" s="116"/>
+      <c r="AP13" s="122"/>
+      <c r="AQ13" s="122"/>
+      <c r="AR13" s="122"/>
+      <c r="AS13" s="116"/>
+      <c r="AT13" s="116"/>
+      <c r="AU13" s="116"/>
+      <c r="AV13" s="122"/>
+      <c r="AW13" s="122"/>
+      <c r="AX13" s="122"/>
+      <c r="AY13" s="116"/>
+      <c r="AZ13" s="116"/>
+      <c r="BA13" s="116"/>
+      <c r="BB13" s="122"/>
+      <c r="BC13" s="122"/>
+      <c r="BD13" s="123"/>
+    </row>
+    <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="94"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="121" t="s">
+        <v>419</v>
+      </c>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="116"/>
+      <c r="P14" s="116"/>
+      <c r="Q14" s="116"/>
+      <c r="R14" s="122"/>
+      <c r="S14" s="122"/>
+      <c r="T14" s="122"/>
+      <c r="U14" s="116"/>
+      <c r="V14" s="116"/>
+      <c r="W14" s="116"/>
+      <c r="X14" s="122"/>
+      <c r="Y14" s="122"/>
+      <c r="Z14" s="122"/>
+      <c r="AA14" s="116"/>
+      <c r="AB14" s="116"/>
+      <c r="AC14" s="116"/>
+      <c r="AD14" s="122"/>
+      <c r="AE14" s="122"/>
+      <c r="AF14" s="122"/>
+      <c r="AG14" s="116"/>
+      <c r="AH14" s="116"/>
+      <c r="AI14" s="117"/>
+      <c r="AJ14" s="121" t="s">
+        <v>419</v>
+      </c>
+      <c r="AK14" s="122"/>
+      <c r="AL14" s="122"/>
+      <c r="AM14" s="116"/>
+      <c r="AN14" s="116"/>
+      <c r="AO14" s="116"/>
+      <c r="AP14" s="122"/>
+      <c r="AQ14" s="122"/>
+      <c r="AR14" s="122"/>
+      <c r="AS14" s="116"/>
+      <c r="AT14" s="116"/>
+      <c r="AU14" s="116"/>
+      <c r="AV14" s="122"/>
+      <c r="AW14" s="122"/>
+      <c r="AX14" s="122"/>
+      <c r="AY14" s="116"/>
+      <c r="AZ14" s="116"/>
+      <c r="BA14" s="116"/>
+      <c r="BB14" s="122"/>
+      <c r="BC14" s="122"/>
+      <c r="BD14" s="122"/>
+      <c r="BE14" s="116"/>
+      <c r="BF14" s="116"/>
+      <c r="BG14" s="117"/>
+    </row>
+    <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="94"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="114"/>
+      <c r="O15" s="138" t="s">
+        <v>420</v>
+      </c>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="133"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="132"/>
+      <c r="W15" s="132"/>
+      <c r="X15" s="133"/>
+      <c r="Y15" s="133"/>
+      <c r="Z15" s="133"/>
+      <c r="AA15" s="132"/>
+      <c r="AB15" s="132"/>
+      <c r="AC15" s="132"/>
+      <c r="AD15" s="122"/>
+      <c r="AE15" s="122"/>
+      <c r="AF15" s="122"/>
+      <c r="AG15" s="116"/>
+      <c r="AH15" s="116"/>
+      <c r="AI15" s="116"/>
+      <c r="AJ15" s="122"/>
+      <c r="AK15" s="122"/>
+      <c r="AL15" s="123"/>
+      <c r="AM15" s="139" t="s">
+        <v>426</v>
+      </c>
+      <c r="AN15" s="140"/>
+      <c r="AO15" s="140"/>
+      <c r="AP15" s="141"/>
+      <c r="AQ15" s="141"/>
+      <c r="AR15" s="141"/>
+      <c r="AS15" s="140"/>
+      <c r="AT15" s="140"/>
+      <c r="AU15" s="140"/>
+      <c r="AV15" s="141"/>
+      <c r="AW15" s="141"/>
+      <c r="AX15" s="141"/>
+      <c r="AY15" s="140"/>
+      <c r="AZ15" s="140"/>
+      <c r="BA15" s="140"/>
+      <c r="BB15" s="122"/>
+      <c r="BC15" s="122"/>
+      <c r="BD15" s="122"/>
+      <c r="BE15" s="116"/>
+      <c r="BF15" s="116"/>
+      <c r="BG15" s="116"/>
+      <c r="BH15" s="122"/>
+      <c r="BI15" s="122"/>
+      <c r="BJ15" s="123"/>
+    </row>
+    <row r="16" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>453</v>
+      </c>
+      <c r="M16" s="142"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="113" t="s">
+        <v>421</v>
+      </c>
+      <c r="S16" s="114"/>
+      <c r="T16" s="114"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="114"/>
+      <c r="Y16" s="114"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="111"/>
+      <c r="AC16" s="111"/>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="114"/>
+      <c r="AF16" s="114"/>
+      <c r="AG16" s="111"/>
+      <c r="AH16" s="111"/>
+      <c r="AI16" s="111"/>
+      <c r="AJ16" s="107"/>
+      <c r="AK16" s="145"/>
+      <c r="AL16" s="146"/>
+      <c r="AM16" s="146"/>
+      <c r="AN16" s="146"/>
+      <c r="AO16" s="147"/>
+      <c r="AP16" s="121" t="s">
+        <v>427</v>
+      </c>
+      <c r="AQ16" s="122"/>
+      <c r="AR16" s="122"/>
+      <c r="AS16" s="116"/>
+      <c r="AT16" s="116"/>
+      <c r="AU16" s="116"/>
+      <c r="AV16" s="122"/>
+      <c r="AW16" s="122"/>
+      <c r="AX16" s="122"/>
+    </row>
+    <row r="17" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>454</v>
+      </c>
+      <c r="B17" s="148"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="143"/>
+      <c r="L17" s="143"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="143"/>
+      <c r="O17" s="143"/>
+      <c r="P17" s="143"/>
+      <c r="Q17" s="144"/>
+      <c r="R17" s="113" t="s">
+        <v>422</v>
+      </c>
+      <c r="S17" s="107"/>
+      <c r="T17" s="149"/>
+      <c r="U17" s="150"/>
+      <c r="V17" s="150"/>
+      <c r="W17" s="150"/>
+      <c r="X17" s="150"/>
+      <c r="Y17" s="150"/>
+      <c r="Z17" s="150"/>
+      <c r="AA17" s="150"/>
+      <c r="AB17" s="150"/>
+      <c r="AC17" s="150"/>
+      <c r="AD17" s="150"/>
+      <c r="AE17" s="150"/>
+      <c r="AF17" s="150"/>
+      <c r="AG17" s="150"/>
+      <c r="AH17" s="150"/>
+      <c r="AI17" s="150"/>
+      <c r="AJ17" s="150"/>
+      <c r="AK17" s="150"/>
+      <c r="AL17" s="150"/>
+      <c r="AM17" s="150"/>
+      <c r="AN17" s="150"/>
+      <c r="AO17" s="151"/>
+      <c r="AP17" s="121" t="s">
+        <v>428</v>
+      </c>
+      <c r="AQ17" s="123"/>
+      <c r="AR17" s="149"/>
+      <c r="AS17" s="150"/>
+      <c r="AT17" s="150"/>
+      <c r="AU17" s="150"/>
+      <c r="AV17" s="150"/>
+      <c r="AW17" s="150"/>
+      <c r="AX17" s="151"/>
+    </row>
+    <row r="18" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>455</v>
+      </c>
+      <c r="B18" s="142"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="143"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="143"/>
+      <c r="N18" s="143"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="143"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="143"/>
+      <c r="T18" s="143"/>
+      <c r="U18" s="143"/>
+      <c r="V18" s="143"/>
+      <c r="W18" s="144"/>
+      <c r="X18" s="152" t="s">
+        <v>422</v>
+      </c>
+      <c r="Y18" s="134"/>
+      <c r="Z18" s="142"/>
+      <c r="AA18" s="143"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="143"/>
+      <c r="AD18" s="143"/>
+      <c r="AE18" s="143"/>
+      <c r="AF18" s="143"/>
+      <c r="AG18" s="143"/>
+      <c r="AH18" s="143"/>
+      <c r="AI18" s="143"/>
+      <c r="AJ18" s="143"/>
+      <c r="AK18" s="143"/>
+      <c r="AL18" s="143"/>
+      <c r="AM18" s="143"/>
+      <c r="AN18" s="143"/>
+      <c r="AO18" s="143"/>
+      <c r="AP18" s="143"/>
+      <c r="AQ18" s="143"/>
+      <c r="AR18" s="143"/>
+      <c r="AS18" s="143"/>
+      <c r="AT18" s="143"/>
+      <c r="AU18" s="144"/>
+      <c r="AV18" s="121" t="s">
+        <v>428</v>
+      </c>
+      <c r="AW18" s="123"/>
+      <c r="AX18" s="146"/>
+      <c r="AY18" s="146"/>
+      <c r="AZ18" s="146"/>
+      <c r="BA18" s="146"/>
+      <c r="BB18" s="146"/>
+      <c r="BC18" s="146"/>
+      <c r="BD18" s="146"/>
+      <c r="BE18" s="146"/>
+      <c r="BF18" s="146"/>
+      <c r="BG18" s="146"/>
+      <c r="BH18" s="146"/>
+      <c r="BI18" s="146"/>
+      <c r="BJ18" s="146"/>
+      <c r="BK18" s="146"/>
+      <c r="BL18" s="146"/>
+      <c r="BM18" s="146"/>
+      <c r="BN18" s="146"/>
+      <c r="BO18" s="146"/>
+      <c r="BP18" s="146"/>
+      <c r="BQ18" s="146"/>
+      <c r="BR18" s="146"/>
+      <c r="BS18" s="147"/>
+    </row>
+    <row r="19" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>456</v>
+      </c>
+      <c r="B19" s="142"/>
+      <c r="C19" s="143"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="143"/>
+      <c r="L19" s="143"/>
+      <c r="M19" s="143"/>
+      <c r="N19" s="143"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="143"/>
+      <c r="Q19" s="143"/>
+      <c r="R19" s="143"/>
+      <c r="S19" s="143"/>
+      <c r="T19" s="144"/>
+      <c r="U19" s="131" t="s">
+        <v>422</v>
+      </c>
+      <c r="V19" s="153"/>
+      <c r="W19" s="142"/>
+      <c r="X19" s="143"/>
+      <c r="Y19" s="143"/>
+      <c r="Z19" s="143"/>
+      <c r="AA19" s="143"/>
+      <c r="AB19" s="143"/>
+      <c r="AC19" s="143"/>
+      <c r="AD19" s="143"/>
+      <c r="AE19" s="143"/>
+      <c r="AF19" s="143"/>
+      <c r="AG19" s="143"/>
+      <c r="AH19" s="143"/>
+      <c r="AI19" s="143"/>
+      <c r="AJ19" s="143"/>
+      <c r="AK19" s="143"/>
+      <c r="AL19" s="143"/>
+      <c r="AM19" s="143"/>
+      <c r="AN19" s="143"/>
+      <c r="AO19" s="143"/>
+      <c r="AP19" s="143"/>
+      <c r="AQ19" s="143"/>
+      <c r="AR19" s="144"/>
+      <c r="AS19" s="139" t="s">
+        <v>428</v>
+      </c>
+      <c r="AT19" s="154"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A12:A15"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A19011B-88C9-4B65-A037-D8DE3A0653BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F379C5-6C33-4FF2-8D54-D7B23D1A2791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangPrimer25K (SLOT無し版)" sheetId="3" r:id="rId1"/>
@@ -1627,10 +1627,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>RESERVE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>joy2_l</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1836,6 +1832,10 @@
   </si>
   <si>
     <t>STATE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pause</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2546,7 +2546,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2820,6 +2820,156 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="35" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2864,159 +3014,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4640,7 +4637,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="91" t="s">
+      <c r="AC9" s="141" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4701,7 +4698,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="91"/>
+      <c r="AC10" s="141"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -4764,7 +4761,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="91"/>
+      <c r="AC11" s="141"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -4825,7 +4822,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="91"/>
+      <c r="AC12" s="141"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -4890,7 +4887,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="91"/>
+      <c r="AC13" s="141"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -4959,7 +4956,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="91"/>
+      <c r="AC14" s="141"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -5222,7 +5219,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="92" t="s">
+      <c r="AC18" s="142" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5287,7 +5284,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="92"/>
+      <c r="AC19" s="142"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -5346,7 +5343,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="92"/>
+      <c r="AC20" s="142"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -5409,7 +5406,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="92"/>
+      <c r="AC21" s="142"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -5470,7 +5467,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="91" t="s">
+      <c r="AC22" s="141" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5533,7 +5530,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="91"/>
+      <c r="AC23" s="141"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -5594,7 +5591,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="91"/>
+      <c r="AC24" s="141"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -5653,7 +5650,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="91"/>
+      <c r="AC25" s="141"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -5716,7 +5713,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="91"/>
+      <c r="AC26" s="141"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -5777,7 +5774,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="91"/>
+      <c r="AC27" s="141"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -6661,7 +6658,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="91" t="s">
+      <c r="AC9" s="141" t="s">
         <v>245</v>
       </c>
     </row>
@@ -6730,7 +6727,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="91"/>
+      <c r="AC10" s="141"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -6797,7 +6794,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="91"/>
+      <c r="AC11" s="141"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -6864,7 +6861,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="91"/>
+      <c r="AC12" s="141"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -6933,7 +6930,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="91"/>
+      <c r="AC13" s="141"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -7006,7 +7003,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="91"/>
+      <c r="AC14" s="141"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -7291,7 +7288,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="92" t="s">
+      <c r="AC18" s="142" t="s">
         <v>246</v>
       </c>
     </row>
@@ -7360,7 +7357,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="92"/>
+      <c r="AC19" s="142"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -7427,7 +7424,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="92"/>
+      <c r="AC20" s="142"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -7498,7 +7495,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="92"/>
+      <c r="AC21" s="142"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -7563,7 +7560,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="91" t="s">
+      <c r="AC22" s="141" t="s">
         <v>244</v>
       </c>
     </row>
@@ -7630,7 +7627,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="91"/>
+      <c r="AC23" s="141"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -7695,7 +7692,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="91"/>
+      <c r="AC24" s="141"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -7758,7 +7755,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="91"/>
+      <c r="AC25" s="141"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -7821,7 +7818,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="91"/>
+      <c r="AC26" s="141"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -7886,7 +7883,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="91"/>
+      <c r="AC27" s="141"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -8015,7 +8012,7 @@
       <c r="AB29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AC29" s="93" t="s">
+      <c r="AC29" s="143" t="s">
         <v>243</v>
       </c>
     </row>
@@ -8086,7 +8083,7 @@
       <c r="AB30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC30" s="93"/>
+      <c r="AC30" s="143"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="21">
@@ -8151,7 +8148,7 @@
       <c r="AB31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC31" s="93"/>
+      <c r="AC31" s="143"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
@@ -8214,7 +8211,7 @@
       <c r="AB32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC32" s="93"/>
+      <c r="AC32" s="143"/>
     </row>
     <row r="33" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
@@ -8318,14 +8315,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -8625,7 +8622,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="93" t="s">
+      <c r="P10" s="143" t="s">
         <v>305</v>
       </c>
     </row>
@@ -8663,7 +8660,7 @@
       <c r="O11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P11" s="93"/>
+      <c r="P11" s="143"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -8886,7 +8883,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="92" t="s">
+      <c r="H18" s="142" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -8927,7 +8924,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="92"/>
+      <c r="H19" s="142"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -8966,7 +8963,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="92"/>
+      <c r="H20" s="142"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -9000,7 +8997,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="92"/>
+      <c r="H21" s="142"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -9127,14 +9124,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -9193,7 +9190,7 @@
       <c r="G4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="91" t="s">
+      <c r="H4" s="141" t="s">
         <v>244</v>
       </c>
       <c r="J4" s="8">
@@ -9232,7 +9229,7 @@
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="91"/>
+      <c r="H5" s="141"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -9269,7 +9266,7 @@
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="91"/>
+      <c r="H6" s="141"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -9307,7 +9304,7 @@
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="91"/>
+      <c r="H7" s="141"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -9382,7 +9379,7 @@
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="91" t="s">
+      <c r="H9" s="141" t="s">
         <v>244</v>
       </c>
       <c r="J9" s="11">
@@ -9424,7 +9421,7 @@
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="91"/>
+      <c r="H10" s="141"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -9443,7 +9440,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="93" t="s">
+      <c r="P10" s="143" t="s">
         <v>305</v>
       </c>
     </row>
@@ -9464,7 +9461,7 @@
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="96" t="s">
+      <c r="H11" s="146" t="s">
         <v>315</v>
       </c>
       <c r="J11" s="11">
@@ -9485,7 +9482,7 @@
       <c r="O11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="93"/>
+      <c r="P11" s="143"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -9504,7 +9501,7 @@
       <c r="G12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="96"/>
+      <c r="H12" s="146"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -9542,7 +9539,7 @@
       <c r="G13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H13" s="96"/>
+      <c r="H13" s="146"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -9559,7 +9556,7 @@
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="93" t="s">
+      <c r="P13" s="143" t="s">
         <v>305</v>
       </c>
     </row>
@@ -9580,7 +9577,7 @@
       <c r="G14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="96"/>
+      <c r="H14" s="146"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -9599,7 +9596,7 @@
       <c r="O14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="93"/>
+      <c r="P14" s="143"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
@@ -9618,7 +9615,7 @@
       <c r="G15" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H15" s="96"/>
+      <c r="H15" s="146"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -9635,7 +9632,7 @@
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="96" t="s">
+      <c r="P15" s="146" t="s">
         <v>316</v>
       </c>
     </row>
@@ -9656,7 +9653,7 @@
       <c r="G16" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="96"/>
+      <c r="H16" s="146"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -9673,7 +9670,7 @@
       <c r="O16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="96"/>
+      <c r="P16" s="146"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -9692,7 +9689,7 @@
       <c r="G17" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H17" s="96"/>
+      <c r="H17" s="146"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -9732,7 +9729,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="92" t="s">
+      <c r="H18" s="142" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -9773,7 +9770,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="92"/>
+      <c r="H19" s="142"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -9812,7 +9809,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="92"/>
+      <c r="H20" s="142"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -9829,7 +9826,7 @@
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="95" t="s">
+      <c r="P20" s="145" t="s">
         <v>316</v>
       </c>
     </row>
@@ -9852,7 +9849,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="92"/>
+      <c r="H21" s="142"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -9869,7 +9866,7 @@
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="95"/>
+      <c r="P21" s="145"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -10093,7 +10090,7 @@
         <v>398</v>
       </c>
       <c r="L4" s="71" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.15">
@@ -10125,7 +10122,7 @@
         <v>399</v>
       </c>
       <c r="L5" s="76" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.15">
@@ -10157,7 +10154,7 @@
         <v>400</v>
       </c>
       <c r="L6" s="76" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.15">
@@ -10186,10 +10183,10 @@
         <v>374</v>
       </c>
       <c r="K7" s="75" t="s">
-        <v>401</v>
+        <v>457</v>
       </c>
       <c r="L7" s="76" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.15">
@@ -10218,10 +10215,10 @@
         <v>375</v>
       </c>
       <c r="K8" s="75" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L8" s="76" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="3:12" x14ac:dyDescent="0.15">
@@ -10250,10 +10247,10 @@
         <v>376</v>
       </c>
       <c r="K9" s="75" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L9" s="76" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="3:12" x14ac:dyDescent="0.15">
@@ -10282,10 +10279,10 @@
         <v>377</v>
       </c>
       <c r="K10" s="75" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L10" s="76" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -10314,10 +10311,10 @@
         <v>378</v>
       </c>
       <c r="K11" s="80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L11" s="81" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.15">
@@ -10423,16 +10420,16 @@
       <c r="D15" s="88" t="s">
         <v>383</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="150" t="s">
         <v>382</v>
       </c>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="102"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="151"/>
+      <c r="I15" s="151"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="152"/>
     </row>
     <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C16" s="89">
@@ -10441,34 +10438,34 @@
       <c r="D16" s="90" t="s">
         <v>345</v>
       </c>
-      <c r="E16" s="97" t="s">
+      <c r="E16" s="147" t="s">
         <v>346</v>
       </c>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="99"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="148"/>
+      <c r="L16" s="149"/>
     </row>
     <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C17" s="89"/>
       <c r="D17" s="56" t="s">
         <v>341</v>
       </c>
-      <c r="E17" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="103" t="s">
+      <c r="E17" s="153" t="s">
+        <v>413</v>
+      </c>
+      <c r="F17" s="154"/>
+      <c r="G17" s="154"/>
+      <c r="H17" s="154"/>
+      <c r="I17" s="155"/>
+      <c r="J17" s="153" t="s">
         <v>363</v>
       </c>
-      <c r="K17" s="104"/>
-      <c r="L17" s="105"/>
+      <c r="K17" s="154"/>
+      <c r="L17" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10489,15 +10486,15 @@
   <sheetFormatPr defaultColWidth="4.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="4.25" style="106"/>
-    <col min="9" max="11" width="4.25" style="106"/>
-    <col min="15" max="17" width="4.25" style="106"/>
-    <col min="21" max="23" width="4.25" style="106"/>
+    <col min="3" max="5" width="4.25" style="91"/>
+    <col min="9" max="11" width="4.25" style="91"/>
+    <col min="15" max="17" width="4.25" style="91"/>
+    <col min="21" max="23" width="4.25" style="91"/>
     <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.25" style="106"/>
-    <col min="33" max="35" width="4.25" style="106"/>
-    <col min="39" max="41" width="4.25" style="106"/>
-    <col min="45" max="47" width="4.25" style="106"/>
+    <col min="27" max="29" width="4.25" style="91"/>
+    <col min="33" max="35" width="4.25" style="91"/>
+    <col min="39" max="41" width="4.25" style="91"/>
+    <col min="45" max="47" width="4.25" style="91"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.15">
@@ -10506,928 +10503,928 @@
       </c>
     </row>
     <row r="2" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
-        <v>457</v>
+      <c r="A2" s="140" t="s">
+        <v>456</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="106">
+      <c r="C2" s="91">
         <v>1</v>
       </c>
-      <c r="D2" s="106">
+      <c r="D2" s="91">
         <v>2</v>
       </c>
-      <c r="E2" s="106">
+      <c r="E2" s="91">
         <v>3</v>
       </c>
-      <c r="F2" s="156">
+      <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2" s="156">
+      <c r="G2">
         <v>5</v>
       </c>
-      <c r="H2" s="156">
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="I2" s="106">
+      <c r="I2" s="91">
         <v>7</v>
       </c>
-      <c r="J2" s="106">
+      <c r="J2" s="91">
         <v>8</v>
       </c>
-      <c r="K2" s="106">
+      <c r="K2" s="91">
         <v>9</v>
       </c>
-      <c r="L2" s="156">
+      <c r="L2">
         <v>10</v>
       </c>
-      <c r="M2" s="156">
+      <c r="M2">
         <v>11</v>
       </c>
-      <c r="N2" s="156">
+      <c r="N2">
         <v>12</v>
       </c>
-      <c r="O2" s="106">
+      <c r="O2" s="91">
         <v>13</v>
       </c>
-      <c r="P2" s="106">
+      <c r="P2" s="91">
         <v>14</v>
       </c>
-      <c r="Q2" s="106">
+      <c r="Q2" s="91">
         <v>15</v>
       </c>
-      <c r="R2" s="156">
+      <c r="R2">
         <v>16</v>
       </c>
-      <c r="S2" s="156">
+      <c r="S2">
         <v>17</v>
       </c>
-      <c r="T2" s="156">
+      <c r="T2">
         <v>18</v>
       </c>
-      <c r="U2" s="106">
+      <c r="U2" s="91">
         <v>19</v>
       </c>
-      <c r="V2" s="106">
+      <c r="V2" s="91">
         <v>20</v>
       </c>
-      <c r="W2" s="106">
+      <c r="W2" s="91">
         <v>21</v>
       </c>
-      <c r="X2" s="156">
+      <c r="X2">
         <v>22</v>
       </c>
-      <c r="Y2" s="156">
+      <c r="Y2">
         <v>23</v>
       </c>
-      <c r="Z2" s="156">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B3" s="107"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="109"/>
-      <c r="Y3" s="109"/>
-      <c r="Z3" s="109"/>
-      <c r="AA3" s="108"/>
-      <c r="AB3" s="108"/>
-      <c r="AC3" s="108"/>
-      <c r="AD3" s="109"/>
-      <c r="AE3" s="109"/>
-      <c r="AF3" s="109"/>
-      <c r="AG3" s="108"/>
-      <c r="AH3" s="108"/>
-      <c r="AI3" s="108"/>
-      <c r="AJ3" s="109"/>
-      <c r="AK3" s="109"/>
-      <c r="AL3" s="109"/>
-      <c r="AM3" s="108"/>
-      <c r="AN3" s="108"/>
-      <c r="AO3" s="108"/>
-      <c r="AP3" s="109"/>
-      <c r="AQ3" s="109"/>
-      <c r="AR3" s="109"/>
-      <c r="AS3" s="108"/>
-      <c r="AT3" s="108"/>
-      <c r="AU3" s="108"/>
-      <c r="AV3" s="109"/>
-      <c r="AW3" s="109"/>
-      <c r="AX3" s="109"/>
+        <v>414</v>
+      </c>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="94"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="93"/>
+      <c r="AH3" s="93"/>
+      <c r="AI3" s="93"/>
+      <c r="AJ3" s="94"/>
+      <c r="AK3" s="94"/>
+      <c r="AL3" s="94"/>
+      <c r="AM3" s="93"/>
+      <c r="AN3" s="93"/>
+      <c r="AO3" s="93"/>
+      <c r="AP3" s="94"/>
+      <c r="AQ3" s="94"/>
+      <c r="AR3" s="94"/>
+      <c r="AS3" s="93"/>
+      <c r="AT3" s="93"/>
+      <c r="AU3" s="93"/>
+      <c r="AV3" s="94"/>
+      <c r="AW3" s="94"/>
+      <c r="AX3" s="94"/>
     </row>
     <row r="4" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="95" t="s">
         <v>416</v>
       </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="110" t="s">
+      <c r="D5" s="96"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="98" t="s">
         <v>417</v>
       </c>
-      <c r="D5" s="111"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="113" t="s">
+      <c r="G5" s="99"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="95" t="s">
         <v>418</v>
       </c>
-      <c r="G5" s="114"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="110" t="s">
+      <c r="J5" s="96"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="98" t="s">
         <v>419</v>
       </c>
-      <c r="J5" s="111"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="113" t="s">
+      <c r="M5" s="99"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="100" t="s">
         <v>420</v>
       </c>
-      <c r="M5" s="114"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="115" t="s">
+      <c r="P5" s="101"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="104" t="s">
         <v>421</v>
       </c>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="119" t="s">
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="105" t="s">
+        <v>421</v>
+      </c>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
+      <c r="Y5" s="104" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z5" s="103"/>
+      <c r="AA5" s="100" t="s">
         <v>422</v>
       </c>
-      <c r="T5" s="118"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="120" t="s">
-        <v>422</v>
-      </c>
-      <c r="W5" s="118"/>
-      <c r="X5" s="118"/>
-      <c r="Y5" s="119" t="s">
-        <v>422</v>
-      </c>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="115" t="s">
+      <c r="AB5" s="101"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="106" t="s">
         <v>423</v>
       </c>
-      <c r="AB5" s="116"/>
-      <c r="AC5" s="117"/>
-      <c r="AD5" s="121" t="s">
+      <c r="AE5" s="107"/>
+      <c r="AF5" s="108"/>
+      <c r="AG5" s="109" t="s">
         <v>424</v>
       </c>
-      <c r="AE5" s="122"/>
-      <c r="AF5" s="123"/>
-      <c r="AG5" s="124" t="s">
+      <c r="AH5" s="110"/>
+      <c r="AI5" s="111"/>
+      <c r="AJ5" s="106" t="s">
         <v>425</v>
       </c>
-      <c r="AH5" s="125"/>
-      <c r="AI5" s="126"/>
-      <c r="AJ5" s="121" t="s">
+      <c r="AK5" s="107"/>
+      <c r="AL5" s="108"/>
+      <c r="AM5" s="109" t="s">
         <v>426</v>
       </c>
-      <c r="AK5" s="122"/>
-      <c r="AL5" s="123"/>
-      <c r="AM5" s="124" t="s">
+      <c r="AN5" s="110"/>
+      <c r="AO5" s="111"/>
+      <c r="AP5" s="112"/>
+      <c r="AQ5" s="113" t="s">
         <v>427</v>
       </c>
-      <c r="AN5" s="125"/>
-      <c r="AO5" s="126"/>
-      <c r="AP5" s="127"/>
-      <c r="AQ5" s="128" t="s">
-        <v>428</v>
-      </c>
-      <c r="AR5" s="127"/>
-      <c r="AS5" s="127"/>
-      <c r="AT5" s="129" t="s">
-        <v>428</v>
-      </c>
-      <c r="AU5" s="127"/>
-      <c r="AV5" s="127"/>
-      <c r="AW5" s="128" t="s">
-        <v>428</v>
-      </c>
-      <c r="AX5" s="127"/>
+      <c r="AR5" s="112"/>
+      <c r="AS5" s="112"/>
+      <c r="AT5" s="114" t="s">
+        <v>427</v>
+      </c>
+      <c r="AU5" s="112"/>
+      <c r="AV5" s="112"/>
+      <c r="AW5" s="113" t="s">
+        <v>427</v>
+      </c>
+      <c r="AX5" s="112"/>
     </row>
     <row r="6" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>428</v>
+      </c>
+      <c r="B6" s="92"/>
+      <c r="C6" s="100" t="s">
         <v>429</v>
       </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="115" t="s">
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="101"/>
+      <c r="P6" s="101"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="106" t="s">
         <v>430</v>
       </c>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="117"/>
-      <c r="R6" s="121" t="s">
+      <c r="S6" s="107"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="101"/>
+      <c r="V6" s="101"/>
+      <c r="W6" s="101"/>
+      <c r="X6" s="107"/>
+      <c r="Y6" s="107"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="100" t="s">
         <v>431</v>
       </c>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="116"/>
-      <c r="V6" s="116"/>
-      <c r="W6" s="116"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="123"/>
-      <c r="AA6" s="115" t="s">
+      <c r="AB6" s="101"/>
+      <c r="AC6" s="101"/>
+      <c r="AD6" s="107"/>
+      <c r="AE6" s="107"/>
+      <c r="AF6" s="107"/>
+      <c r="AG6" s="101"/>
+      <c r="AH6" s="101"/>
+      <c r="AI6" s="101"/>
+      <c r="AJ6" s="107"/>
+      <c r="AK6" s="107"/>
+      <c r="AL6" s="107"/>
+      <c r="AM6" s="101"/>
+      <c r="AN6" s="101"/>
+      <c r="AO6" s="102"/>
+      <c r="AP6" s="106" t="s">
         <v>432</v>
       </c>
-      <c r="AB6" s="116"/>
-      <c r="AC6" s="116"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="122"/>
-      <c r="AF6" s="122"/>
-      <c r="AG6" s="116"/>
-      <c r="AH6" s="116"/>
-      <c r="AI6" s="116"/>
-      <c r="AJ6" s="122"/>
-      <c r="AK6" s="122"/>
-      <c r="AL6" s="122"/>
-      <c r="AM6" s="116"/>
-      <c r="AN6" s="116"/>
-      <c r="AO6" s="117"/>
-      <c r="AP6" s="121" t="s">
-        <v>433</v>
-      </c>
-      <c r="AQ6" s="122"/>
-      <c r="AR6" s="122"/>
-      <c r="AS6" s="116"/>
-      <c r="AT6" s="116"/>
-      <c r="AU6" s="116"/>
-      <c r="AV6" s="122"/>
-      <c r="AW6" s="122"/>
-      <c r="AX6" s="123"/>
+      <c r="AQ6" s="107"/>
+      <c r="AR6" s="107"/>
+      <c r="AS6" s="101"/>
+      <c r="AT6" s="101"/>
+      <c r="AU6" s="101"/>
+      <c r="AV6" s="107"/>
+      <c r="AW6" s="107"/>
+      <c r="AX6" s="108"/>
     </row>
     <row r="7" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B7" s="98" t="s">
         <v>434</v>
       </c>
-      <c r="B7" s="113" t="s">
+      <c r="C7" s="96"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="95" t="s">
         <v>435</v>
       </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="110" t="s">
+      <c r="F7" s="99"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="98" t="s">
         <v>436</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="113" t="s">
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="I7" s="111"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="110" t="s">
+      <c r="L7" s="99"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="98" t="s">
         <v>438</v>
       </c>
-      <c r="L7" s="114"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="113" t="s">
+      <c r="O7" s="96"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="95" t="s">
         <v>439</v>
       </c>
-      <c r="O7" s="111"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="110" t="s">
+      <c r="R7" s="99"/>
+      <c r="S7" s="92"/>
+      <c r="T7" s="98" t="s">
         <v>440</v>
       </c>
-      <c r="R7" s="114"/>
-      <c r="S7" s="107"/>
-      <c r="T7" s="113" t="s">
+      <c r="U7" s="96"/>
+      <c r="V7" s="97"/>
+      <c r="W7" s="95" t="s">
         <v>441</v>
       </c>
-      <c r="U7" s="111"/>
-      <c r="V7" s="112"/>
-      <c r="W7" s="110" t="s">
+      <c r="X7" s="99"/>
+      <c r="Y7" s="92"/>
+      <c r="Z7" s="98" t="s">
+        <v>434</v>
+      </c>
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="102"/>
+      <c r="AC7" s="101" t="s">
         <v>442</v>
       </c>
-      <c r="X7" s="114"/>
-      <c r="Y7" s="107"/>
-      <c r="Z7" s="113" t="s">
-        <v>435</v>
-      </c>
-      <c r="AA7" s="116"/>
-      <c r="AB7" s="117"/>
-      <c r="AC7" s="116" t="s">
+      <c r="AD7" s="107"/>
+      <c r="AE7" s="108"/>
+      <c r="AF7" s="107" t="s">
         <v>443</v>
       </c>
-      <c r="AD7" s="122"/>
-      <c r="AE7" s="123"/>
-      <c r="AF7" s="122" t="s">
+      <c r="AG7" s="110"/>
+      <c r="AH7" s="111"/>
+      <c r="AI7" s="110" t="s">
         <v>444</v>
       </c>
-      <c r="AG7" s="125"/>
-      <c r="AH7" s="126"/>
-      <c r="AI7" s="125" t="s">
+      <c r="AJ7" s="107"/>
+      <c r="AK7" s="108"/>
+      <c r="AL7" s="107" t="s">
         <v>445</v>
       </c>
-      <c r="AJ7" s="122"/>
-      <c r="AK7" s="123"/>
-      <c r="AL7" s="122" t="s">
+      <c r="AM7" s="110"/>
+      <c r="AN7" s="111"/>
+      <c r="AO7" s="110" t="s">
         <v>446</v>
       </c>
-      <c r="AM7" s="125"/>
-      <c r="AN7" s="126"/>
-      <c r="AO7" s="125" t="s">
+      <c r="AP7" s="107"/>
+      <c r="AQ7" s="108"/>
+      <c r="AR7" s="107" t="s">
         <v>447</v>
       </c>
-      <c r="AP7" s="122"/>
-      <c r="AQ7" s="123"/>
-      <c r="AR7" s="122" t="s">
+      <c r="AS7" s="110"/>
+      <c r="AT7" s="111"/>
+      <c r="AU7" s="110" t="s">
         <v>448</v>
       </c>
-      <c r="AS7" s="125"/>
-      <c r="AT7" s="126"/>
-      <c r="AU7" s="125" t="s">
+      <c r="AV7" s="107"/>
+      <c r="AW7" s="108"/>
+      <c r="AX7" s="107" t="s">
         <v>449</v>
       </c>
-      <c r="AV7" s="122"/>
-      <c r="AW7" s="123"/>
-      <c r="AX7" s="122" t="s">
-        <v>450</v>
-      </c>
     </row>
     <row r="8" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="O8" s="111"/>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="114"/>
-      <c r="S8" s="114"/>
-      <c r="T8" s="114"/>
-      <c r="U8" s="111"/>
-      <c r="V8" s="111"/>
-      <c r="W8" s="111"/>
-      <c r="X8" s="114"/>
-      <c r="Y8" s="114"/>
-      <c r="Z8" s="114"/>
-      <c r="AM8" s="111"/>
-      <c r="AN8" s="111"/>
-      <c r="AO8" s="111"/>
-      <c r="AP8" s="114"/>
-      <c r="AQ8" s="114"/>
-      <c r="AR8" s="114"/>
-      <c r="AS8" s="111"/>
-      <c r="AT8" s="111"/>
-      <c r="AU8" s="111"/>
-      <c r="AV8" s="114"/>
-      <c r="AW8" s="114"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="99"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="96"/>
+      <c r="W8" s="96"/>
+      <c r="X8" s="99"/>
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="99"/>
+      <c r="AM8" s="96"/>
+      <c r="AN8" s="96"/>
+      <c r="AO8" s="96"/>
+      <c r="AP8" s="99"/>
+      <c r="AQ8" s="99"/>
+      <c r="AR8" s="99"/>
+      <c r="AS8" s="96"/>
+      <c r="AT8" s="96"/>
+      <c r="AU8" s="96"/>
+      <c r="AV8" s="99"/>
+      <c r="AW8" s="99"/>
     </row>
     <row r="9" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="115"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="119"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="116"/>
+      <c r="AB9" s="117"/>
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="118"/>
+      <c r="AF9" s="118"/>
+      <c r="AG9" s="117"/>
+      <c r="AH9" s="117"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="118"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="119"/>
+      <c r="AW9" s="115"/>
+    </row>
+    <row r="11" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="118"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+    </row>
+    <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="144" t="s">
         <v>451</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="134"/>
-      <c r="Z9" s="130"/>
-      <c r="AA9" s="131"/>
-      <c r="AB9" s="132"/>
-      <c r="AC9" s="132"/>
-      <c r="AD9" s="133"/>
-      <c r="AE9" s="133"/>
-      <c r="AF9" s="133"/>
-      <c r="AG9" s="132"/>
-      <c r="AH9" s="132"/>
-      <c r="AI9" s="132"/>
-      <c r="AJ9" s="133"/>
-      <c r="AK9" s="133"/>
-      <c r="AL9" s="134"/>
-      <c r="AW9" s="130"/>
-    </row>
-    <row r="11" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="133"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-    </row>
-    <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="94" t="s">
-        <v>452</v>
-      </c>
-      <c r="B12" s="114"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="113" t="s">
+      <c r="B12" s="99"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="98" t="s">
+        <v>416</v>
+      </c>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="120"/>
+      <c r="S12" s="120"/>
+      <c r="T12" s="120"/>
+      <c r="U12" s="121"/>
+      <c r="V12" s="121"/>
+      <c r="W12" s="121"/>
+      <c r="X12" s="120"/>
+      <c r="Y12" s="120"/>
+      <c r="Z12" s="120"/>
+      <c r="AA12" s="121"/>
+      <c r="AB12" s="121"/>
+      <c r="AC12" s="122"/>
+      <c r="AD12" s="98" t="s">
+        <v>416</v>
+      </c>
+      <c r="AE12" s="99"/>
+      <c r="AF12" s="99"/>
+      <c r="AG12" s="96"/>
+      <c r="AH12" s="96"/>
+      <c r="AI12" s="96"/>
+      <c r="AJ12" s="120"/>
+      <c r="AK12" s="120"/>
+      <c r="AL12" s="120"/>
+      <c r="AM12" s="121"/>
+      <c r="AN12" s="121"/>
+      <c r="AO12" s="121"/>
+      <c r="AP12" s="120"/>
+      <c r="AQ12" s="120"/>
+      <c r="AR12" s="120"/>
+      <c r="AS12" s="121"/>
+      <c r="AT12" s="121"/>
+      <c r="AU12" s="121"/>
+      <c r="AV12" s="120"/>
+      <c r="AW12" s="120"/>
+      <c r="AX12" s="120"/>
+      <c r="AY12" s="121"/>
+      <c r="AZ12" s="121"/>
+      <c r="BA12" s="122"/>
+    </row>
+    <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="144"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="100" t="s">
         <v>417</v>
       </c>
-      <c r="G12" s="114"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="135"/>
-      <c r="M12" s="135"/>
-      <c r="N12" s="135"/>
-      <c r="O12" s="136"/>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="136"/>
-      <c r="R12" s="135"/>
-      <c r="S12" s="135"/>
-      <c r="T12" s="135"/>
-      <c r="U12" s="136"/>
-      <c r="V12" s="136"/>
-      <c r="W12" s="136"/>
-      <c r="X12" s="135"/>
-      <c r="Y12" s="135"/>
-      <c r="Z12" s="135"/>
-      <c r="AA12" s="136"/>
-      <c r="AB12" s="136"/>
-      <c r="AC12" s="137"/>
-      <c r="AD12" s="113" t="s">
-        <v>417</v>
-      </c>
-      <c r="AE12" s="114"/>
-      <c r="AF12" s="114"/>
-      <c r="AG12" s="111"/>
-      <c r="AH12" s="111"/>
-      <c r="AI12" s="111"/>
-      <c r="AJ12" s="135"/>
-      <c r="AK12" s="135"/>
-      <c r="AL12" s="135"/>
-      <c r="AM12" s="136"/>
-      <c r="AN12" s="136"/>
-      <c r="AO12" s="136"/>
-      <c r="AP12" s="135"/>
-      <c r="AQ12" s="135"/>
-      <c r="AR12" s="135"/>
-      <c r="AS12" s="136"/>
-      <c r="AT12" s="136"/>
-      <c r="AU12" s="136"/>
-      <c r="AV12" s="135"/>
-      <c r="AW12" s="135"/>
-      <c r="AX12" s="135"/>
-      <c r="AY12" s="136"/>
-      <c r="AZ12" s="136"/>
-      <c r="BA12" s="137"/>
-    </row>
-    <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="94"/>
-      <c r="B13" s="114"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="114"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="115" t="s">
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="99"/>
+      <c r="S13" s="99"/>
+      <c r="T13" s="99"/>
+      <c r="U13" s="96"/>
+      <c r="V13" s="96"/>
+      <c r="W13" s="96"/>
+      <c r="X13" s="99"/>
+      <c r="Y13" s="99"/>
+      <c r="Z13" s="99"/>
+      <c r="AA13" s="96"/>
+      <c r="AB13" s="96"/>
+      <c r="AC13" s="96"/>
+      <c r="AD13" s="99"/>
+      <c r="AE13" s="99"/>
+      <c r="AF13" s="92"/>
+      <c r="AG13" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="AH13" s="101"/>
+      <c r="AI13" s="101"/>
+      <c r="AJ13" s="107"/>
+      <c r="AK13" s="107"/>
+      <c r="AL13" s="107"/>
+      <c r="AM13" s="101"/>
+      <c r="AN13" s="101"/>
+      <c r="AO13" s="101"/>
+      <c r="AP13" s="107"/>
+      <c r="AQ13" s="107"/>
+      <c r="AR13" s="107"/>
+      <c r="AS13" s="101"/>
+      <c r="AT13" s="101"/>
+      <c r="AU13" s="101"/>
+      <c r="AV13" s="107"/>
+      <c r="AW13" s="107"/>
+      <c r="AX13" s="107"/>
+      <c r="AY13" s="101"/>
+      <c r="AZ13" s="101"/>
+      <c r="BA13" s="101"/>
+      <c r="BB13" s="107"/>
+      <c r="BC13" s="107"/>
+      <c r="BD13" s="108"/>
+    </row>
+    <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="144"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="106" t="s">
         <v>418</v>
       </c>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="114"/>
-      <c r="M13" s="114"/>
-      <c r="N13" s="114"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
-      <c r="R13" s="114"/>
-      <c r="S13" s="114"/>
-      <c r="T13" s="114"/>
-      <c r="U13" s="111"/>
-      <c r="V13" s="111"/>
-      <c r="W13" s="111"/>
-      <c r="X13" s="114"/>
-      <c r="Y13" s="114"/>
-      <c r="Z13" s="114"/>
-      <c r="AA13" s="111"/>
-      <c r="AB13" s="111"/>
-      <c r="AC13" s="111"/>
-      <c r="AD13" s="114"/>
-      <c r="AE13" s="114"/>
-      <c r="AF13" s="107"/>
-      <c r="AG13" s="115" t="s">
-        <v>424</v>
-      </c>
-      <c r="AH13" s="116"/>
-      <c r="AI13" s="116"/>
-      <c r="AJ13" s="122"/>
-      <c r="AK13" s="122"/>
-      <c r="AL13" s="122"/>
-      <c r="AM13" s="116"/>
-      <c r="AN13" s="116"/>
-      <c r="AO13" s="116"/>
-      <c r="AP13" s="122"/>
-      <c r="AQ13" s="122"/>
-      <c r="AR13" s="122"/>
-      <c r="AS13" s="116"/>
-      <c r="AT13" s="116"/>
-      <c r="AU13" s="116"/>
-      <c r="AV13" s="122"/>
-      <c r="AW13" s="122"/>
-      <c r="AX13" s="122"/>
-      <c r="AY13" s="116"/>
-      <c r="AZ13" s="116"/>
-      <c r="BA13" s="116"/>
-      <c r="BB13" s="122"/>
-      <c r="BC13" s="122"/>
-      <c r="BD13" s="123"/>
-    </row>
-    <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="94"/>
-      <c r="B14" s="114"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="121" t="s">
+      <c r="M14" s="107"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="107"/>
+      <c r="S14" s="107"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="101"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="107"/>
+      <c r="Y14" s="107"/>
+      <c r="Z14" s="107"/>
+      <c r="AA14" s="101"/>
+      <c r="AB14" s="101"/>
+      <c r="AC14" s="101"/>
+      <c r="AD14" s="107"/>
+      <c r="AE14" s="107"/>
+      <c r="AF14" s="107"/>
+      <c r="AG14" s="101"/>
+      <c r="AH14" s="101"/>
+      <c r="AI14" s="102"/>
+      <c r="AJ14" s="106" t="s">
+        <v>418</v>
+      </c>
+      <c r="AK14" s="107"/>
+      <c r="AL14" s="107"/>
+      <c r="AM14" s="101"/>
+      <c r="AN14" s="101"/>
+      <c r="AO14" s="101"/>
+      <c r="AP14" s="107"/>
+      <c r="AQ14" s="107"/>
+      <c r="AR14" s="107"/>
+      <c r="AS14" s="101"/>
+      <c r="AT14" s="101"/>
+      <c r="AU14" s="101"/>
+      <c r="AV14" s="107"/>
+      <c r="AW14" s="107"/>
+      <c r="AX14" s="107"/>
+      <c r="AY14" s="101"/>
+      <c r="AZ14" s="101"/>
+      <c r="BA14" s="101"/>
+      <c r="BB14" s="107"/>
+      <c r="BC14" s="107"/>
+      <c r="BD14" s="107"/>
+      <c r="BE14" s="101"/>
+      <c r="BF14" s="101"/>
+      <c r="BG14" s="102"/>
+    </row>
+    <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="144"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="99"/>
+      <c r="O15" s="123" t="s">
         <v>419</v>
       </c>
-      <c r="M14" s="122"/>
-      <c r="N14" s="122"/>
-      <c r="O14" s="116"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="122"/>
-      <c r="S14" s="122"/>
-      <c r="T14" s="122"/>
-      <c r="U14" s="116"/>
-      <c r="V14" s="116"/>
-      <c r="W14" s="116"/>
-      <c r="X14" s="122"/>
-      <c r="Y14" s="122"/>
-      <c r="Z14" s="122"/>
-      <c r="AA14" s="116"/>
-      <c r="AB14" s="116"/>
-      <c r="AC14" s="116"/>
-      <c r="AD14" s="122"/>
-      <c r="AE14" s="122"/>
-      <c r="AF14" s="122"/>
-      <c r="AG14" s="116"/>
-      <c r="AH14" s="116"/>
-      <c r="AI14" s="117"/>
-      <c r="AJ14" s="121" t="s">
-        <v>419</v>
-      </c>
-      <c r="AK14" s="122"/>
-      <c r="AL14" s="122"/>
-      <c r="AM14" s="116"/>
-      <c r="AN14" s="116"/>
-      <c r="AO14" s="116"/>
-      <c r="AP14" s="122"/>
-      <c r="AQ14" s="122"/>
-      <c r="AR14" s="122"/>
-      <c r="AS14" s="116"/>
-      <c r="AT14" s="116"/>
-      <c r="AU14" s="116"/>
-      <c r="AV14" s="122"/>
-      <c r="AW14" s="122"/>
-      <c r="AX14" s="122"/>
-      <c r="AY14" s="116"/>
-      <c r="AZ14" s="116"/>
-      <c r="BA14" s="116"/>
-      <c r="BB14" s="122"/>
-      <c r="BC14" s="122"/>
-      <c r="BD14" s="122"/>
-      <c r="BE14" s="116"/>
-      <c r="BF14" s="116"/>
-      <c r="BG14" s="117"/>
-    </row>
-    <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="94"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="114"/>
-      <c r="O15" s="138" t="s">
-        <v>420</v>
-      </c>
-      <c r="R15" s="133"/>
-      <c r="S15" s="133"/>
-      <c r="T15" s="133"/>
-      <c r="U15" s="132"/>
-      <c r="V15" s="132"/>
-      <c r="W15" s="132"/>
-      <c r="X15" s="133"/>
-      <c r="Y15" s="133"/>
-      <c r="Z15" s="133"/>
-      <c r="AA15" s="132"/>
-      <c r="AB15" s="132"/>
-      <c r="AC15" s="132"/>
-      <c r="AD15" s="122"/>
-      <c r="AE15" s="122"/>
-      <c r="AF15" s="122"/>
-      <c r="AG15" s="116"/>
-      <c r="AH15" s="116"/>
-      <c r="AI15" s="116"/>
-      <c r="AJ15" s="122"/>
-      <c r="AK15" s="122"/>
-      <c r="AL15" s="123"/>
-      <c r="AM15" s="139" t="s">
-        <v>426</v>
-      </c>
-      <c r="AN15" s="140"/>
-      <c r="AO15" s="140"/>
-      <c r="AP15" s="141"/>
-      <c r="AQ15" s="141"/>
-      <c r="AR15" s="141"/>
-      <c r="AS15" s="140"/>
-      <c r="AT15" s="140"/>
-      <c r="AU15" s="140"/>
-      <c r="AV15" s="141"/>
-      <c r="AW15" s="141"/>
-      <c r="AX15" s="141"/>
-      <c r="AY15" s="140"/>
-      <c r="AZ15" s="140"/>
-      <c r="BA15" s="140"/>
-      <c r="BB15" s="122"/>
-      <c r="BC15" s="122"/>
-      <c r="BD15" s="122"/>
-      <c r="BE15" s="116"/>
-      <c r="BF15" s="116"/>
-      <c r="BG15" s="116"/>
-      <c r="BH15" s="122"/>
-      <c r="BI15" s="122"/>
-      <c r="BJ15" s="123"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="118"/>
+      <c r="T15" s="118"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="117"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="118"/>
+      <c r="Y15" s="118"/>
+      <c r="Z15" s="118"/>
+      <c r="AA15" s="117"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="117"/>
+      <c r="AD15" s="107"/>
+      <c r="AE15" s="107"/>
+      <c r="AF15" s="107"/>
+      <c r="AG15" s="101"/>
+      <c r="AH15" s="101"/>
+      <c r="AI15" s="101"/>
+      <c r="AJ15" s="107"/>
+      <c r="AK15" s="107"/>
+      <c r="AL15" s="108"/>
+      <c r="AM15" s="124" t="s">
+        <v>425</v>
+      </c>
+      <c r="AN15" s="125"/>
+      <c r="AO15" s="125"/>
+      <c r="AP15" s="126"/>
+      <c r="AQ15" s="126"/>
+      <c r="AR15" s="126"/>
+      <c r="AS15" s="125"/>
+      <c r="AT15" s="125"/>
+      <c r="AU15" s="125"/>
+      <c r="AV15" s="126"/>
+      <c r="AW15" s="126"/>
+      <c r="AX15" s="126"/>
+      <c r="AY15" s="125"/>
+      <c r="AZ15" s="125"/>
+      <c r="BA15" s="125"/>
+      <c r="BB15" s="107"/>
+      <c r="BC15" s="107"/>
+      <c r="BD15" s="107"/>
+      <c r="BE15" s="101"/>
+      <c r="BF15" s="101"/>
+      <c r="BG15" s="101"/>
+      <c r="BH15" s="107"/>
+      <c r="BI15" s="107"/>
+      <c r="BJ15" s="108"/>
     </row>
     <row r="16" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>453</v>
-      </c>
-      <c r="M16" s="142"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="143"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="113" t="s">
-        <v>421</v>
-      </c>
-      <c r="S16" s="114"/>
-      <c r="T16" s="114"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="114"/>
-      <c r="Y16" s="114"/>
-      <c r="Z16" s="114"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="111"/>
-      <c r="AC16" s="111"/>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="114"/>
-      <c r="AF16" s="114"/>
-      <c r="AG16" s="111"/>
-      <c r="AH16" s="111"/>
-      <c r="AI16" s="111"/>
-      <c r="AJ16" s="107"/>
-      <c r="AK16" s="145"/>
-      <c r="AL16" s="146"/>
-      <c r="AM16" s="146"/>
-      <c r="AN16" s="146"/>
-      <c r="AO16" s="147"/>
-      <c r="AP16" s="121" t="s">
-        <v>427</v>
-      </c>
-      <c r="AQ16" s="122"/>
-      <c r="AR16" s="122"/>
-      <c r="AS16" s="116"/>
-      <c r="AT16" s="116"/>
-      <c r="AU16" s="116"/>
-      <c r="AV16" s="122"/>
-      <c r="AW16" s="122"/>
-      <c r="AX16" s="122"/>
+        <v>452</v>
+      </c>
+      <c r="M16" s="127"/>
+      <c r="N16" s="128"/>
+      <c r="O16" s="128"/>
+      <c r="P16" s="128"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="98" t="s">
+        <v>420</v>
+      </c>
+      <c r="S16" s="99"/>
+      <c r="T16" s="99"/>
+      <c r="U16" s="96"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="96"/>
+      <c r="X16" s="99"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="96"/>
+      <c r="AB16" s="96"/>
+      <c r="AC16" s="96"/>
+      <c r="AD16" s="99"/>
+      <c r="AE16" s="99"/>
+      <c r="AF16" s="99"/>
+      <c r="AG16" s="96"/>
+      <c r="AH16" s="96"/>
+      <c r="AI16" s="96"/>
+      <c r="AJ16" s="92"/>
+      <c r="AK16" s="130"/>
+      <c r="AL16" s="131"/>
+      <c r="AM16" s="131"/>
+      <c r="AN16" s="131"/>
+      <c r="AO16" s="132"/>
+      <c r="AP16" s="106" t="s">
+        <v>426</v>
+      </c>
+      <c r="AQ16" s="107"/>
+      <c r="AR16" s="107"/>
+      <c r="AS16" s="101"/>
+      <c r="AT16" s="101"/>
+      <c r="AU16" s="101"/>
+      <c r="AV16" s="107"/>
+      <c r="AW16" s="107"/>
+      <c r="AX16" s="107"/>
     </row>
     <row r="17" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>454</v>
-      </c>
-      <c r="B17" s="148"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="143"/>
-      <c r="K17" s="143"/>
-      <c r="L17" s="143"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="143"/>
-      <c r="O17" s="143"/>
-      <c r="P17" s="143"/>
-      <c r="Q17" s="144"/>
-      <c r="R17" s="113" t="s">
-        <v>422</v>
-      </c>
-      <c r="S17" s="107"/>
-      <c r="T17" s="149"/>
-      <c r="U17" s="150"/>
-      <c r="V17" s="150"/>
-      <c r="W17" s="150"/>
-      <c r="X17" s="150"/>
-      <c r="Y17" s="150"/>
-      <c r="Z17" s="150"/>
-      <c r="AA17" s="150"/>
-      <c r="AB17" s="150"/>
-      <c r="AC17" s="150"/>
-      <c r="AD17" s="150"/>
-      <c r="AE17" s="150"/>
-      <c r="AF17" s="150"/>
-      <c r="AG17" s="150"/>
-      <c r="AH17" s="150"/>
-      <c r="AI17" s="150"/>
-      <c r="AJ17" s="150"/>
-      <c r="AK17" s="150"/>
-      <c r="AL17" s="150"/>
-      <c r="AM17" s="150"/>
-      <c r="AN17" s="150"/>
-      <c r="AO17" s="151"/>
-      <c r="AP17" s="121" t="s">
-        <v>428</v>
-      </c>
-      <c r="AQ17" s="123"/>
-      <c r="AR17" s="149"/>
-      <c r="AS17" s="150"/>
-      <c r="AT17" s="150"/>
-      <c r="AU17" s="150"/>
-      <c r="AV17" s="150"/>
-      <c r="AW17" s="150"/>
-      <c r="AX17" s="151"/>
+        <v>453</v>
+      </c>
+      <c r="B17" s="133"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="128"/>
+      <c r="P17" s="128"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="98" t="s">
+        <v>421</v>
+      </c>
+      <c r="S17" s="92"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="135"/>
+      <c r="V17" s="135"/>
+      <c r="W17" s="135"/>
+      <c r="X17" s="135"/>
+      <c r="Y17" s="135"/>
+      <c r="Z17" s="135"/>
+      <c r="AA17" s="135"/>
+      <c r="AB17" s="135"/>
+      <c r="AC17" s="135"/>
+      <c r="AD17" s="135"/>
+      <c r="AE17" s="135"/>
+      <c r="AF17" s="135"/>
+      <c r="AG17" s="135"/>
+      <c r="AH17" s="135"/>
+      <c r="AI17" s="135"/>
+      <c r="AJ17" s="135"/>
+      <c r="AK17" s="135"/>
+      <c r="AL17" s="135"/>
+      <c r="AM17" s="135"/>
+      <c r="AN17" s="135"/>
+      <c r="AO17" s="136"/>
+      <c r="AP17" s="106" t="s">
+        <v>427</v>
+      </c>
+      <c r="AQ17" s="108"/>
+      <c r="AR17" s="134"/>
+      <c r="AS17" s="135"/>
+      <c r="AT17" s="135"/>
+      <c r="AU17" s="135"/>
+      <c r="AV17" s="135"/>
+      <c r="AW17" s="135"/>
+      <c r="AX17" s="136"/>
     </row>
     <row r="18" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>455</v>
-      </c>
-      <c r="B18" s="142"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="143"/>
-      <c r="J18" s="143"/>
-      <c r="K18" s="143"/>
-      <c r="L18" s="143"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="143"/>
-      <c r="O18" s="143"/>
-      <c r="P18" s="143"/>
-      <c r="Q18" s="143"/>
-      <c r="R18" s="143"/>
-      <c r="S18" s="143"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="143"/>
-      <c r="V18" s="143"/>
-      <c r="W18" s="144"/>
-      <c r="X18" s="152" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y18" s="134"/>
-      <c r="Z18" s="142"/>
-      <c r="AA18" s="143"/>
-      <c r="AB18" s="143"/>
-      <c r="AC18" s="143"/>
-      <c r="AD18" s="143"/>
-      <c r="AE18" s="143"/>
-      <c r="AF18" s="143"/>
-      <c r="AG18" s="143"/>
-      <c r="AH18" s="143"/>
-      <c r="AI18" s="143"/>
-      <c r="AJ18" s="143"/>
-      <c r="AK18" s="143"/>
-      <c r="AL18" s="143"/>
-      <c r="AM18" s="143"/>
-      <c r="AN18" s="143"/>
-      <c r="AO18" s="143"/>
-      <c r="AP18" s="143"/>
-      <c r="AQ18" s="143"/>
-      <c r="AR18" s="143"/>
-      <c r="AS18" s="143"/>
-      <c r="AT18" s="143"/>
-      <c r="AU18" s="144"/>
-      <c r="AV18" s="121" t="s">
-        <v>428</v>
-      </c>
-      <c r="AW18" s="123"/>
-      <c r="AX18" s="146"/>
-      <c r="AY18" s="146"/>
-      <c r="AZ18" s="146"/>
-      <c r="BA18" s="146"/>
-      <c r="BB18" s="146"/>
-      <c r="BC18" s="146"/>
-      <c r="BD18" s="146"/>
-      <c r="BE18" s="146"/>
-      <c r="BF18" s="146"/>
-      <c r="BG18" s="146"/>
-      <c r="BH18" s="146"/>
-      <c r="BI18" s="146"/>
-      <c r="BJ18" s="146"/>
-      <c r="BK18" s="146"/>
-      <c r="BL18" s="146"/>
-      <c r="BM18" s="146"/>
-      <c r="BN18" s="146"/>
-      <c r="BO18" s="146"/>
-      <c r="BP18" s="146"/>
-      <c r="BQ18" s="146"/>
-      <c r="BR18" s="146"/>
-      <c r="BS18" s="147"/>
+        <v>454</v>
+      </c>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="128"/>
+      <c r="O18" s="128"/>
+      <c r="P18" s="128"/>
+      <c r="Q18" s="128"/>
+      <c r="R18" s="128"/>
+      <c r="S18" s="128"/>
+      <c r="T18" s="128"/>
+      <c r="U18" s="128"/>
+      <c r="V18" s="128"/>
+      <c r="W18" s="129"/>
+      <c r="X18" s="137" t="s">
+        <v>421</v>
+      </c>
+      <c r="Y18" s="119"/>
+      <c r="Z18" s="127"/>
+      <c r="AA18" s="128"/>
+      <c r="AB18" s="128"/>
+      <c r="AC18" s="128"/>
+      <c r="AD18" s="128"/>
+      <c r="AE18" s="128"/>
+      <c r="AF18" s="128"/>
+      <c r="AG18" s="128"/>
+      <c r="AH18" s="128"/>
+      <c r="AI18" s="128"/>
+      <c r="AJ18" s="128"/>
+      <c r="AK18" s="128"/>
+      <c r="AL18" s="128"/>
+      <c r="AM18" s="128"/>
+      <c r="AN18" s="128"/>
+      <c r="AO18" s="128"/>
+      <c r="AP18" s="128"/>
+      <c r="AQ18" s="128"/>
+      <c r="AR18" s="128"/>
+      <c r="AS18" s="128"/>
+      <c r="AT18" s="128"/>
+      <c r="AU18" s="129"/>
+      <c r="AV18" s="106" t="s">
+        <v>427</v>
+      </c>
+      <c r="AW18" s="108"/>
+      <c r="AX18" s="131"/>
+      <c r="AY18" s="131"/>
+      <c r="AZ18" s="131"/>
+      <c r="BA18" s="131"/>
+      <c r="BB18" s="131"/>
+      <c r="BC18" s="131"/>
+      <c r="BD18" s="131"/>
+      <c r="BE18" s="131"/>
+      <c r="BF18" s="131"/>
+      <c r="BG18" s="131"/>
+      <c r="BH18" s="131"/>
+      <c r="BI18" s="131"/>
+      <c r="BJ18" s="131"/>
+      <c r="BK18" s="131"/>
+      <c r="BL18" s="131"/>
+      <c r="BM18" s="131"/>
+      <c r="BN18" s="131"/>
+      <c r="BO18" s="131"/>
+      <c r="BP18" s="131"/>
+      <c r="BQ18" s="131"/>
+      <c r="BR18" s="131"/>
+      <c r="BS18" s="132"/>
     </row>
     <row r="19" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B19" s="142"/>
-      <c r="C19" s="143"/>
-      <c r="D19" s="143"/>
-      <c r="E19" s="143"/>
-      <c r="F19" s="143"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="143"/>
-      <c r="I19" s="143"/>
-      <c r="J19" s="143"/>
-      <c r="K19" s="143"/>
-      <c r="L19" s="143"/>
-      <c r="M19" s="143"/>
-      <c r="N19" s="143"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="143"/>
-      <c r="Q19" s="143"/>
-      <c r="R19" s="143"/>
-      <c r="S19" s="143"/>
-      <c r="T19" s="144"/>
-      <c r="U19" s="131" t="s">
-        <v>422</v>
-      </c>
-      <c r="V19" s="153"/>
-      <c r="W19" s="142"/>
-      <c r="X19" s="143"/>
-      <c r="Y19" s="143"/>
-      <c r="Z19" s="143"/>
-      <c r="AA19" s="143"/>
-      <c r="AB19" s="143"/>
-      <c r="AC19" s="143"/>
-      <c r="AD19" s="143"/>
-      <c r="AE19" s="143"/>
-      <c r="AF19" s="143"/>
-      <c r="AG19" s="143"/>
-      <c r="AH19" s="143"/>
-      <c r="AI19" s="143"/>
-      <c r="AJ19" s="143"/>
-      <c r="AK19" s="143"/>
-      <c r="AL19" s="143"/>
-      <c r="AM19" s="143"/>
-      <c r="AN19" s="143"/>
-      <c r="AO19" s="143"/>
-      <c r="AP19" s="143"/>
-      <c r="AQ19" s="143"/>
-      <c r="AR19" s="144"/>
-      <c r="AS19" s="139" t="s">
-        <v>428</v>
-      </c>
-      <c r="AT19" s="154"/>
+        <v>455</v>
+      </c>
+      <c r="B19" s="127"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="128"/>
+      <c r="O19" s="128"/>
+      <c r="P19" s="128"/>
+      <c r="Q19" s="128"/>
+      <c r="R19" s="128"/>
+      <c r="S19" s="128"/>
+      <c r="T19" s="129"/>
+      <c r="U19" s="116" t="s">
+        <v>421</v>
+      </c>
+      <c r="V19" s="138"/>
+      <c r="W19" s="127"/>
+      <c r="X19" s="128"/>
+      <c r="Y19" s="128"/>
+      <c r="Z19" s="128"/>
+      <c r="AA19" s="128"/>
+      <c r="AB19" s="128"/>
+      <c r="AC19" s="128"/>
+      <c r="AD19" s="128"/>
+      <c r="AE19" s="128"/>
+      <c r="AF19" s="128"/>
+      <c r="AG19" s="128"/>
+      <c r="AH19" s="128"/>
+      <c r="AI19" s="128"/>
+      <c r="AJ19" s="128"/>
+      <c r="AK19" s="128"/>
+      <c r="AL19" s="128"/>
+      <c r="AM19" s="128"/>
+      <c r="AN19" s="128"/>
+      <c r="AO19" s="128"/>
+      <c r="AP19" s="128"/>
+      <c r="AQ19" s="128"/>
+      <c r="AR19" s="129"/>
+      <c r="AS19" s="124" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT19" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F379C5-6C33-4FF2-8D54-D7B23D1A2791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9AFCB7-F9E3-4ABA-B975-F52D20D8E9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangPrimer25K (SLOT無し版)" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="457">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1250,10 +1250,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>RESET</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>IO_CLK</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1317,10 +1313,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>マイコン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>LCD</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1836,6 +1828,10 @@
   </si>
   <si>
     <t>pause</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RESET_N</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2546,7 +2542,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2700,9 +2696,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3014,6 +3007,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4637,7 +4636,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="141" t="s">
+      <c r="AC9" s="140" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4698,7 +4697,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="141"/>
+      <c r="AC10" s="140"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -4761,7 +4760,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="141"/>
+      <c r="AC11" s="140"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -4822,7 +4821,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="141"/>
+      <c r="AC12" s="140"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -4887,7 +4886,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="141"/>
+      <c r="AC13" s="140"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -4956,7 +4955,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="141"/>
+      <c r="AC14" s="140"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -5219,7 +5218,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="142" t="s">
+      <c r="AC18" s="141" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5284,7 +5283,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="142"/>
+      <c r="AC19" s="141"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -5343,7 +5342,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="142"/>
+      <c r="AC20" s="141"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -5406,7 +5405,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="142"/>
+      <c r="AC21" s="141"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -5467,7 +5466,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="141" t="s">
+      <c r="AC22" s="140" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5530,7 +5529,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="141"/>
+      <c r="AC23" s="140"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -5591,7 +5590,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="141"/>
+      <c r="AC24" s="140"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -5650,7 +5649,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="141"/>
+      <c r="AC25" s="140"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -5713,7 +5712,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="141"/>
+      <c r="AC26" s="140"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -5774,7 +5773,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="141"/>
+      <c r="AC27" s="140"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -6658,7 +6657,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="141" t="s">
+      <c r="AC9" s="140" t="s">
         <v>245</v>
       </c>
     </row>
@@ -6727,7 +6726,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="141"/>
+      <c r="AC10" s="140"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -6794,7 +6793,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="141"/>
+      <c r="AC11" s="140"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -6861,7 +6860,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="141"/>
+      <c r="AC12" s="140"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -6930,7 +6929,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="141"/>
+      <c r="AC13" s="140"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -7003,7 +7002,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="141"/>
+      <c r="AC14" s="140"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -7288,7 +7287,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="142" t="s">
+      <c r="AC18" s="141" t="s">
         <v>246</v>
       </c>
     </row>
@@ -7357,7 +7356,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="142"/>
+      <c r="AC19" s="141"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -7424,7 +7423,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="142"/>
+      <c r="AC20" s="141"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -7495,7 +7494,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="142"/>
+      <c r="AC21" s="141"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -7560,7 +7559,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="141" t="s">
+      <c r="AC22" s="140" t="s">
         <v>244</v>
       </c>
     </row>
@@ -7627,7 +7626,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="141"/>
+      <c r="AC23" s="140"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -7692,7 +7691,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="141"/>
+      <c r="AC24" s="140"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -7755,7 +7754,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="141"/>
+      <c r="AC25" s="140"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -7818,7 +7817,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="141"/>
+      <c r="AC26" s="140"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -7883,7 +7882,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="141"/>
+      <c r="AC27" s="140"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -8012,7 +8011,7 @@
       <c r="AB29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AC29" s="143" t="s">
+      <c r="AC29" s="142" t="s">
         <v>243</v>
       </c>
     </row>
@@ -8083,7 +8082,7 @@
       <c r="AB30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC30" s="143"/>
+      <c r="AC30" s="142"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="21">
@@ -8148,7 +8147,7 @@
       <c r="AB31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC31" s="143"/>
+      <c r="AC31" s="142"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
@@ -8211,7 +8210,7 @@
       <c r="AB32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC32" s="143"/>
+      <c r="AC32" s="142"/>
     </row>
     <row r="33" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
@@ -8315,14 +8314,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="143" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -8418,7 +8417,7 @@
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="52"/>
+      <c r="H5" s="51"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -8455,7 +8454,7 @@
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="52"/>
+      <c r="H6" s="51"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -8493,7 +8492,7 @@
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="52"/>
+      <c r="H7" s="51"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -8506,15 +8505,13 @@
       <c r="M7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="24" t="s">
-        <v>313</v>
+      <c r="N7" s="19" t="s">
+        <v>326</v>
       </c>
       <c r="O7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="51" t="s">
-        <v>317</v>
-      </c>
+      <c r="P7" s="53"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
@@ -8527,11 +8524,11 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F8" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F8" s="52"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="51"/>
       <c r="J8" s="11">
         <v>36</v>
       </c>
@@ -8542,9 +8539,9 @@
         <v>4</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="N8" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="N8" s="52"/>
       <c r="O8" s="12"/>
       <c r="P8" s="47"/>
     </row>
@@ -8567,7 +8564,7 @@
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="52"/>
+      <c r="H9" s="51"/>
       <c r="J9" s="11">
         <v>35</v>
       </c>
@@ -8578,11 +8575,11 @@
         <v>4</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="N9" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="N9" s="52"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="52"/>
+      <c r="P9" s="51"/>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="11">
@@ -8603,7 +8600,7 @@
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="52"/>
+      <c r="H10" s="51"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -8622,8 +8619,8 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="143" t="s">
-        <v>305</v>
+      <c r="P10" s="142" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8637,11 +8634,11 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F11" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F11" s="52"/>
       <c r="G11" s="12"/>
-      <c r="H11" s="52"/>
+      <c r="H11" s="51"/>
       <c r="J11" s="11">
         <v>33</v>
       </c>
@@ -8660,7 +8657,7 @@
       <c r="O11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P11" s="143"/>
+      <c r="P11" s="142"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -8673,9 +8670,9 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F12" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F12" s="52"/>
       <c r="G12" s="12"/>
       <c r="H12" s="33"/>
       <c r="J12" s="11">
@@ -8691,10 +8688,10 @@
         <v>296</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P12" s="33"/>
     </row>
@@ -8709,9 +8706,9 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F13" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F13" s="52"/>
       <c r="G13" s="12"/>
       <c r="H13" s="33"/>
       <c r="J13" s="11">
@@ -8724,9 +8721,9 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="N13" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="N13" s="52"/>
       <c r="O13" s="12"/>
       <c r="P13" s="33"/>
     </row>
@@ -8741,9 +8738,9 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F14" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F14" s="52"/>
       <c r="G14" s="12"/>
       <c r="H14" s="33"/>
       <c r="J14" s="11">
@@ -8765,7 +8762,7 @@
         <v>48</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
@@ -8779,9 +8776,9 @@
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F15" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F15" s="52"/>
       <c r="G15" s="12"/>
       <c r="H15" s="33"/>
       <c r="J15" s="11">
@@ -8794,11 +8791,11 @@
         <v>3</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="N15" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="N15" s="52"/>
       <c r="O15" s="12"/>
-      <c r="P15" s="52"/>
+      <c r="P15" s="51"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
@@ -8811,9 +8808,9 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F16" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F16" s="52"/>
       <c r="G16" s="12"/>
       <c r="H16" s="33"/>
       <c r="J16" s="11">
@@ -8828,7 +8825,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="12"/>
-      <c r="P16" s="52"/>
+      <c r="P16" s="51"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -8841,9 +8838,9 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F17" s="53"/>
+        <v>316</v>
+      </c>
+      <c r="F17" s="52"/>
       <c r="G17" s="12"/>
       <c r="H17" s="33"/>
       <c r="J17" s="11">
@@ -8858,11 +8855,9 @@
       <c r="M17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N17" s="19" t="s">
-        <v>328</v>
-      </c>
+      <c r="N17" s="155"/>
       <c r="O17" s="12"/>
-      <c r="P17" s="54"/>
+      <c r="P17" s="156"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -8878,12 +8873,12 @@
         <v>263</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="142" t="s">
+      <c r="H18" s="141" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -8919,12 +8914,12 @@
         <v>263</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="142"/>
+      <c r="H19" s="141"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -8963,7 +8958,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="142"/>
+      <c r="H20" s="141"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -8976,7 +8971,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="12"/>
-      <c r="P20" s="52"/>
+      <c r="P20" s="51"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B21" s="11">
@@ -8997,7 +8992,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="142"/>
+      <c r="H21" s="141"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -9010,7 +9005,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="12"/>
-      <c r="P21" s="52"/>
+      <c r="P21" s="51"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -9124,14 +9119,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="143" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -9185,12 +9180,12 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="141" t="s">
+      <c r="H4" s="140" t="s">
         <v>244</v>
       </c>
       <c r="J4" s="8">
@@ -9224,12 +9219,12 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="141"/>
+      <c r="H5" s="140"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -9261,12 +9256,12 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="141"/>
+      <c r="H6" s="140"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -9299,12 +9294,12 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="19" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="141"/>
+      <c r="H7" s="140"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -9317,14 +9312,14 @@
       <c r="M7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="24" t="s">
-        <v>313</v>
+      <c r="N7" s="19" t="s">
+        <v>326</v>
       </c>
       <c r="O7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="51" t="s">
-        <v>317</v>
+      <c r="P7" s="53" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
@@ -9339,13 +9334,13 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="44" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>210</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J8" s="11">
         <v>36</v>
@@ -9374,12 +9369,12 @@
         <v>263</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="141" t="s">
+      <c r="H9" s="140" t="s">
         <v>244</v>
       </c>
       <c r="J9" s="11">
@@ -9399,7 +9394,7 @@
         <v>48</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -9416,12 +9411,12 @@
         <v>263</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="141"/>
+      <c r="H10" s="140"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -9440,8 +9435,8 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="143" t="s">
-        <v>305</v>
+      <c r="P10" s="142" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -9456,13 +9451,13 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="146" t="s">
-        <v>315</v>
+      <c r="H11" s="145" t="s">
+        <v>314</v>
       </c>
       <c r="J11" s="11">
         <v>33</v>
@@ -9482,7 +9477,7 @@
       <c r="O11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="143"/>
+      <c r="P11" s="142"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -9496,12 +9491,12 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="44" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="146"/>
+      <c r="H12" s="145"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -9515,10 +9510,10 @@
         <v>296</v>
       </c>
       <c r="N12" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="O12" s="12" t="s">
         <v>311</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>312</v>
       </c>
       <c r="P12" s="33"/>
     </row>
@@ -9534,12 +9529,12 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H13" s="146"/>
+      <c r="H13" s="145"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -9551,13 +9546,13 @@
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="143" t="s">
-        <v>305</v>
+      <c r="P13" s="142" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.15">
@@ -9572,12 +9567,12 @@
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="146"/>
+      <c r="H14" s="145"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -9596,7 +9591,7 @@
       <c r="O14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="143"/>
+      <c r="P14" s="142"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
@@ -9610,12 +9605,12 @@
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="44" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H15" s="146"/>
+      <c r="H15" s="145"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -9632,8 +9627,8 @@
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="146" t="s">
-        <v>316</v>
+      <c r="P15" s="145" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
@@ -9648,12 +9643,12 @@
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="44" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="146"/>
+      <c r="H16" s="145"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -9670,7 +9665,7 @@
       <c r="O16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="146"/>
+      <c r="P16" s="145"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -9684,12 +9679,12 @@
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H17" s="146"/>
+      <c r="H17" s="145"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -9702,13 +9697,9 @@
       <c r="M17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N17" s="19" t="s">
-        <v>328</v>
-      </c>
+      <c r="N17" s="155"/>
       <c r="O17" s="12"/>
-      <c r="P17" s="54" t="s">
-        <v>336</v>
-      </c>
+      <c r="P17" s="156"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -9724,12 +9715,12 @@
         <v>263</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="142" t="s">
+      <c r="H18" s="141" t="s">
         <v>292</v>
       </c>
       <c r="J18" s="8">
@@ -9765,12 +9756,12 @@
         <v>263</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>230</v>
+        <v>327</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="142"/>
+      <c r="H19" s="141"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -9809,7 +9800,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="142"/>
+      <c r="H20" s="141"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -9821,13 +9812,13 @@
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="45" t="s">
-        <v>302</v>
+        <v>456</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="145" t="s">
-        <v>316</v>
+      <c r="P20" s="144" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.15">
@@ -9849,7 +9840,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="142"/>
+      <c r="H21" s="141"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -9861,12 +9852,12 @@
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="45" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="145"/>
+      <c r="P21" s="144"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -9946,30 +9937,30 @@
     </row>
     <row r="36" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -9996,476 +9987,476 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="3" customWidth="1"/>
-    <col min="3" max="3" width="3.5" style="55" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="9" style="55"/>
+    <col min="3" max="3" width="3.5" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="9" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C2" s="57"/>
-      <c r="D2" s="58" t="s">
+      <c r="C2" s="56"/>
+      <c r="D2" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="E2" s="58">
+        <v>0</v>
+      </c>
+      <c r="F2" s="59">
+        <v>1</v>
+      </c>
+      <c r="G2" s="59">
+        <v>2</v>
+      </c>
+      <c r="H2" s="59">
+        <v>3</v>
+      </c>
+      <c r="I2" s="59">
+        <v>4</v>
+      </c>
+      <c r="J2" s="59">
+        <v>5</v>
+      </c>
+      <c r="K2" s="59">
+        <v>6</v>
+      </c>
+      <c r="L2" s="57">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="60"/>
+      <c r="D3" s="61" t="s">
+        <v>336</v>
+      </c>
+      <c r="E3" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="E2" s="59">
+      <c r="F3" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="G3" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="H3" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="I3" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="J3" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="K3" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="L3" s="65" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C4" s="66">
+        <v>1</v>
+      </c>
+      <c r="D4" s="67" t="s">
+        <v>345</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>353</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>362</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>378</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>388</v>
+      </c>
+      <c r="I4" s="69" t="s">
+        <v>370</v>
+      </c>
+      <c r="J4" s="69" t="s">
+        <v>370</v>
+      </c>
+      <c r="K4" s="69" t="s">
+        <v>396</v>
+      </c>
+      <c r="L4" s="70" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C5" s="71">
+        <v>2</v>
+      </c>
+      <c r="D5" s="72" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="73" t="s">
+        <v>354</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>369</v>
+      </c>
+      <c r="G5" s="74" t="s">
+        <v>379</v>
+      </c>
+      <c r="H5" s="74" t="s">
+        <v>389</v>
+      </c>
+      <c r="I5" s="74" t="s">
+        <v>377</v>
+      </c>
+      <c r="J5" s="74" t="s">
+        <v>377</v>
+      </c>
+      <c r="K5" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="L5" s="75" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C6" s="71">
+        <v>3</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>347</v>
+      </c>
+      <c r="E6" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="F6" s="74" t="s">
+        <v>363</v>
+      </c>
+      <c r="G6" s="74" t="s">
+        <v>382</v>
+      </c>
+      <c r="H6" s="74" t="s">
+        <v>390</v>
+      </c>
+      <c r="I6" s="74" t="s">
+        <v>371</v>
+      </c>
+      <c r="J6" s="74" t="s">
+        <v>371</v>
+      </c>
+      <c r="K6" s="74" t="s">
+        <v>398</v>
+      </c>
+      <c r="L6" s="75" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C7" s="71">
+        <v>4</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" s="74" t="s">
+        <v>364</v>
+      </c>
+      <c r="G7" s="74" t="s">
+        <v>383</v>
+      </c>
+      <c r="H7" s="74" t="s">
+        <v>391</v>
+      </c>
+      <c r="I7" s="74" t="s">
+        <v>372</v>
+      </c>
+      <c r="J7" s="74" t="s">
+        <v>372</v>
+      </c>
+      <c r="K7" s="74" t="s">
+        <v>455</v>
+      </c>
+      <c r="L7" s="75" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C8" s="71">
+        <v>5</v>
+      </c>
+      <c r="D8" s="72" t="s">
+        <v>349</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>357</v>
+      </c>
+      <c r="F8" s="74" t="s">
+        <v>365</v>
+      </c>
+      <c r="G8" s="74" t="s">
+        <v>384</v>
+      </c>
+      <c r="H8" s="74" t="s">
+        <v>392</v>
+      </c>
+      <c r="I8" s="74" t="s">
+        <v>373</v>
+      </c>
+      <c r="J8" s="74" t="s">
+        <v>373</v>
+      </c>
+      <c r="K8" s="74" t="s">
+        <v>399</v>
+      </c>
+      <c r="L8" s="75" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C9" s="71">
+        <v>6</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="74" t="s">
+        <v>366</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>385</v>
+      </c>
+      <c r="H9" s="74" t="s">
+        <v>393</v>
+      </c>
+      <c r="I9" s="74" t="s">
+        <v>374</v>
+      </c>
+      <c r="J9" s="74" t="s">
+        <v>374</v>
+      </c>
+      <c r="K9" s="74" t="s">
+        <v>400</v>
+      </c>
+      <c r="L9" s="75" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C10" s="71">
+        <v>7</v>
+      </c>
+      <c r="D10" s="72" t="s">
+        <v>351</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>359</v>
+      </c>
+      <c r="F10" s="74" t="s">
+        <v>367</v>
+      </c>
+      <c r="G10" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="H10" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="I10" s="74" t="s">
+        <v>375</v>
+      </c>
+      <c r="J10" s="74" t="s">
+        <v>375</v>
+      </c>
+      <c r="K10" s="74" t="s">
+        <v>401</v>
+      </c>
+      <c r="L10" s="75" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="76">
+        <v>8</v>
+      </c>
+      <c r="D11" s="77" t="s">
+        <v>352</v>
+      </c>
+      <c r="E11" s="78" t="s">
+        <v>360</v>
+      </c>
+      <c r="F11" s="79" t="s">
+        <v>368</v>
+      </c>
+      <c r="G11" s="79" t="s">
+        <v>387</v>
+      </c>
+      <c r="H11" s="79" t="s">
+        <v>395</v>
+      </c>
+      <c r="I11" s="79" t="s">
+        <v>376</v>
+      </c>
+      <c r="J11" s="79" t="s">
+        <v>376</v>
+      </c>
+      <c r="K11" s="79" t="s">
+        <v>402</v>
+      </c>
+      <c r="L11" s="80" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C12" s="56">
+        <v>9</v>
+      </c>
+      <c r="D12" s="81" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="58">
         <v>0</v>
       </c>
-      <c r="F2" s="60">
+      <c r="F12" s="59">
+        <v>0</v>
+      </c>
+      <c r="G12" s="59">
+        <v>0</v>
+      </c>
+      <c r="H12" s="59">
+        <v>0</v>
+      </c>
+      <c r="I12" s="59">
         <v>1</v>
       </c>
-      <c r="G2" s="60">
-        <v>2</v>
-      </c>
-      <c r="H2" s="60">
-        <v>3</v>
-      </c>
-      <c r="I2" s="60">
-        <v>4</v>
-      </c>
-      <c r="J2" s="60">
-        <v>5</v>
-      </c>
-      <c r="K2" s="60">
-        <v>6</v>
-      </c>
-      <c r="L2" s="58">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="61"/>
-      <c r="D3" s="62" t="s">
-        <v>338</v>
-      </c>
-      <c r="E3" s="63" t="s">
+      <c r="J12" s="59">
+        <v>1</v>
+      </c>
+      <c r="K12" s="59">
+        <v>1</v>
+      </c>
+      <c r="L12" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C13" s="71">
+        <v>10</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="E13" s="73">
+        <v>0</v>
+      </c>
+      <c r="F13" s="74">
+        <v>0</v>
+      </c>
+      <c r="G13" s="74">
+        <v>1</v>
+      </c>
+      <c r="H13" s="74">
+        <v>1</v>
+      </c>
+      <c r="I13" s="74">
+        <v>0</v>
+      </c>
+      <c r="J13" s="74">
+        <v>0</v>
+      </c>
+      <c r="K13" s="74">
+        <v>1</v>
+      </c>
+      <c r="L13" s="75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="60">
+        <v>11</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>342</v>
+      </c>
+      <c r="E14" s="84">
+        <v>0</v>
+      </c>
+      <c r="F14" s="85">
+        <v>1</v>
+      </c>
+      <c r="G14" s="85">
+        <v>0</v>
+      </c>
+      <c r="H14" s="85">
+        <v>1</v>
+      </c>
+      <c r="I14" s="85">
+        <v>0</v>
+      </c>
+      <c r="J14" s="85">
+        <v>1</v>
+      </c>
+      <c r="K14" s="85">
+        <v>0</v>
+      </c>
+      <c r="L14" s="61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="86">
+        <v>12</v>
+      </c>
+      <c r="D15" s="87" t="s">
+        <v>381</v>
+      </c>
+      <c r="E15" s="149" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="151"/>
+    </row>
+    <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="88">
+        <v>13</v>
+      </c>
+      <c r="D16" s="89" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="146" t="s">
+        <v>344</v>
+      </c>
+      <c r="F16" s="147"/>
+      <c r="G16" s="147"/>
+      <c r="H16" s="147"/>
+      <c r="I16" s="147"/>
+      <c r="J16" s="147"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="148"/>
+    </row>
+    <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="88"/>
+      <c r="D17" s="55" t="s">
         <v>339</v>
       </c>
-      <c r="F3" s="64" t="s">
-        <v>339</v>
-      </c>
-      <c r="G3" s="64" t="s">
-        <v>339</v>
-      </c>
-      <c r="H3" s="64" t="s">
-        <v>339</v>
-      </c>
-      <c r="I3" s="64" t="s">
-        <v>339</v>
-      </c>
-      <c r="J3" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="K3" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="L3" s="66" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C4" s="67">
-        <v>1</v>
-      </c>
-      <c r="D4" s="68" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>355</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>364</v>
-      </c>
-      <c r="G4" s="70" t="s">
-        <v>380</v>
-      </c>
-      <c r="H4" s="70" t="s">
-        <v>390</v>
-      </c>
-      <c r="I4" s="70" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="70" t="s">
-        <v>372</v>
-      </c>
-      <c r="K4" s="70" t="s">
-        <v>398</v>
-      </c>
-      <c r="L4" s="71" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C5" s="72">
-        <v>2</v>
-      </c>
-      <c r="D5" s="73" t="s">
-        <v>348</v>
-      </c>
-      <c r="E5" s="74" t="s">
-        <v>356</v>
-      </c>
-      <c r="F5" s="75" t="s">
-        <v>371</v>
-      </c>
-      <c r="G5" s="75" t="s">
-        <v>381</v>
-      </c>
-      <c r="H5" s="75" t="s">
-        <v>391</v>
-      </c>
-      <c r="I5" s="75" t="s">
-        <v>379</v>
-      </c>
-      <c r="J5" s="75" t="s">
-        <v>379</v>
-      </c>
-      <c r="K5" s="75" t="s">
-        <v>399</v>
-      </c>
-      <c r="L5" s="76" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C6" s="72">
-        <v>3</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>349</v>
-      </c>
-      <c r="E6" s="74" t="s">
-        <v>357</v>
-      </c>
-      <c r="F6" s="75" t="s">
-        <v>365</v>
-      </c>
-      <c r="G6" s="75" t="s">
-        <v>384</v>
-      </c>
-      <c r="H6" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="I6" s="75" t="s">
-        <v>373</v>
-      </c>
-      <c r="J6" s="75" t="s">
-        <v>373</v>
-      </c>
-      <c r="K6" s="75" t="s">
-        <v>400</v>
-      </c>
-      <c r="L6" s="76" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C7" s="72">
-        <v>4</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>350</v>
-      </c>
-      <c r="E7" s="74" t="s">
-        <v>358</v>
-      </c>
-      <c r="F7" s="75" t="s">
-        <v>366</v>
-      </c>
-      <c r="G7" s="75" t="s">
-        <v>385</v>
-      </c>
-      <c r="H7" s="75" t="s">
-        <v>393</v>
-      </c>
-      <c r="I7" s="75" t="s">
-        <v>374</v>
-      </c>
-      <c r="J7" s="75" t="s">
-        <v>374</v>
-      </c>
-      <c r="K7" s="75" t="s">
-        <v>457</v>
-      </c>
-      <c r="L7" s="76" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C8" s="72">
-        <v>5</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>351</v>
-      </c>
-      <c r="E8" s="74" t="s">
-        <v>359</v>
-      </c>
-      <c r="F8" s="75" t="s">
-        <v>367</v>
-      </c>
-      <c r="G8" s="75" t="s">
-        <v>386</v>
-      </c>
-      <c r="H8" s="75" t="s">
-        <v>394</v>
-      </c>
-      <c r="I8" s="75" t="s">
-        <v>375</v>
-      </c>
-      <c r="J8" s="75" t="s">
-        <v>375</v>
-      </c>
-      <c r="K8" s="75" t="s">
-        <v>401</v>
-      </c>
-      <c r="L8" s="76" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C9" s="72">
-        <v>6</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>352</v>
-      </c>
-      <c r="E9" s="74" t="s">
-        <v>360</v>
-      </c>
-      <c r="F9" s="75" t="s">
-        <v>368</v>
-      </c>
-      <c r="G9" s="75" t="s">
-        <v>387</v>
-      </c>
-      <c r="H9" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="I9" s="75" t="s">
-        <v>376</v>
-      </c>
-      <c r="J9" s="75" t="s">
-        <v>376</v>
-      </c>
-      <c r="K9" s="75" t="s">
-        <v>402</v>
-      </c>
-      <c r="L9" s="76" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C10" s="72">
-        <v>7</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>353</v>
-      </c>
-      <c r="E10" s="74" t="s">
+      <c r="E17" s="152" t="s">
+        <v>411</v>
+      </c>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="154"/>
+      <c r="J17" s="152" t="s">
         <v>361</v>
       </c>
-      <c r="F10" s="75" t="s">
-        <v>369</v>
-      </c>
-      <c r="G10" s="75" t="s">
-        <v>388</v>
-      </c>
-      <c r="H10" s="75" t="s">
-        <v>396</v>
-      </c>
-      <c r="I10" s="75" t="s">
-        <v>377</v>
-      </c>
-      <c r="J10" s="75" t="s">
-        <v>377</v>
-      </c>
-      <c r="K10" s="75" t="s">
-        <v>403</v>
-      </c>
-      <c r="L10" s="76" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="77">
-        <v>8</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>354</v>
-      </c>
-      <c r="E11" s="79" t="s">
-        <v>362</v>
-      </c>
-      <c r="F11" s="80" t="s">
-        <v>370</v>
-      </c>
-      <c r="G11" s="80" t="s">
-        <v>389</v>
-      </c>
-      <c r="H11" s="80" t="s">
-        <v>397</v>
-      </c>
-      <c r="I11" s="80" t="s">
-        <v>378</v>
-      </c>
-      <c r="J11" s="80" t="s">
-        <v>378</v>
-      </c>
-      <c r="K11" s="80" t="s">
-        <v>404</v>
-      </c>
-      <c r="L11" s="81" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C12" s="57">
-        <v>9</v>
-      </c>
-      <c r="D12" s="82" t="s">
-        <v>342</v>
-      </c>
-      <c r="E12" s="59">
-        <v>0</v>
-      </c>
-      <c r="F12" s="60">
-        <v>0</v>
-      </c>
-      <c r="G12" s="60">
-        <v>0</v>
-      </c>
-      <c r="H12" s="60">
-        <v>0</v>
-      </c>
-      <c r="I12" s="60">
-        <v>1</v>
-      </c>
-      <c r="J12" s="60">
-        <v>1</v>
-      </c>
-      <c r="K12" s="60">
-        <v>1</v>
-      </c>
-      <c r="L12" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C13" s="72">
-        <v>10</v>
-      </c>
-      <c r="D13" s="83" t="s">
-        <v>343</v>
-      </c>
-      <c r="E13" s="74">
-        <v>0</v>
-      </c>
-      <c r="F13" s="75">
-        <v>0</v>
-      </c>
-      <c r="G13" s="75">
-        <v>1</v>
-      </c>
-      <c r="H13" s="75">
-        <v>1</v>
-      </c>
-      <c r="I13" s="75">
-        <v>0</v>
-      </c>
-      <c r="J13" s="75">
-        <v>0</v>
-      </c>
-      <c r="K13" s="75">
-        <v>1</v>
-      </c>
-      <c r="L13" s="76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="61">
-        <v>11</v>
-      </c>
-      <c r="D14" s="84" t="s">
-        <v>344</v>
-      </c>
-      <c r="E14" s="85">
-        <v>0</v>
-      </c>
-      <c r="F14" s="86">
-        <v>1</v>
-      </c>
-      <c r="G14" s="86">
-        <v>0</v>
-      </c>
-      <c r="H14" s="86">
-        <v>1</v>
-      </c>
-      <c r="I14" s="86">
-        <v>0</v>
-      </c>
-      <c r="J14" s="86">
-        <v>1</v>
-      </c>
-      <c r="K14" s="86">
-        <v>0</v>
-      </c>
-      <c r="L14" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="87">
-        <v>12</v>
-      </c>
-      <c r="D15" s="88" t="s">
-        <v>383</v>
-      </c>
-      <c r="E15" s="150" t="s">
-        <v>382</v>
-      </c>
-      <c r="F15" s="151"/>
-      <c r="G15" s="151"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="151"/>
-      <c r="J15" s="151"/>
-      <c r="K15" s="151"/>
-      <c r="L15" s="152"/>
-    </row>
-    <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="89">
-        <v>13</v>
-      </c>
-      <c r="D16" s="90" t="s">
-        <v>345</v>
-      </c>
-      <c r="E16" s="147" t="s">
-        <v>346</v>
-      </c>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="148"/>
-      <c r="L16" s="149"/>
-    </row>
-    <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="89"/>
-      <c r="D17" s="56" t="s">
-        <v>341</v>
-      </c>
-      <c r="E17" s="153" t="s">
-        <v>413</v>
-      </c>
-      <c r="F17" s="154"/>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="155"/>
-      <c r="J17" s="153" t="s">
-        <v>363</v>
-      </c>
-      <c r="K17" s="154"/>
-      <c r="L17" s="155"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10486,15 +10477,15 @@
   <sheetFormatPr defaultColWidth="4.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="4.25" style="91"/>
-    <col min="9" max="11" width="4.25" style="91"/>
-    <col min="15" max="17" width="4.25" style="91"/>
-    <col min="21" max="23" width="4.25" style="91"/>
+    <col min="3" max="5" width="4.25" style="90"/>
+    <col min="9" max="11" width="4.25" style="90"/>
+    <col min="15" max="17" width="4.25" style="90"/>
+    <col min="21" max="23" width="4.25" style="90"/>
     <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.25" style="91"/>
-    <col min="33" max="35" width="4.25" style="91"/>
-    <col min="39" max="41" width="4.25" style="91"/>
-    <col min="45" max="47" width="4.25" style="91"/>
+    <col min="27" max="29" width="4.25" style="90"/>
+    <col min="33" max="35" width="4.25" style="90"/>
+    <col min="39" max="41" width="4.25" style="90"/>
+    <col min="45" max="47" width="4.25" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.15">
@@ -10503,19 +10494,19 @@
       </c>
     </row>
     <row r="2" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="140" t="s">
-        <v>456</v>
+      <c r="A2" s="139" t="s">
+        <v>454</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="91">
+      <c r="C2" s="90">
         <v>1</v>
       </c>
-      <c r="D2" s="91">
+      <c r="D2" s="90">
         <v>2</v>
       </c>
-      <c r="E2" s="91">
+      <c r="E2" s="90">
         <v>3</v>
       </c>
       <c r="F2">
@@ -10527,13 +10518,13 @@
       <c r="H2">
         <v>6</v>
       </c>
-      <c r="I2" s="91">
+      <c r="I2" s="90">
         <v>7</v>
       </c>
-      <c r="J2" s="91">
+      <c r="J2" s="90">
         <v>8</v>
       </c>
-      <c r="K2" s="91">
+      <c r="K2" s="90">
         <v>9</v>
       </c>
       <c r="L2">
@@ -10545,13 +10536,13 @@
       <c r="N2">
         <v>12</v>
       </c>
-      <c r="O2" s="91">
+      <c r="O2" s="90">
         <v>13</v>
       </c>
-      <c r="P2" s="91">
+      <c r="P2" s="90">
         <v>14</v>
       </c>
-      <c r="Q2" s="91">
+      <c r="Q2" s="90">
         <v>15</v>
       </c>
       <c r="R2">
@@ -10563,13 +10554,13 @@
       <c r="T2">
         <v>18</v>
       </c>
-      <c r="U2" s="91">
+      <c r="U2" s="90">
         <v>19</v>
       </c>
-      <c r="V2" s="91">
+      <c r="V2" s="90">
         <v>20</v>
       </c>
-      <c r="W2" s="91">
+      <c r="W2" s="90">
         <v>21</v>
       </c>
       <c r="X2">
@@ -10584,847 +10575,847 @@
     </row>
     <row r="3" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>414</v>
-      </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="93"/>
-      <c r="V3" s="93"/>
-      <c r="W3" s="93"/>
-      <c r="X3" s="94"/>
-      <c r="Y3" s="94"/>
-      <c r="Z3" s="94"/>
-      <c r="AA3" s="93"/>
-      <c r="AB3" s="93"/>
-      <c r="AC3" s="93"/>
-      <c r="AD3" s="94"/>
-      <c r="AE3" s="94"/>
-      <c r="AF3" s="94"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="93"/>
-      <c r="AJ3" s="94"/>
-      <c r="AK3" s="94"/>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="93"/>
-      <c r="AN3" s="93"/>
-      <c r="AO3" s="93"/>
-      <c r="AP3" s="94"/>
-      <c r="AQ3" s="94"/>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="93"/>
-      <c r="AT3" s="93"/>
-      <c r="AU3" s="93"/>
-      <c r="AV3" s="94"/>
-      <c r="AW3" s="94"/>
-      <c r="AX3" s="94"/>
+        <v>412</v>
+      </c>
+      <c r="B3" s="91"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="93"/>
+      <c r="AF3" s="93"/>
+      <c r="AG3" s="92"/>
+      <c r="AH3" s="92"/>
+      <c r="AI3" s="92"/>
+      <c r="AJ3" s="93"/>
+      <c r="AK3" s="93"/>
+      <c r="AL3" s="93"/>
+      <c r="AM3" s="92"/>
+      <c r="AN3" s="92"/>
+      <c r="AO3" s="92"/>
+      <c r="AP3" s="93"/>
+      <c r="AQ3" s="93"/>
+      <c r="AR3" s="93"/>
+      <c r="AS3" s="92"/>
+      <c r="AT3" s="92"/>
+      <c r="AU3" s="92"/>
+      <c r="AV3" s="93"/>
+      <c r="AW3" s="93"/>
+      <c r="AX3" s="93"/>
     </row>
     <row r="4" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B5" s="91"/>
+      <c r="C5" s="94" t="s">
+        <v>414</v>
+      </c>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97" t="s">
         <v>415</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="95" t="s">
+      <c r="G5" s="98"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="94" t="s">
         <v>416</v>
       </c>
-      <c r="D5" s="96"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98" t="s">
+      <c r="J5" s="95"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="97" t="s">
         <v>417</v>
       </c>
-      <c r="G5" s="99"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="95" t="s">
+      <c r="M5" s="98"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="99" t="s">
         <v>418</v>
       </c>
-      <c r="J5" s="96"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="98" t="s">
+      <c r="P5" s="100"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="103" t="s">
         <v>419</v>
       </c>
-      <c r="M5" s="99"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="100" t="s">
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="104" t="s">
+        <v>419</v>
+      </c>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="103" t="s">
+        <v>419</v>
+      </c>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="99" t="s">
         <v>420</v>
       </c>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="104" t="s">
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="101"/>
+      <c r="AD5" s="105" t="s">
         <v>421</v>
       </c>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="105" t="s">
-        <v>421</v>
-      </c>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="104" t="s">
-        <v>421</v>
-      </c>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="100" t="s">
+      <c r="AE5" s="106"/>
+      <c r="AF5" s="107"/>
+      <c r="AG5" s="108" t="s">
         <v>422</v>
       </c>
-      <c r="AB5" s="101"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="106" t="s">
+      <c r="AH5" s="109"/>
+      <c r="AI5" s="110"/>
+      <c r="AJ5" s="105" t="s">
         <v>423</v>
       </c>
-      <c r="AE5" s="107"/>
-      <c r="AF5" s="108"/>
-      <c r="AG5" s="109" t="s">
+      <c r="AK5" s="106"/>
+      <c r="AL5" s="107"/>
+      <c r="AM5" s="108" t="s">
         <v>424</v>
       </c>
-      <c r="AH5" s="110"/>
-      <c r="AI5" s="111"/>
-      <c r="AJ5" s="106" t="s">
+      <c r="AN5" s="109"/>
+      <c r="AO5" s="110"/>
+      <c r="AP5" s="111"/>
+      <c r="AQ5" s="112" t="s">
         <v>425</v>
       </c>
-      <c r="AK5" s="107"/>
-      <c r="AL5" s="108"/>
-      <c r="AM5" s="109" t="s">
-        <v>426</v>
-      </c>
-      <c r="AN5" s="110"/>
-      <c r="AO5" s="111"/>
-      <c r="AP5" s="112"/>
-      <c r="AQ5" s="113" t="s">
-        <v>427</v>
-      </c>
-      <c r="AR5" s="112"/>
-      <c r="AS5" s="112"/>
-      <c r="AT5" s="114" t="s">
-        <v>427</v>
-      </c>
-      <c r="AU5" s="112"/>
-      <c r="AV5" s="112"/>
-      <c r="AW5" s="113" t="s">
-        <v>427</v>
-      </c>
-      <c r="AX5" s="112"/>
+      <c r="AR5" s="111"/>
+      <c r="AS5" s="111"/>
+      <c r="AT5" s="113" t="s">
+        <v>425</v>
+      </c>
+      <c r="AU5" s="111"/>
+      <c r="AV5" s="111"/>
+      <c r="AW5" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="AX5" s="111"/>
     </row>
     <row r="6" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B6" s="91"/>
+      <c r="C6" s="99" t="s">
+        <v>427</v>
+      </c>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="100"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="105" t="s">
         <v>428</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="100" t="s">
+      <c r="S6" s="106"/>
+      <c r="T6" s="106"/>
+      <c r="U6" s="100"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
+      <c r="X6" s="106"/>
+      <c r="Y6" s="106"/>
+      <c r="Z6" s="107"/>
+      <c r="AA6" s="99" t="s">
         <v>429</v>
       </c>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="101"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="107"/>
-      <c r="O6" s="101"/>
-      <c r="P6" s="101"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="106" t="s">
+      <c r="AB6" s="100"/>
+      <c r="AC6" s="100"/>
+      <c r="AD6" s="106"/>
+      <c r="AE6" s="106"/>
+      <c r="AF6" s="106"/>
+      <c r="AG6" s="100"/>
+      <c r="AH6" s="100"/>
+      <c r="AI6" s="100"/>
+      <c r="AJ6" s="106"/>
+      <c r="AK6" s="106"/>
+      <c r="AL6" s="106"/>
+      <c r="AM6" s="100"/>
+      <c r="AN6" s="100"/>
+      <c r="AO6" s="101"/>
+      <c r="AP6" s="105" t="s">
         <v>430</v>
       </c>
-      <c r="S6" s="107"/>
-      <c r="T6" s="107"/>
-      <c r="U6" s="101"/>
-      <c r="V6" s="101"/>
-      <c r="W6" s="101"/>
-      <c r="X6" s="107"/>
-      <c r="Y6" s="107"/>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="100" t="s">
-        <v>431</v>
-      </c>
-      <c r="AB6" s="101"/>
-      <c r="AC6" s="101"/>
-      <c r="AD6" s="107"/>
-      <c r="AE6" s="107"/>
-      <c r="AF6" s="107"/>
-      <c r="AG6" s="101"/>
-      <c r="AH6" s="101"/>
-      <c r="AI6" s="101"/>
-      <c r="AJ6" s="107"/>
-      <c r="AK6" s="107"/>
-      <c r="AL6" s="107"/>
-      <c r="AM6" s="101"/>
-      <c r="AN6" s="101"/>
-      <c r="AO6" s="102"/>
-      <c r="AP6" s="106" t="s">
-        <v>432</v>
-      </c>
-      <c r="AQ6" s="107"/>
-      <c r="AR6" s="107"/>
-      <c r="AS6" s="101"/>
-      <c r="AT6" s="101"/>
-      <c r="AU6" s="101"/>
-      <c r="AV6" s="107"/>
-      <c r="AW6" s="107"/>
-      <c r="AX6" s="108"/>
+      <c r="AQ6" s="106"/>
+      <c r="AR6" s="106"/>
+      <c r="AS6" s="100"/>
+      <c r="AT6" s="100"/>
+      <c r="AU6" s="100"/>
+      <c r="AV6" s="106"/>
+      <c r="AW6" s="106"/>
+      <c r="AX6" s="107"/>
     </row>
     <row r="7" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" s="97" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" s="95"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="94" t="s">
         <v>433</v>
       </c>
-      <c r="B7" s="98" t="s">
+      <c r="F7" s="98"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="97" t="s">
         <v>434</v>
       </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="95" t="s">
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="94" t="s">
         <v>435</v>
       </c>
-      <c r="F7" s="99"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="98" t="s">
+      <c r="L7" s="98"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="97" t="s">
         <v>436</v>
       </c>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="95" t="s">
+      <c r="O7" s="95"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="94" t="s">
         <v>437</v>
       </c>
-      <c r="L7" s="99"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="98" t="s">
+      <c r="R7" s="98"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="97" t="s">
         <v>438</v>
       </c>
-      <c r="O7" s="96"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="95" t="s">
+      <c r="U7" s="95"/>
+      <c r="V7" s="96"/>
+      <c r="W7" s="94" t="s">
         <v>439</v>
       </c>
-      <c r="R7" s="99"/>
-      <c r="S7" s="92"/>
-      <c r="T7" s="98" t="s">
+      <c r="X7" s="98"/>
+      <c r="Y7" s="91"/>
+      <c r="Z7" s="97" t="s">
+        <v>432</v>
+      </c>
+      <c r="AA7" s="100"/>
+      <c r="AB7" s="101"/>
+      <c r="AC7" s="100" t="s">
         <v>440</v>
       </c>
-      <c r="U7" s="96"/>
-      <c r="V7" s="97"/>
-      <c r="W7" s="95" t="s">
+      <c r="AD7" s="106"/>
+      <c r="AE7" s="107"/>
+      <c r="AF7" s="106" t="s">
         <v>441</v>
       </c>
-      <c r="X7" s="99"/>
-      <c r="Y7" s="92"/>
-      <c r="Z7" s="98" t="s">
-        <v>434</v>
-      </c>
-      <c r="AA7" s="101"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="101" t="s">
+      <c r="AG7" s="109"/>
+      <c r="AH7" s="110"/>
+      <c r="AI7" s="109" t="s">
         <v>442</v>
       </c>
-      <c r="AD7" s="107"/>
-      <c r="AE7" s="108"/>
-      <c r="AF7" s="107" t="s">
+      <c r="AJ7" s="106"/>
+      <c r="AK7" s="107"/>
+      <c r="AL7" s="106" t="s">
         <v>443</v>
       </c>
-      <c r="AG7" s="110"/>
-      <c r="AH7" s="111"/>
-      <c r="AI7" s="110" t="s">
+      <c r="AM7" s="109"/>
+      <c r="AN7" s="110"/>
+      <c r="AO7" s="109" t="s">
         <v>444</v>
       </c>
-      <c r="AJ7" s="107"/>
-      <c r="AK7" s="108"/>
-      <c r="AL7" s="107" t="s">
+      <c r="AP7" s="106"/>
+      <c r="AQ7" s="107"/>
+      <c r="AR7" s="106" t="s">
         <v>445</v>
       </c>
-      <c r="AM7" s="110"/>
-      <c r="AN7" s="111"/>
-      <c r="AO7" s="110" t="s">
+      <c r="AS7" s="109"/>
+      <c r="AT7" s="110"/>
+      <c r="AU7" s="109" t="s">
         <v>446</v>
       </c>
-      <c r="AP7" s="107"/>
-      <c r="AQ7" s="108"/>
-      <c r="AR7" s="107" t="s">
+      <c r="AV7" s="106"/>
+      <c r="AW7" s="107"/>
+      <c r="AX7" s="106" t="s">
         <v>447</v>
       </c>
-      <c r="AS7" s="110"/>
-      <c r="AT7" s="111"/>
-      <c r="AU7" s="110" t="s">
-        <v>448</v>
-      </c>
-      <c r="AV7" s="107"/>
-      <c r="AW7" s="108"/>
-      <c r="AX7" s="107" t="s">
-        <v>449</v>
-      </c>
     </row>
     <row r="8" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="99"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="96"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="99"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
-      <c r="AM8" s="96"/>
-      <c r="AN8" s="96"/>
-      <c r="AO8" s="96"/>
-      <c r="AP8" s="99"/>
-      <c r="AQ8" s="99"/>
-      <c r="AR8" s="99"/>
-      <c r="AS8" s="96"/>
-      <c r="AT8" s="96"/>
-      <c r="AU8" s="96"/>
-      <c r="AV8" s="99"/>
-      <c r="AW8" s="99"/>
+      <c r="O8" s="95"/>
+      <c r="P8" s="95"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="95"/>
+      <c r="W8" s="95"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AM8" s="95"/>
+      <c r="AN8" s="95"/>
+      <c r="AO8" s="95"/>
+      <c r="AP8" s="98"/>
+      <c r="AQ8" s="98"/>
+      <c r="AR8" s="98"/>
+      <c r="AS8" s="95"/>
+      <c r="AT8" s="95"/>
+      <c r="AU8" s="95"/>
+      <c r="AV8" s="98"/>
+      <c r="AW8" s="98"/>
     </row>
     <row r="9" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>450</v>
-      </c>
-      <c r="B9" s="115"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="119"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="116"/>
-      <c r="AB9" s="117"/>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="118"/>
-      <c r="AE9" s="118"/>
-      <c r="AF9" s="118"/>
-      <c r="AG9" s="117"/>
-      <c r="AH9" s="117"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="118"/>
-      <c r="AL9" s="119"/>
-      <c r="AW9" s="115"/>
+        <v>448</v>
+      </c>
+      <c r="B9" s="114"/>
+      <c r="C9" s="115"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="118"/>
+      <c r="Z9" s="114"/>
+      <c r="AA9" s="115"/>
+      <c r="AB9" s="116"/>
+      <c r="AC9" s="116"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="117"/>
+      <c r="AG9" s="116"/>
+      <c r="AH9" s="116"/>
+      <c r="AI9" s="116"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="118"/>
+      <c r="AW9" s="114"/>
     </row>
     <row r="11" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="118"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
     </row>
     <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="144" t="s">
-        <v>451</v>
-      </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="98" t="s">
+      <c r="A12" s="143" t="s">
+        <v>449</v>
+      </c>
+      <c r="B12" s="98"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="97" t="s">
+        <v>414</v>
+      </c>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="120"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="119"/>
+      <c r="S12" s="119"/>
+      <c r="T12" s="119"/>
+      <c r="U12" s="120"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="120"/>
+      <c r="X12" s="119"/>
+      <c r="Y12" s="119"/>
+      <c r="Z12" s="119"/>
+      <c r="AA12" s="120"/>
+      <c r="AB12" s="120"/>
+      <c r="AC12" s="121"/>
+      <c r="AD12" s="97" t="s">
+        <v>414</v>
+      </c>
+      <c r="AE12" s="98"/>
+      <c r="AF12" s="98"/>
+      <c r="AG12" s="95"/>
+      <c r="AH12" s="95"/>
+      <c r="AI12" s="95"/>
+      <c r="AJ12" s="119"/>
+      <c r="AK12" s="119"/>
+      <c r="AL12" s="119"/>
+      <c r="AM12" s="120"/>
+      <c r="AN12" s="120"/>
+      <c r="AO12" s="120"/>
+      <c r="AP12" s="119"/>
+      <c r="AQ12" s="119"/>
+      <c r="AR12" s="119"/>
+      <c r="AS12" s="120"/>
+      <c r="AT12" s="120"/>
+      <c r="AU12" s="120"/>
+      <c r="AV12" s="119"/>
+      <c r="AW12" s="119"/>
+      <c r="AX12" s="119"/>
+      <c r="AY12" s="120"/>
+      <c r="AZ12" s="120"/>
+      <c r="BA12" s="121"/>
+    </row>
+    <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="143"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="99" t="s">
+        <v>415</v>
+      </c>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="95"/>
+      <c r="P13" s="95"/>
+      <c r="Q13" s="95"/>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="95"/>
+      <c r="V13" s="95"/>
+      <c r="W13" s="95"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="98"/>
+      <c r="AA13" s="95"/>
+      <c r="AB13" s="95"/>
+      <c r="AC13" s="95"/>
+      <c r="AD13" s="98"/>
+      <c r="AE13" s="98"/>
+      <c r="AF13" s="91"/>
+      <c r="AG13" s="99" t="s">
+        <v>421</v>
+      </c>
+      <c r="AH13" s="100"/>
+      <c r="AI13" s="100"/>
+      <c r="AJ13" s="106"/>
+      <c r="AK13" s="106"/>
+      <c r="AL13" s="106"/>
+      <c r="AM13" s="100"/>
+      <c r="AN13" s="100"/>
+      <c r="AO13" s="100"/>
+      <c r="AP13" s="106"/>
+      <c r="AQ13" s="106"/>
+      <c r="AR13" s="106"/>
+      <c r="AS13" s="100"/>
+      <c r="AT13" s="100"/>
+      <c r="AU13" s="100"/>
+      <c r="AV13" s="106"/>
+      <c r="AW13" s="106"/>
+      <c r="AX13" s="106"/>
+      <c r="AY13" s="100"/>
+      <c r="AZ13" s="100"/>
+      <c r="BA13" s="100"/>
+      <c r="BB13" s="106"/>
+      <c r="BC13" s="106"/>
+      <c r="BD13" s="107"/>
+    </row>
+    <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="143"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="105" t="s">
         <v>416</v>
       </c>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="120"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="121"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="120"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="120"/>
-      <c r="U12" s="121"/>
-      <c r="V12" s="121"/>
-      <c r="W12" s="121"/>
-      <c r="X12" s="120"/>
-      <c r="Y12" s="120"/>
-      <c r="Z12" s="120"/>
-      <c r="AA12" s="121"/>
-      <c r="AB12" s="121"/>
-      <c r="AC12" s="122"/>
-      <c r="AD12" s="98" t="s">
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="100"/>
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="106"/>
+      <c r="S14" s="106"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="100"/>
+      <c r="X14" s="106"/>
+      <c r="Y14" s="106"/>
+      <c r="Z14" s="106"/>
+      <c r="AA14" s="100"/>
+      <c r="AB14" s="100"/>
+      <c r="AC14" s="100"/>
+      <c r="AD14" s="106"/>
+      <c r="AE14" s="106"/>
+      <c r="AF14" s="106"/>
+      <c r="AG14" s="100"/>
+      <c r="AH14" s="100"/>
+      <c r="AI14" s="101"/>
+      <c r="AJ14" s="105" t="s">
         <v>416</v>
       </c>
-      <c r="AE12" s="99"/>
-      <c r="AF12" s="99"/>
-      <c r="AG12" s="96"/>
-      <c r="AH12" s="96"/>
-      <c r="AI12" s="96"/>
-      <c r="AJ12" s="120"/>
-      <c r="AK12" s="120"/>
-      <c r="AL12" s="120"/>
-      <c r="AM12" s="121"/>
-      <c r="AN12" s="121"/>
-      <c r="AO12" s="121"/>
-      <c r="AP12" s="120"/>
-      <c r="AQ12" s="120"/>
-      <c r="AR12" s="120"/>
-      <c r="AS12" s="121"/>
-      <c r="AT12" s="121"/>
-      <c r="AU12" s="121"/>
-      <c r="AV12" s="120"/>
-      <c r="AW12" s="120"/>
-      <c r="AX12" s="120"/>
-      <c r="AY12" s="121"/>
-      <c r="AZ12" s="121"/>
-      <c r="BA12" s="122"/>
-    </row>
-    <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="144"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="92"/>
-      <c r="I13" s="100" t="s">
+      <c r="AK14" s="106"/>
+      <c r="AL14" s="106"/>
+      <c r="AM14" s="100"/>
+      <c r="AN14" s="100"/>
+      <c r="AO14" s="100"/>
+      <c r="AP14" s="106"/>
+      <c r="AQ14" s="106"/>
+      <c r="AR14" s="106"/>
+      <c r="AS14" s="100"/>
+      <c r="AT14" s="100"/>
+      <c r="AU14" s="100"/>
+      <c r="AV14" s="106"/>
+      <c r="AW14" s="106"/>
+      <c r="AX14" s="106"/>
+      <c r="AY14" s="100"/>
+      <c r="AZ14" s="100"/>
+      <c r="BA14" s="100"/>
+      <c r="BB14" s="106"/>
+      <c r="BC14" s="106"/>
+      <c r="BD14" s="106"/>
+      <c r="BE14" s="100"/>
+      <c r="BF14" s="100"/>
+      <c r="BG14" s="101"/>
+    </row>
+    <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="143"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="98"/>
+      <c r="O15" s="122" t="s">
         <v>417</v>
       </c>
-      <c r="J13" s="101"/>
-      <c r="K13" s="101"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="99"/>
-      <c r="S13" s="99"/>
-      <c r="T13" s="99"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="99"/>
-      <c r="Y13" s="99"/>
-      <c r="Z13" s="99"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="96"/>
-      <c r="AC13" s="96"/>
-      <c r="AD13" s="99"/>
-      <c r="AE13" s="99"/>
-      <c r="AF13" s="92"/>
-      <c r="AG13" s="100" t="s">
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="116"/>
+      <c r="V15" s="116"/>
+      <c r="W15" s="116"/>
+      <c r="X15" s="117"/>
+      <c r="Y15" s="117"/>
+      <c r="Z15" s="117"/>
+      <c r="AA15" s="116"/>
+      <c r="AB15" s="116"/>
+      <c r="AC15" s="116"/>
+      <c r="AD15" s="106"/>
+      <c r="AE15" s="106"/>
+      <c r="AF15" s="106"/>
+      <c r="AG15" s="100"/>
+      <c r="AH15" s="100"/>
+      <c r="AI15" s="100"/>
+      <c r="AJ15" s="106"/>
+      <c r="AK15" s="106"/>
+      <c r="AL15" s="107"/>
+      <c r="AM15" s="123" t="s">
         <v>423</v>
       </c>
-      <c r="AH13" s="101"/>
-      <c r="AI13" s="101"/>
-      <c r="AJ13" s="107"/>
-      <c r="AK13" s="107"/>
-      <c r="AL13" s="107"/>
-      <c r="AM13" s="101"/>
-      <c r="AN13" s="101"/>
-      <c r="AO13" s="101"/>
-      <c r="AP13" s="107"/>
-      <c r="AQ13" s="107"/>
-      <c r="AR13" s="107"/>
-      <c r="AS13" s="101"/>
-      <c r="AT13" s="101"/>
-      <c r="AU13" s="101"/>
-      <c r="AV13" s="107"/>
-      <c r="AW13" s="107"/>
-      <c r="AX13" s="107"/>
-      <c r="AY13" s="101"/>
-      <c r="AZ13" s="101"/>
-      <c r="BA13" s="101"/>
-      <c r="BB13" s="107"/>
-      <c r="BC13" s="107"/>
-      <c r="BD13" s="108"/>
-    </row>
-    <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="144"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="106" t="s">
-        <v>418</v>
-      </c>
-      <c r="M14" s="107"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="101"/>
-      <c r="P14" s="101"/>
-      <c r="Q14" s="101"/>
-      <c r="R14" s="107"/>
-      <c r="S14" s="107"/>
-      <c r="T14" s="107"/>
-      <c r="U14" s="101"/>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="107"/>
-      <c r="Y14" s="107"/>
-      <c r="Z14" s="107"/>
-      <c r="AA14" s="101"/>
-      <c r="AB14" s="101"/>
-      <c r="AC14" s="101"/>
-      <c r="AD14" s="107"/>
-      <c r="AE14" s="107"/>
-      <c r="AF14" s="107"/>
-      <c r="AG14" s="101"/>
-      <c r="AH14" s="101"/>
-      <c r="AI14" s="102"/>
-      <c r="AJ14" s="106" t="s">
-        <v>418</v>
-      </c>
-      <c r="AK14" s="107"/>
-      <c r="AL14" s="107"/>
-      <c r="AM14" s="101"/>
-      <c r="AN14" s="101"/>
-      <c r="AO14" s="101"/>
-      <c r="AP14" s="107"/>
-      <c r="AQ14" s="107"/>
-      <c r="AR14" s="107"/>
-      <c r="AS14" s="101"/>
-      <c r="AT14" s="101"/>
-      <c r="AU14" s="101"/>
-      <c r="AV14" s="107"/>
-      <c r="AW14" s="107"/>
-      <c r="AX14" s="107"/>
-      <c r="AY14" s="101"/>
-      <c r="AZ14" s="101"/>
-      <c r="BA14" s="101"/>
-      <c r="BB14" s="107"/>
-      <c r="BC14" s="107"/>
-      <c r="BD14" s="107"/>
-      <c r="BE14" s="101"/>
-      <c r="BF14" s="101"/>
-      <c r="BG14" s="102"/>
-    </row>
-    <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="144"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="99"/>
-      <c r="O15" s="123" t="s">
-        <v>419</v>
-      </c>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="118"/>
-      <c r="Y15" s="118"/>
-      <c r="Z15" s="118"/>
-      <c r="AA15" s="117"/>
-      <c r="AB15" s="117"/>
-      <c r="AC15" s="117"/>
-      <c r="AD15" s="107"/>
-      <c r="AE15" s="107"/>
-      <c r="AF15" s="107"/>
-      <c r="AG15" s="101"/>
-      <c r="AH15" s="101"/>
-      <c r="AI15" s="101"/>
-      <c r="AJ15" s="107"/>
-      <c r="AK15" s="107"/>
-      <c r="AL15" s="108"/>
-      <c r="AM15" s="124" t="s">
-        <v>425</v>
-      </c>
-      <c r="AN15" s="125"/>
-      <c r="AO15" s="125"/>
-      <c r="AP15" s="126"/>
-      <c r="AQ15" s="126"/>
-      <c r="AR15" s="126"/>
-      <c r="AS15" s="125"/>
-      <c r="AT15" s="125"/>
-      <c r="AU15" s="125"/>
-      <c r="AV15" s="126"/>
-      <c r="AW15" s="126"/>
-      <c r="AX15" s="126"/>
-      <c r="AY15" s="125"/>
-      <c r="AZ15" s="125"/>
-      <c r="BA15" s="125"/>
-      <c r="BB15" s="107"/>
-      <c r="BC15" s="107"/>
-      <c r="BD15" s="107"/>
-      <c r="BE15" s="101"/>
-      <c r="BF15" s="101"/>
-      <c r="BG15" s="101"/>
-      <c r="BH15" s="107"/>
-      <c r="BI15" s="107"/>
-      <c r="BJ15" s="108"/>
+      <c r="AN15" s="124"/>
+      <c r="AO15" s="124"/>
+      <c r="AP15" s="125"/>
+      <c r="AQ15" s="125"/>
+      <c r="AR15" s="125"/>
+      <c r="AS15" s="124"/>
+      <c r="AT15" s="124"/>
+      <c r="AU15" s="124"/>
+      <c r="AV15" s="125"/>
+      <c r="AW15" s="125"/>
+      <c r="AX15" s="125"/>
+      <c r="AY15" s="124"/>
+      <c r="AZ15" s="124"/>
+      <c r="BA15" s="124"/>
+      <c r="BB15" s="106"/>
+      <c r="BC15" s="106"/>
+      <c r="BD15" s="106"/>
+      <c r="BE15" s="100"/>
+      <c r="BF15" s="100"/>
+      <c r="BG15" s="100"/>
+      <c r="BH15" s="106"/>
+      <c r="BI15" s="106"/>
+      <c r="BJ15" s="107"/>
     </row>
     <row r="16" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>452</v>
-      </c>
-      <c r="M16" s="127"/>
-      <c r="N16" s="128"/>
-      <c r="O16" s="128"/>
-      <c r="P16" s="128"/>
-      <c r="Q16" s="129"/>
-      <c r="R16" s="98" t="s">
-        <v>420</v>
-      </c>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="96"/>
-      <c r="V16" s="96"/>
-      <c r="W16" s="96"/>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="99"/>
-      <c r="Z16" s="99"/>
-      <c r="AA16" s="96"/>
-      <c r="AB16" s="96"/>
-      <c r="AC16" s="96"/>
-      <c r="AD16" s="99"/>
-      <c r="AE16" s="99"/>
-      <c r="AF16" s="99"/>
-      <c r="AG16" s="96"/>
-      <c r="AH16" s="96"/>
-      <c r="AI16" s="96"/>
-      <c r="AJ16" s="92"/>
-      <c r="AK16" s="130"/>
-      <c r="AL16" s="131"/>
-      <c r="AM16" s="131"/>
-      <c r="AN16" s="131"/>
-      <c r="AO16" s="132"/>
-      <c r="AP16" s="106" t="s">
-        <v>426</v>
-      </c>
-      <c r="AQ16" s="107"/>
-      <c r="AR16" s="107"/>
-      <c r="AS16" s="101"/>
-      <c r="AT16" s="101"/>
-      <c r="AU16" s="101"/>
-      <c r="AV16" s="107"/>
-      <c r="AW16" s="107"/>
-      <c r="AX16" s="107"/>
+        <v>450</v>
+      </c>
+      <c r="M16" s="126"/>
+      <c r="N16" s="127"/>
+      <c r="O16" s="127"/>
+      <c r="P16" s="127"/>
+      <c r="Q16" s="128"/>
+      <c r="R16" s="97" t="s">
+        <v>418</v>
+      </c>
+      <c r="S16" s="98"/>
+      <c r="T16" s="98"/>
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="98"/>
+      <c r="AE16" s="98"/>
+      <c r="AF16" s="98"/>
+      <c r="AG16" s="95"/>
+      <c r="AH16" s="95"/>
+      <c r="AI16" s="95"/>
+      <c r="AJ16" s="91"/>
+      <c r="AK16" s="129"/>
+      <c r="AL16" s="130"/>
+      <c r="AM16" s="130"/>
+      <c r="AN16" s="130"/>
+      <c r="AO16" s="131"/>
+      <c r="AP16" s="105" t="s">
+        <v>424</v>
+      </c>
+      <c r="AQ16" s="106"/>
+      <c r="AR16" s="106"/>
+      <c r="AS16" s="100"/>
+      <c r="AT16" s="100"/>
+      <c r="AU16" s="100"/>
+      <c r="AV16" s="106"/>
+      <c r="AW16" s="106"/>
+      <c r="AX16" s="106"/>
     </row>
     <row r="17" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>453</v>
-      </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="128"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="128"/>
-      <c r="P17" s="128"/>
-      <c r="Q17" s="129"/>
-      <c r="R17" s="98" t="s">
-        <v>421</v>
-      </c>
-      <c r="S17" s="92"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="135"/>
-      <c r="V17" s="135"/>
-      <c r="W17" s="135"/>
-      <c r="X17" s="135"/>
-      <c r="Y17" s="135"/>
-      <c r="Z17" s="135"/>
-      <c r="AA17" s="135"/>
-      <c r="AB17" s="135"/>
-      <c r="AC17" s="135"/>
-      <c r="AD17" s="135"/>
-      <c r="AE17" s="135"/>
-      <c r="AF17" s="135"/>
-      <c r="AG17" s="135"/>
-      <c r="AH17" s="135"/>
-      <c r="AI17" s="135"/>
-      <c r="AJ17" s="135"/>
-      <c r="AK17" s="135"/>
-      <c r="AL17" s="135"/>
-      <c r="AM17" s="135"/>
-      <c r="AN17" s="135"/>
-      <c r="AO17" s="136"/>
-      <c r="AP17" s="106" t="s">
-        <v>427</v>
-      </c>
-      <c r="AQ17" s="108"/>
-      <c r="AR17" s="134"/>
-      <c r="AS17" s="135"/>
-      <c r="AT17" s="135"/>
-      <c r="AU17" s="135"/>
-      <c r="AV17" s="135"/>
-      <c r="AW17" s="135"/>
-      <c r="AX17" s="136"/>
+        <v>451</v>
+      </c>
+      <c r="B17" s="132"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="128"/>
+      <c r="R17" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="S17" s="91"/>
+      <c r="T17" s="133"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="134"/>
+      <c r="W17" s="134"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="134"/>
+      <c r="AE17" s="134"/>
+      <c r="AF17" s="134"/>
+      <c r="AG17" s="134"/>
+      <c r="AH17" s="134"/>
+      <c r="AI17" s="134"/>
+      <c r="AJ17" s="134"/>
+      <c r="AK17" s="134"/>
+      <c r="AL17" s="134"/>
+      <c r="AM17" s="134"/>
+      <c r="AN17" s="134"/>
+      <c r="AO17" s="135"/>
+      <c r="AP17" s="105" t="s">
+        <v>425</v>
+      </c>
+      <c r="AQ17" s="107"/>
+      <c r="AR17" s="133"/>
+      <c r="AS17" s="134"/>
+      <c r="AT17" s="134"/>
+      <c r="AU17" s="134"/>
+      <c r="AV17" s="134"/>
+      <c r="AW17" s="134"/>
+      <c r="AX17" s="135"/>
     </row>
     <row r="18" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>454</v>
-      </c>
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="128"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="128"/>
-      <c r="L18" s="128"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="128"/>
-      <c r="O18" s="128"/>
-      <c r="P18" s="128"/>
-      <c r="Q18" s="128"/>
-      <c r="R18" s="128"/>
-      <c r="S18" s="128"/>
-      <c r="T18" s="128"/>
-      <c r="U18" s="128"/>
-      <c r="V18" s="128"/>
-      <c r="W18" s="129"/>
-      <c r="X18" s="137" t="s">
-        <v>421</v>
-      </c>
-      <c r="Y18" s="119"/>
-      <c r="Z18" s="127"/>
-      <c r="AA18" s="128"/>
-      <c r="AB18" s="128"/>
-      <c r="AC18" s="128"/>
-      <c r="AD18" s="128"/>
-      <c r="AE18" s="128"/>
-      <c r="AF18" s="128"/>
-      <c r="AG18" s="128"/>
-      <c r="AH18" s="128"/>
-      <c r="AI18" s="128"/>
-      <c r="AJ18" s="128"/>
-      <c r="AK18" s="128"/>
-      <c r="AL18" s="128"/>
-      <c r="AM18" s="128"/>
-      <c r="AN18" s="128"/>
-      <c r="AO18" s="128"/>
-      <c r="AP18" s="128"/>
-      <c r="AQ18" s="128"/>
-      <c r="AR18" s="128"/>
-      <c r="AS18" s="128"/>
-      <c r="AT18" s="128"/>
-      <c r="AU18" s="129"/>
-      <c r="AV18" s="106" t="s">
-        <v>427</v>
-      </c>
-      <c r="AW18" s="108"/>
-      <c r="AX18" s="131"/>
-      <c r="AY18" s="131"/>
-      <c r="AZ18" s="131"/>
-      <c r="BA18" s="131"/>
-      <c r="BB18" s="131"/>
-      <c r="BC18" s="131"/>
-      <c r="BD18" s="131"/>
-      <c r="BE18" s="131"/>
-      <c r="BF18" s="131"/>
-      <c r="BG18" s="131"/>
-      <c r="BH18" s="131"/>
-      <c r="BI18" s="131"/>
-      <c r="BJ18" s="131"/>
-      <c r="BK18" s="131"/>
-      <c r="BL18" s="131"/>
-      <c r="BM18" s="131"/>
-      <c r="BN18" s="131"/>
-      <c r="BO18" s="131"/>
-      <c r="BP18" s="131"/>
-      <c r="BQ18" s="131"/>
-      <c r="BR18" s="131"/>
-      <c r="BS18" s="132"/>
+        <v>452</v>
+      </c>
+      <c r="B18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="127"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="127"/>
+      <c r="R18" s="127"/>
+      <c r="S18" s="127"/>
+      <c r="T18" s="127"/>
+      <c r="U18" s="127"/>
+      <c r="V18" s="127"/>
+      <c r="W18" s="128"/>
+      <c r="X18" s="136" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y18" s="118"/>
+      <c r="Z18" s="126"/>
+      <c r="AA18" s="127"/>
+      <c r="AB18" s="127"/>
+      <c r="AC18" s="127"/>
+      <c r="AD18" s="127"/>
+      <c r="AE18" s="127"/>
+      <c r="AF18" s="127"/>
+      <c r="AG18" s="127"/>
+      <c r="AH18" s="127"/>
+      <c r="AI18" s="127"/>
+      <c r="AJ18" s="127"/>
+      <c r="AK18" s="127"/>
+      <c r="AL18" s="127"/>
+      <c r="AM18" s="127"/>
+      <c r="AN18" s="127"/>
+      <c r="AO18" s="127"/>
+      <c r="AP18" s="127"/>
+      <c r="AQ18" s="127"/>
+      <c r="AR18" s="127"/>
+      <c r="AS18" s="127"/>
+      <c r="AT18" s="127"/>
+      <c r="AU18" s="128"/>
+      <c r="AV18" s="105" t="s">
+        <v>425</v>
+      </c>
+      <c r="AW18" s="107"/>
+      <c r="AX18" s="130"/>
+      <c r="AY18" s="130"/>
+      <c r="AZ18" s="130"/>
+      <c r="BA18" s="130"/>
+      <c r="BB18" s="130"/>
+      <c r="BC18" s="130"/>
+      <c r="BD18" s="130"/>
+      <c r="BE18" s="130"/>
+      <c r="BF18" s="130"/>
+      <c r="BG18" s="130"/>
+      <c r="BH18" s="130"/>
+      <c r="BI18" s="130"/>
+      <c r="BJ18" s="130"/>
+      <c r="BK18" s="130"/>
+      <c r="BL18" s="130"/>
+      <c r="BM18" s="130"/>
+      <c r="BN18" s="130"/>
+      <c r="BO18" s="130"/>
+      <c r="BP18" s="130"/>
+      <c r="BQ18" s="130"/>
+      <c r="BR18" s="130"/>
+      <c r="BS18" s="131"/>
     </row>
     <row r="19" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>455</v>
-      </c>
-      <c r="B19" s="127"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="128"/>
-      <c r="O19" s="128"/>
-      <c r="P19" s="128"/>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="128"/>
-      <c r="S19" s="128"/>
-      <c r="T19" s="129"/>
-      <c r="U19" s="116" t="s">
-        <v>421</v>
-      </c>
-      <c r="V19" s="138"/>
-      <c r="W19" s="127"/>
-      <c r="X19" s="128"/>
-      <c r="Y19" s="128"/>
-      <c r="Z19" s="128"/>
-      <c r="AA19" s="128"/>
-      <c r="AB19" s="128"/>
-      <c r="AC19" s="128"/>
-      <c r="AD19" s="128"/>
-      <c r="AE19" s="128"/>
-      <c r="AF19" s="128"/>
-      <c r="AG19" s="128"/>
-      <c r="AH19" s="128"/>
-      <c r="AI19" s="128"/>
-      <c r="AJ19" s="128"/>
-      <c r="AK19" s="128"/>
-      <c r="AL19" s="128"/>
-      <c r="AM19" s="128"/>
-      <c r="AN19" s="128"/>
-      <c r="AO19" s="128"/>
-      <c r="AP19" s="128"/>
-      <c r="AQ19" s="128"/>
-      <c r="AR19" s="129"/>
-      <c r="AS19" s="124" t="s">
-        <v>427</v>
-      </c>
-      <c r="AT19" s="139"/>
+        <v>453</v>
+      </c>
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="127"/>
+      <c r="K19" s="127"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="127"/>
+      <c r="P19" s="127"/>
+      <c r="Q19" s="127"/>
+      <c r="R19" s="127"/>
+      <c r="S19" s="127"/>
+      <c r="T19" s="128"/>
+      <c r="U19" s="115" t="s">
+        <v>419</v>
+      </c>
+      <c r="V19" s="137"/>
+      <c r="W19" s="126"/>
+      <c r="X19" s="127"/>
+      <c r="Y19" s="127"/>
+      <c r="Z19" s="127"/>
+      <c r="AA19" s="127"/>
+      <c r="AB19" s="127"/>
+      <c r="AC19" s="127"/>
+      <c r="AD19" s="127"/>
+      <c r="AE19" s="127"/>
+      <c r="AF19" s="127"/>
+      <c r="AG19" s="127"/>
+      <c r="AH19" s="127"/>
+      <c r="AI19" s="127"/>
+      <c r="AJ19" s="127"/>
+      <c r="AK19" s="127"/>
+      <c r="AL19" s="127"/>
+      <c r="AM19" s="127"/>
+      <c r="AN19" s="127"/>
+      <c r="AO19" s="127"/>
+      <c r="AP19" s="127"/>
+      <c r="AQ19" s="127"/>
+      <c r="AR19" s="128"/>
+      <c r="AS19" s="123" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT19" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangFPGA_pin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9AFCB7-F9E3-4ABA-B975-F52D20D8E9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC54DC1-D684-4516-A4BA-C41325417430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="0" windowWidth="12555" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TangPrimer25K (SLOT無し版)" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="459">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1832,6 +1832,14 @@
   </si>
   <si>
     <t>RESET_N</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom1_cs_n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srom2_cs_n</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2542,7 +2550,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2690,306 +2698,306 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="35" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3007,12 +3015,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4636,7 +4638,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="140" t="s">
+      <c r="AC9" s="145" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4697,7 +4699,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="140"/>
+      <c r="AC10" s="145"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -4760,7 +4762,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="140"/>
+      <c r="AC11" s="145"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -4821,7 +4823,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="140"/>
+      <c r="AC12" s="145"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -4886,7 +4888,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="140"/>
+      <c r="AC13" s="145"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -4955,7 +4957,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="140"/>
+      <c r="AC14" s="145"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -5466,7 +5468,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="140" t="s">
+      <c r="AC22" s="145" t="s">
         <v>244</v>
       </c>
     </row>
@@ -5529,7 +5531,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="140"/>
+      <c r="AC23" s="145"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -5590,7 +5592,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="140"/>
+      <c r="AC24" s="145"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -5649,7 +5651,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="140"/>
+      <c r="AC25" s="145"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -5712,7 +5714,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="140"/>
+      <c r="AC26" s="145"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -5773,7 +5775,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="140"/>
+      <c r="AC27" s="145"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -6657,7 +6659,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="140" t="s">
+      <c r="AC9" s="145" t="s">
         <v>245</v>
       </c>
     </row>
@@ -6726,7 +6728,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="140"/>
+      <c r="AC10" s="145"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -6793,7 +6795,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="140"/>
+      <c r="AC11" s="145"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -6860,7 +6862,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="140"/>
+      <c r="AC12" s="145"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -6929,7 +6931,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="140"/>
+      <c r="AC13" s="145"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -7002,7 +7004,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="140"/>
+      <c r="AC14" s="145"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -7559,7 +7561,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="140" t="s">
+      <c r="AC22" s="145" t="s">
         <v>244</v>
       </c>
     </row>
@@ -7626,7 +7628,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="140"/>
+      <c r="AC23" s="145"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -7691,7 +7693,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="140"/>
+      <c r="AC24" s="145"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -7754,7 +7756,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="140"/>
+      <c r="AC25" s="145"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -7817,7 +7819,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="140"/>
+      <c r="AC26" s="145"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -7882,7 +7884,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="140"/>
+      <c r="AC27" s="145"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -8011,7 +8013,7 @@
       <c r="AB29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AC29" s="142" t="s">
+      <c r="AC29" s="144" t="s">
         <v>243</v>
       </c>
     </row>
@@ -8082,7 +8084,7 @@
       <c r="AB30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC30" s="142"/>
+      <c r="AC30" s="144"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="21">
@@ -8147,7 +8149,7 @@
       <c r="AB31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC31" s="142"/>
+      <c r="AC31" s="144"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
@@ -8210,7 +8212,7 @@
       <c r="AB32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC32" s="142"/>
+      <c r="AC32" s="144"/>
     </row>
     <row r="33" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
@@ -8314,14 +8316,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="143" t="s">
+      <c r="B1" s="140" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -8375,10 +8377,10 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="H4" s="33"/>
       <c r="J4" s="8">
@@ -8412,12 +8414,12 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="19" t="s">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="51"/>
+      <c r="H5" s="50"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -8449,12 +8451,12 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19" t="s">
-        <v>219</v>
+        <v>331</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="51"/>
+        <v>210</v>
+      </c>
+      <c r="H6" s="50"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -8473,7 +8475,7 @@
       <c r="O6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="50"/>
+      <c r="P6" s="49"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B7" s="11">
@@ -8487,12 +8489,12 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="19" t="s">
-        <v>220</v>
+        <v>328</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="51"/>
+      <c r="H7" s="50"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -8511,7 +8513,9 @@
       <c r="O7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="53"/>
+      <c r="P7" s="52" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
@@ -8526,9 +8530,9 @@
       <c r="E8" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F8" s="52"/>
+      <c r="F8" s="51"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="51"/>
+      <c r="H8" s="50"/>
       <c r="J8" s="11">
         <v>36</v>
       </c>
@@ -8541,7 +8545,7 @@
       <c r="M8" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="N8" s="52"/>
+      <c r="N8" s="51"/>
       <c r="O8" s="12"/>
       <c r="P8" s="47"/>
     </row>
@@ -8559,12 +8563,12 @@
         <v>263</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>221</v>
+        <v>332</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="51"/>
+      <c r="H9" s="50"/>
       <c r="J9" s="11">
         <v>35</v>
       </c>
@@ -8577,9 +8581,9 @@
       <c r="M9" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="N9" s="52"/>
+      <c r="N9" s="51"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="51"/>
+      <c r="P9" s="50"/>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="11">
@@ -8595,12 +8599,12 @@
         <v>263</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>222</v>
+        <v>333</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="51"/>
+      <c r="H10" s="50"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -8619,7 +8623,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="142" t="s">
+      <c r="P10" s="144" t="s">
         <v>304</v>
       </c>
     </row>
@@ -8636,9 +8640,9 @@
       <c r="E11" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="52"/>
+      <c r="F11" s="51"/>
       <c r="G11" s="12"/>
-      <c r="H11" s="51"/>
+      <c r="H11" s="50"/>
       <c r="J11" s="11">
         <v>33</v>
       </c>
@@ -8657,7 +8661,7 @@
       <c r="O11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P11" s="142"/>
+      <c r="P11" s="144"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -8672,7 +8676,7 @@
       <c r="E12" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F12" s="52"/>
+      <c r="F12" s="51"/>
       <c r="G12" s="12"/>
       <c r="H12" s="33"/>
       <c r="J12" s="11">
@@ -8708,7 +8712,7 @@
       <c r="E13" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F13" s="52"/>
+      <c r="F13" s="51"/>
       <c r="G13" s="12"/>
       <c r="H13" s="33"/>
       <c r="J13" s="11">
@@ -8723,7 +8727,7 @@
       <c r="M13" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="N13" s="52"/>
+      <c r="N13" s="51"/>
       <c r="O13" s="12"/>
       <c r="P13" s="33"/>
     </row>
@@ -8740,7 +8744,7 @@
       <c r="E14" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F14" s="52"/>
+      <c r="F14" s="51"/>
       <c r="G14" s="12"/>
       <c r="H14" s="33"/>
       <c r="J14" s="11">
@@ -8778,7 +8782,7 @@
       <c r="E15" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F15" s="52"/>
+      <c r="F15" s="51"/>
       <c r="G15" s="12"/>
       <c r="H15" s="33"/>
       <c r="J15" s="11">
@@ -8793,9 +8797,9 @@
       <c r="M15" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="N15" s="52"/>
+      <c r="N15" s="51"/>
       <c r="O15" s="12"/>
-      <c r="P15" s="51"/>
+      <c r="P15" s="50"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
@@ -8810,7 +8814,7 @@
       <c r="E16" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F16" s="52"/>
+      <c r="F16" s="51"/>
       <c r="G16" s="12"/>
       <c r="H16" s="33"/>
       <c r="J16" s="11">
@@ -8823,9 +8827,15 @@
         <v>0</v>
       </c>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="51"/>
+      <c r="N16" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P16" s="52" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -8840,7 +8850,7 @@
       <c r="E17" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F17" s="52"/>
+      <c r="F17" s="51"/>
       <c r="G17" s="12"/>
       <c r="H17" s="33"/>
       <c r="J17" s="11">
@@ -8855,9 +8865,8 @@
       <c r="M17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N17" s="155"/>
+      <c r="N17" s="1"/>
       <c r="O17" s="12"/>
-      <c r="P17" s="156"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -8971,7 +8980,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="12"/>
-      <c r="P20" s="51"/>
+      <c r="P20" s="50"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B21" s="11">
@@ -9005,7 +9014,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="12"/>
-      <c r="P21" s="51"/>
+      <c r="P21" s="50"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -9119,15 +9128,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="143" t="s">
+      <c r="B1" s="140" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
@@ -9180,12 +9188,12 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="H4" s="140" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="145" t="s">
         <v>244</v>
       </c>
       <c r="J4" s="8">
@@ -9224,7 +9232,7 @@
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="140"/>
+      <c r="H5" s="145"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -9256,12 +9264,12 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="140"/>
+        <v>210</v>
+      </c>
+      <c r="H6" s="145"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -9280,7 +9288,7 @@
       <c r="O6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="50"/>
+      <c r="P6" s="49"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B7" s="11">
@@ -9294,12 +9302,12 @@
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="19" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="140"/>
+      <c r="H7" s="145"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -9313,12 +9321,12 @@
         <v>44</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>326</v>
+        <v>457</v>
       </c>
       <c r="O7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="53" t="s">
+      <c r="P7" s="52" t="s">
         <v>334</v>
       </c>
     </row>
@@ -9352,8 +9360,15 @@
         <v>4</v>
       </c>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="12"/>
+      <c r="N8" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P8" s="142" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B9" s="11">
@@ -9374,7 +9389,7 @@
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="140" t="s">
+      <c r="H9" s="145" t="s">
         <v>244</v>
       </c>
       <c r="J9" s="11">
@@ -9393,9 +9408,7 @@
       <c r="O9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P9" s="49" t="s">
-        <v>315</v>
-      </c>
+      <c r="P9" s="142"/>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="11">
@@ -9416,7 +9429,7 @@
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="140"/>
+      <c r="H10" s="145"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -9435,7 +9448,7 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="142" t="s">
+      <c r="P10" s="144" t="s">
         <v>304</v>
       </c>
     </row>
@@ -9456,7 +9469,7 @@
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="145" t="s">
+      <c r="H11" s="143" t="s">
         <v>314</v>
       </c>
       <c r="J11" s="11">
@@ -9477,7 +9490,7 @@
       <c r="O11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="142"/>
+      <c r="P11" s="144"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -9496,7 +9509,7 @@
       <c r="G12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="145"/>
+      <c r="H12" s="143"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -9534,7 +9547,7 @@
       <c r="G13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H13" s="145"/>
+      <c r="H13" s="143"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -9551,7 +9564,7 @@
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="142" t="s">
+      <c r="P13" s="144" t="s">
         <v>304</v>
       </c>
     </row>
@@ -9572,7 +9585,7 @@
       <c r="G14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="145"/>
+      <c r="H14" s="143"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -9591,7 +9604,7 @@
       <c r="O14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="142"/>
+      <c r="P14" s="144"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
@@ -9610,7 +9623,7 @@
       <c r="G15" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H15" s="145"/>
+      <c r="H15" s="143"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -9627,7 +9640,7 @@
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="145" t="s">
+      <c r="P15" s="139" t="s">
         <v>315</v>
       </c>
     </row>
@@ -9648,7 +9661,7 @@
       <c r="G16" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="145"/>
+      <c r="H16" s="143"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -9659,13 +9672,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="1"/>
-      <c r="N16" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="P16" s="145"/>
+      <c r="N16" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="O16" s="12"/>
+      <c r="P16" s="52" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -9684,7 +9697,7 @@
       <c r="G17" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H17" s="145"/>
+      <c r="H17" s="143"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -9697,9 +9710,8 @@
       <c r="M17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="N17" s="155"/>
+      <c r="N17" s="1"/>
       <c r="O17" s="12"/>
-      <c r="P17" s="156"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -9798,7 +9810,7 @@
         <v>231</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H20" s="141"/>
       <c r="J20" s="11">
@@ -9817,7 +9829,7 @@
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="144" t="s">
+      <c r="P20" s="142" t="s">
         <v>315</v>
       </c>
     </row>
@@ -9838,7 +9850,7 @@
         <v>232</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H21" s="141"/>
       <c r="J21" s="11">
@@ -9857,7 +9869,7 @@
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="144"/>
+      <c r="P21" s="142"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -9968,12 +9980,12 @@
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H18:H21"/>
     <mergeCell ref="P20:P21"/>
-    <mergeCell ref="P15:P16"/>
     <mergeCell ref="P13:P14"/>
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="H11:H17"/>
     <mergeCell ref="H9:H10"/>
+    <mergeCell ref="P8:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9987,428 +9999,428 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="3" customWidth="1"/>
-    <col min="3" max="3" width="3.5" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="9" style="54"/>
+    <col min="3" max="3" width="3.5" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="9" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C2" s="56"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="56" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="57">
         <v>0</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="58">
         <v>1</v>
       </c>
-      <c r="G2" s="59">
+      <c r="G2" s="58">
         <v>2</v>
       </c>
-      <c r="H2" s="59">
+      <c r="H2" s="58">
         <v>3</v>
       </c>
-      <c r="I2" s="59">
+      <c r="I2" s="58">
         <v>4</v>
       </c>
-      <c r="J2" s="59">
+      <c r="J2" s="58">
         <v>5</v>
       </c>
-      <c r="K2" s="59">
+      <c r="K2" s="58">
         <v>6</v>
       </c>
-      <c r="L2" s="57">
+      <c r="L2" s="56">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="60"/>
-      <c r="D3" s="61" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="60" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="61" t="s">
         <v>337</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="I3" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="63" t="s">
         <v>338</v>
       </c>
-      <c r="K3" s="64" t="s">
+      <c r="K3" s="63" t="s">
         <v>338</v>
       </c>
-      <c r="L3" s="65" t="s">
+      <c r="L3" s="64" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C4" s="66">
+      <c r="C4" s="65">
         <v>1</v>
       </c>
-      <c r="D4" s="67" t="s">
+      <c r="D4" s="66" t="s">
         <v>345</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="67" t="s">
         <v>353</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="68" t="s">
         <v>378</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="68" t="s">
         <v>388</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="68" t="s">
         <v>370</v>
       </c>
-      <c r="J4" s="69" t="s">
+      <c r="J4" s="68" t="s">
         <v>370</v>
       </c>
-      <c r="K4" s="69" t="s">
+      <c r="K4" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="L4" s="70" t="s">
+      <c r="L4" s="69" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C5" s="71">
+      <c r="C5" s="70">
         <v>2</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="72" t="s">
         <v>354</v>
       </c>
-      <c r="F5" s="74" t="s">
+      <c r="F5" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="H5" s="74" t="s">
+      <c r="H5" s="73" t="s">
         <v>389</v>
       </c>
-      <c r="I5" s="74" t="s">
+      <c r="I5" s="73" t="s">
         <v>377</v>
       </c>
-      <c r="J5" s="74" t="s">
+      <c r="J5" s="73" t="s">
         <v>377</v>
       </c>
-      <c r="K5" s="74" t="s">
+      <c r="K5" s="73" t="s">
         <v>397</v>
       </c>
-      <c r="L5" s="75" t="s">
+      <c r="L5" s="74" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C6" s="71">
+      <c r="C6" s="70">
         <v>3</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="71" t="s">
         <v>347</v>
       </c>
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="72" t="s">
         <v>355</v>
       </c>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="73" t="s">
         <v>363</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="73" t="s">
         <v>390</v>
       </c>
-      <c r="I6" s="74" t="s">
+      <c r="I6" s="73" t="s">
         <v>371</v>
       </c>
-      <c r="J6" s="74" t="s">
+      <c r="J6" s="73" t="s">
         <v>371</v>
       </c>
-      <c r="K6" s="74" t="s">
+      <c r="K6" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="L6" s="75" t="s">
+      <c r="L6" s="74" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C7" s="71">
+      <c r="C7" s="70">
         <v>4</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="71" t="s">
         <v>348</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="72" t="s">
         <v>356</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="73" t="s">
         <v>364</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="73" t="s">
         <v>383</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="73" t="s">
         <v>391</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="73" t="s">
         <v>372</v>
       </c>
-      <c r="J7" s="74" t="s">
+      <c r="J7" s="73" t="s">
         <v>372</v>
       </c>
-      <c r="K7" s="74" t="s">
+      <c r="K7" s="73" t="s">
         <v>455</v>
       </c>
-      <c r="L7" s="75" t="s">
+      <c r="L7" s="74" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C8" s="71">
+      <c r="C8" s="70">
         <v>5</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="71" t="s">
         <v>349</v>
       </c>
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="72" t="s">
         <v>357</v>
       </c>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="73" t="s">
         <v>365</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="73" t="s">
         <v>384</v>
       </c>
-      <c r="H8" s="74" t="s">
+      <c r="H8" s="73" t="s">
         <v>392</v>
       </c>
-      <c r="I8" s="74" t="s">
+      <c r="I8" s="73" t="s">
         <v>373</v>
       </c>
-      <c r="J8" s="74" t="s">
+      <c r="J8" s="73" t="s">
         <v>373</v>
       </c>
-      <c r="K8" s="74" t="s">
+      <c r="K8" s="73" t="s">
         <v>399</v>
       </c>
-      <c r="L8" s="75" t="s">
+      <c r="L8" s="74" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="9" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C9" s="71">
+      <c r="C9" s="70">
         <v>6</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="71" t="s">
         <v>350</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="72" t="s">
         <v>358</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F9" s="73" t="s">
         <v>366</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="73" t="s">
         <v>385</v>
       </c>
-      <c r="H9" s="74" t="s">
+      <c r="H9" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="I9" s="74" t="s">
+      <c r="I9" s="73" t="s">
         <v>374</v>
       </c>
-      <c r="J9" s="74" t="s">
+      <c r="J9" s="73" t="s">
         <v>374</v>
       </c>
-      <c r="K9" s="74" t="s">
+      <c r="K9" s="73" t="s">
         <v>400</v>
       </c>
-      <c r="L9" s="75" t="s">
+      <c r="L9" s="74" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="10" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C10" s="71">
+      <c r="C10" s="70">
         <v>7</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="71" t="s">
         <v>351</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="72" t="s">
         <v>359</v>
       </c>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="73" t="s">
         <v>367</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="73" t="s">
         <v>386</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="73" t="s">
         <v>394</v>
       </c>
-      <c r="I10" s="74" t="s">
+      <c r="I10" s="73" t="s">
         <v>375</v>
       </c>
-      <c r="J10" s="74" t="s">
+      <c r="J10" s="73" t="s">
         <v>375</v>
       </c>
-      <c r="K10" s="74" t="s">
+      <c r="K10" s="73" t="s">
         <v>401</v>
       </c>
-      <c r="L10" s="75" t="s">
+      <c r="L10" s="74" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="11" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="76">
+      <c r="C11" s="75">
         <v>8</v>
       </c>
-      <c r="D11" s="77" t="s">
+      <c r="D11" s="76" t="s">
         <v>352</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="77" t="s">
         <v>360</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="78" t="s">
         <v>368</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H11" s="79" t="s">
+      <c r="H11" s="78" t="s">
         <v>395</v>
       </c>
-      <c r="I11" s="79" t="s">
+      <c r="I11" s="78" t="s">
         <v>376</v>
       </c>
-      <c r="J11" s="79" t="s">
+      <c r="J11" s="78" t="s">
         <v>376</v>
       </c>
-      <c r="K11" s="79" t="s">
+      <c r="K11" s="78" t="s">
         <v>402</v>
       </c>
-      <c r="L11" s="80" t="s">
+      <c r="L11" s="79" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C12" s="56">
+      <c r="C12" s="55">
         <v>9</v>
       </c>
-      <c r="D12" s="81" t="s">
+      <c r="D12" s="80" t="s">
         <v>340</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="57">
         <v>0</v>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="58">
         <v>0</v>
       </c>
-      <c r="G12" s="59">
+      <c r="G12" s="58">
         <v>0</v>
       </c>
-      <c r="H12" s="59">
+      <c r="H12" s="58">
         <v>0</v>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="58">
         <v>1</v>
       </c>
-      <c r="J12" s="59">
+      <c r="J12" s="58">
         <v>1</v>
       </c>
-      <c r="K12" s="59">
+      <c r="K12" s="58">
         <v>1</v>
       </c>
-      <c r="L12" s="57">
+      <c r="L12" s="56">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="3:12" x14ac:dyDescent="0.15">
-      <c r="C13" s="71">
+      <c r="C13" s="70">
         <v>10</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="81" t="s">
         <v>341</v>
       </c>
-      <c r="E13" s="73">
+      <c r="E13" s="72">
         <v>0</v>
       </c>
-      <c r="F13" s="74">
+      <c r="F13" s="73">
         <v>0</v>
       </c>
-      <c r="G13" s="74">
+      <c r="G13" s="73">
         <v>1</v>
       </c>
-      <c r="H13" s="74">
+      <c r="H13" s="73">
         <v>1</v>
       </c>
-      <c r="I13" s="74">
+      <c r="I13" s="73">
         <v>0</v>
       </c>
-      <c r="J13" s="74">
+      <c r="J13" s="73">
         <v>0</v>
       </c>
-      <c r="K13" s="74">
+      <c r="K13" s="73">
         <v>1</v>
       </c>
-      <c r="L13" s="75">
+      <c r="L13" s="74">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="60">
+      <c r="C14" s="59">
         <v>11</v>
       </c>
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="E14" s="84">
+      <c r="E14" s="83">
         <v>0</v>
       </c>
-      <c r="F14" s="85">
+      <c r="F14" s="84">
         <v>1</v>
       </c>
-      <c r="G14" s="85">
+      <c r="G14" s="84">
         <v>0</v>
       </c>
-      <c r="H14" s="85">
+      <c r="H14" s="84">
         <v>1</v>
       </c>
-      <c r="I14" s="85">
+      <c r="I14" s="84">
         <v>0</v>
       </c>
-      <c r="J14" s="85">
+      <c r="J14" s="84">
         <v>1</v>
       </c>
-      <c r="K14" s="85">
+      <c r="K14" s="84">
         <v>0</v>
       </c>
-      <c r="L14" s="61">
+      <c r="L14" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="86">
+      <c r="C15" s="85">
         <v>12</v>
       </c>
-      <c r="D15" s="87" t="s">
+      <c r="D15" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E15" s="149" t="s">
@@ -10423,10 +10435,10 @@
       <c r="L15" s="151"/>
     </row>
     <row r="16" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="88">
+      <c r="C16" s="87">
         <v>13</v>
       </c>
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="88" t="s">
         <v>343</v>
       </c>
       <c r="E16" s="146" t="s">
@@ -10441,8 +10453,8 @@
       <c r="L16" s="148"/>
     </row>
     <row r="17" spans="3:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="88"/>
-      <c r="D17" s="55" t="s">
+      <c r="C17" s="87"/>
+      <c r="D17" s="54" t="s">
         <v>339</v>
       </c>
       <c r="E17" s="152" t="s">
@@ -10477,15 +10489,15 @@
   <sheetFormatPr defaultColWidth="4.25" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="4.25" style="90"/>
-    <col min="9" max="11" width="4.25" style="90"/>
-    <col min="15" max="17" width="4.25" style="90"/>
-    <col min="21" max="23" width="4.25" style="90"/>
+    <col min="3" max="5" width="4.25" style="89"/>
+    <col min="9" max="11" width="4.25" style="89"/>
+    <col min="15" max="17" width="4.25" style="89"/>
+    <col min="21" max="23" width="4.25" style="89"/>
     <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.25" style="90"/>
-    <col min="33" max="35" width="4.25" style="90"/>
-    <col min="39" max="41" width="4.25" style="90"/>
-    <col min="45" max="47" width="4.25" style="90"/>
+    <col min="27" max="29" width="4.25" style="89"/>
+    <col min="33" max="35" width="4.25" style="89"/>
+    <col min="39" max="41" width="4.25" style="89"/>
+    <col min="45" max="47" width="4.25" style="89"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.15">
@@ -10494,19 +10506,19 @@
       </c>
     </row>
     <row r="2" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="138" t="s">
         <v>454</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="90">
+      <c r="C2" s="89">
         <v>1</v>
       </c>
-      <c r="D2" s="90">
+      <c r="D2" s="89">
         <v>2</v>
       </c>
-      <c r="E2" s="90">
+      <c r="E2" s="89">
         <v>3</v>
       </c>
       <c r="F2">
@@ -10518,13 +10530,13 @@
       <c r="H2">
         <v>6</v>
       </c>
-      <c r="I2" s="90">
+      <c r="I2" s="89">
         <v>7</v>
       </c>
-      <c r="J2" s="90">
+      <c r="J2" s="89">
         <v>8</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="89">
         <v>9</v>
       </c>
       <c r="L2">
@@ -10536,13 +10548,13 @@
       <c r="N2">
         <v>12</v>
       </c>
-      <c r="O2" s="90">
+      <c r="O2" s="89">
         <v>13</v>
       </c>
-      <c r="P2" s="90">
+      <c r="P2" s="89">
         <v>14</v>
       </c>
-      <c r="Q2" s="90">
+      <c r="Q2" s="89">
         <v>15</v>
       </c>
       <c r="R2">
@@ -10554,13 +10566,13 @@
       <c r="T2">
         <v>18</v>
       </c>
-      <c r="U2" s="90">
+      <c r="U2" s="89">
         <v>19</v>
       </c>
-      <c r="V2" s="90">
+      <c r="V2" s="89">
         <v>20</v>
       </c>
-      <c r="W2" s="90">
+      <c r="W2" s="89">
         <v>21</v>
       </c>
       <c r="X2">
@@ -10577,845 +10589,845 @@
       <c r="A3" t="s">
         <v>412</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="92"/>
-      <c r="P3" s="92"/>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="93"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="93"/>
-      <c r="Y3" s="93"/>
-      <c r="Z3" s="93"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="93"/>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="92"/>
-      <c r="AH3" s="92"/>
-      <c r="AI3" s="92"/>
-      <c r="AJ3" s="93"/>
-      <c r="AK3" s="93"/>
-      <c r="AL3" s="93"/>
-      <c r="AM3" s="92"/>
-      <c r="AN3" s="92"/>
-      <c r="AO3" s="92"/>
-      <c r="AP3" s="93"/>
-      <c r="AQ3" s="93"/>
-      <c r="AR3" s="93"/>
-      <c r="AS3" s="92"/>
-      <c r="AT3" s="92"/>
-      <c r="AU3" s="92"/>
-      <c r="AV3" s="93"/>
-      <c r="AW3" s="93"/>
-      <c r="AX3" s="93"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="91"/>
+      <c r="V3" s="91"/>
+      <c r="W3" s="91"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="91"/>
+      <c r="AB3" s="91"/>
+      <c r="AC3" s="91"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="91"/>
+      <c r="AH3" s="91"/>
+      <c r="AI3" s="91"/>
+      <c r="AJ3" s="92"/>
+      <c r="AK3" s="92"/>
+      <c r="AL3" s="92"/>
+      <c r="AM3" s="91"/>
+      <c r="AN3" s="91"/>
+      <c r="AO3" s="91"/>
+      <c r="AP3" s="92"/>
+      <c r="AQ3" s="92"/>
+      <c r="AR3" s="92"/>
+      <c r="AS3" s="91"/>
+      <c r="AT3" s="91"/>
+      <c r="AU3" s="91"/>
+      <c r="AV3" s="92"/>
+      <c r="AW3" s="92"/>
+      <c r="AX3" s="92"/>
     </row>
     <row r="4" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>413</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="94" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="93" t="s">
         <v>414</v>
       </c>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97" t="s">
+      <c r="D5" s="94"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="96" t="s">
         <v>415</v>
       </c>
-      <c r="G5" s="98"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="94" t="s">
+      <c r="G5" s="97"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="93" t="s">
         <v>416</v>
       </c>
-      <c r="J5" s="95"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="97" t="s">
+      <c r="J5" s="94"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="96" t="s">
         <v>417</v>
       </c>
-      <c r="M5" s="98"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="99" t="s">
+      <c r="M5" s="97"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="98" t="s">
         <v>418</v>
       </c>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="103" t="s">
+      <c r="P5" s="99"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="102" t="s">
         <v>419</v>
       </c>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="104" t="s">
+      <c r="T5" s="101"/>
+      <c r="U5" s="101"/>
+      <c r="V5" s="103" t="s">
         <v>419</v>
       </c>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="103" t="s">
+      <c r="W5" s="101"/>
+      <c r="X5" s="101"/>
+      <c r="Y5" s="102" t="s">
         <v>419</v>
       </c>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="99" t="s">
+      <c r="Z5" s="101"/>
+      <c r="AA5" s="98" t="s">
         <v>420</v>
       </c>
-      <c r="AB5" s="100"/>
-      <c r="AC5" s="101"/>
-      <c r="AD5" s="105" t="s">
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="100"/>
+      <c r="AD5" s="104" t="s">
         <v>421</v>
       </c>
-      <c r="AE5" s="106"/>
-      <c r="AF5" s="107"/>
-      <c r="AG5" s="108" t="s">
+      <c r="AE5" s="105"/>
+      <c r="AF5" s="106"/>
+      <c r="AG5" s="107" t="s">
         <v>422</v>
       </c>
-      <c r="AH5" s="109"/>
-      <c r="AI5" s="110"/>
-      <c r="AJ5" s="105" t="s">
+      <c r="AH5" s="108"/>
+      <c r="AI5" s="109"/>
+      <c r="AJ5" s="104" t="s">
         <v>423</v>
       </c>
-      <c r="AK5" s="106"/>
-      <c r="AL5" s="107"/>
-      <c r="AM5" s="108" t="s">
+      <c r="AK5" s="105"/>
+      <c r="AL5" s="106"/>
+      <c r="AM5" s="107" t="s">
         <v>424</v>
       </c>
-      <c r="AN5" s="109"/>
-      <c r="AO5" s="110"/>
-      <c r="AP5" s="111"/>
-      <c r="AQ5" s="112" t="s">
+      <c r="AN5" s="108"/>
+      <c r="AO5" s="109"/>
+      <c r="AP5" s="110"/>
+      <c r="AQ5" s="111" t="s">
         <v>425</v>
       </c>
-      <c r="AR5" s="111"/>
-      <c r="AS5" s="111"/>
-      <c r="AT5" s="113" t="s">
+      <c r="AR5" s="110"/>
+      <c r="AS5" s="110"/>
+      <c r="AT5" s="112" t="s">
         <v>425</v>
       </c>
-      <c r="AU5" s="111"/>
-      <c r="AV5" s="111"/>
-      <c r="AW5" s="112" t="s">
+      <c r="AU5" s="110"/>
+      <c r="AV5" s="110"/>
+      <c r="AW5" s="111" t="s">
         <v>425</v>
       </c>
-      <c r="AX5" s="111"/>
+      <c r="AX5" s="110"/>
     </row>
     <row r="6" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>426</v>
       </c>
-      <c r="B6" s="91"/>
-      <c r="C6" s="99" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="98" t="s">
         <v>427</v>
       </c>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="100"/>
-      <c r="P6" s="100"/>
-      <c r="Q6" s="101"/>
-      <c r="R6" s="105" t="s">
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="104" t="s">
         <v>428</v>
       </c>
-      <c r="S6" s="106"/>
-      <c r="T6" s="106"/>
-      <c r="U6" s="100"/>
-      <c r="V6" s="100"/>
-      <c r="W6" s="100"/>
-      <c r="X6" s="106"/>
-      <c r="Y6" s="106"/>
-      <c r="Z6" s="107"/>
-      <c r="AA6" s="99" t="s">
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="99"/>
+      <c r="V6" s="99"/>
+      <c r="W6" s="99"/>
+      <c r="X6" s="105"/>
+      <c r="Y6" s="105"/>
+      <c r="Z6" s="106"/>
+      <c r="AA6" s="98" t="s">
         <v>429</v>
       </c>
-      <c r="AB6" s="100"/>
-      <c r="AC6" s="100"/>
-      <c r="AD6" s="106"/>
-      <c r="AE6" s="106"/>
-      <c r="AF6" s="106"/>
-      <c r="AG6" s="100"/>
-      <c r="AH6" s="100"/>
-      <c r="AI6" s="100"/>
-      <c r="AJ6" s="106"/>
-      <c r="AK6" s="106"/>
-      <c r="AL6" s="106"/>
-      <c r="AM6" s="100"/>
-      <c r="AN6" s="100"/>
-      <c r="AO6" s="101"/>
-      <c r="AP6" s="105" t="s">
+      <c r="AB6" s="99"/>
+      <c r="AC6" s="99"/>
+      <c r="AD6" s="105"/>
+      <c r="AE6" s="105"/>
+      <c r="AF6" s="105"/>
+      <c r="AG6" s="99"/>
+      <c r="AH6" s="99"/>
+      <c r="AI6" s="99"/>
+      <c r="AJ6" s="105"/>
+      <c r="AK6" s="105"/>
+      <c r="AL6" s="105"/>
+      <c r="AM6" s="99"/>
+      <c r="AN6" s="99"/>
+      <c r="AO6" s="100"/>
+      <c r="AP6" s="104" t="s">
         <v>430</v>
       </c>
-      <c r="AQ6" s="106"/>
-      <c r="AR6" s="106"/>
-      <c r="AS6" s="100"/>
-      <c r="AT6" s="100"/>
-      <c r="AU6" s="100"/>
-      <c r="AV6" s="106"/>
-      <c r="AW6" s="106"/>
-      <c r="AX6" s="107"/>
+      <c r="AQ6" s="105"/>
+      <c r="AR6" s="105"/>
+      <c r="AS6" s="99"/>
+      <c r="AT6" s="99"/>
+      <c r="AU6" s="99"/>
+      <c r="AV6" s="105"/>
+      <c r="AW6" s="105"/>
+      <c r="AX6" s="106"/>
     </row>
     <row r="7" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>431</v>
       </c>
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="96" t="s">
         <v>432</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="94" t="s">
+      <c r="C7" s="94"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="93" t="s">
         <v>433</v>
       </c>
-      <c r="F7" s="98"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="97" t="s">
+      <c r="F7" s="97"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="96" t="s">
         <v>434</v>
       </c>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="94" t="s">
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="93" t="s">
         <v>435</v>
       </c>
-      <c r="L7" s="98"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="97" t="s">
+      <c r="L7" s="97"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="96" t="s">
         <v>436</v>
       </c>
-      <c r="O7" s="95"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="94" t="s">
+      <c r="O7" s="94"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="93" t="s">
         <v>437</v>
       </c>
-      <c r="R7" s="98"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="97" t="s">
+      <c r="R7" s="97"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="96" t="s">
         <v>438</v>
       </c>
-      <c r="U7" s="95"/>
-      <c r="V7" s="96"/>
-      <c r="W7" s="94" t="s">
+      <c r="U7" s="94"/>
+      <c r="V7" s="95"/>
+      <c r="W7" s="93" t="s">
         <v>439</v>
       </c>
-      <c r="X7" s="98"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="97" t="s">
+      <c r="X7" s="97"/>
+      <c r="Y7" s="90"/>
+      <c r="Z7" s="96" t="s">
         <v>432</v>
       </c>
-      <c r="AA7" s="100"/>
-      <c r="AB7" s="101"/>
-      <c r="AC7" s="100" t="s">
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="100"/>
+      <c r="AC7" s="99" t="s">
         <v>440</v>
       </c>
-      <c r="AD7" s="106"/>
-      <c r="AE7" s="107"/>
-      <c r="AF7" s="106" t="s">
+      <c r="AD7" s="105"/>
+      <c r="AE7" s="106"/>
+      <c r="AF7" s="105" t="s">
         <v>441</v>
       </c>
-      <c r="AG7" s="109"/>
-      <c r="AH7" s="110"/>
-      <c r="AI7" s="109" t="s">
+      <c r="AG7" s="108"/>
+      <c r="AH7" s="109"/>
+      <c r="AI7" s="108" t="s">
         <v>442</v>
       </c>
-      <c r="AJ7" s="106"/>
-      <c r="AK7" s="107"/>
-      <c r="AL7" s="106" t="s">
+      <c r="AJ7" s="105"/>
+      <c r="AK7" s="106"/>
+      <c r="AL7" s="105" t="s">
         <v>443</v>
       </c>
-      <c r="AM7" s="109"/>
-      <c r="AN7" s="110"/>
-      <c r="AO7" s="109" t="s">
+      <c r="AM7" s="108"/>
+      <c r="AN7" s="109"/>
+      <c r="AO7" s="108" t="s">
         <v>444</v>
       </c>
-      <c r="AP7" s="106"/>
-      <c r="AQ7" s="107"/>
-      <c r="AR7" s="106" t="s">
+      <c r="AP7" s="105"/>
+      <c r="AQ7" s="106"/>
+      <c r="AR7" s="105" t="s">
         <v>445</v>
       </c>
-      <c r="AS7" s="109"/>
-      <c r="AT7" s="110"/>
-      <c r="AU7" s="109" t="s">
+      <c r="AS7" s="108"/>
+      <c r="AT7" s="109"/>
+      <c r="AU7" s="108" t="s">
         <v>446</v>
       </c>
-      <c r="AV7" s="106"/>
-      <c r="AW7" s="107"/>
-      <c r="AX7" s="106" t="s">
+      <c r="AV7" s="105"/>
+      <c r="AW7" s="106"/>
+      <c r="AX7" s="105" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="O8" s="95"/>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="98"/>
-      <c r="U8" s="95"/>
-      <c r="V8" s="95"/>
-      <c r="W8" s="95"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="98"/>
-      <c r="Z8" s="98"/>
-      <c r="AM8" s="95"/>
-      <c r="AN8" s="95"/>
-      <c r="AO8" s="95"/>
-      <c r="AP8" s="98"/>
-      <c r="AQ8" s="98"/>
-      <c r="AR8" s="98"/>
-      <c r="AS8" s="95"/>
-      <c r="AT8" s="95"/>
-      <c r="AU8" s="95"/>
-      <c r="AV8" s="98"/>
-      <c r="AW8" s="98"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="94"/>
+      <c r="R8" s="97"/>
+      <c r="S8" s="97"/>
+      <c r="T8" s="97"/>
+      <c r="U8" s="94"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="94"/>
+      <c r="X8" s="97"/>
+      <c r="Y8" s="97"/>
+      <c r="Z8" s="97"/>
+      <c r="AM8" s="94"/>
+      <c r="AN8" s="94"/>
+      <c r="AO8" s="94"/>
+      <c r="AP8" s="97"/>
+      <c r="AQ8" s="97"/>
+      <c r="AR8" s="97"/>
+      <c r="AS8" s="94"/>
+      <c r="AT8" s="94"/>
+      <c r="AU8" s="94"/>
+      <c r="AV8" s="97"/>
+      <c r="AW8" s="97"/>
     </row>
     <row r="9" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>448</v>
       </c>
-      <c r="B9" s="114"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="116"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="118"/>
-      <c r="Z9" s="114"/>
-      <c r="AA9" s="115"/>
-      <c r="AB9" s="116"/>
-      <c r="AC9" s="116"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="117"/>
-      <c r="AF9" s="117"/>
-      <c r="AG9" s="116"/>
-      <c r="AH9" s="116"/>
-      <c r="AI9" s="116"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="118"/>
-      <c r="AW9" s="114"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="116"/>
+      <c r="N9" s="117"/>
+      <c r="Z9" s="113"/>
+      <c r="AA9" s="114"/>
+      <c r="AB9" s="115"/>
+      <c r="AC9" s="115"/>
+      <c r="AD9" s="116"/>
+      <c r="AE9" s="116"/>
+      <c r="AF9" s="116"/>
+      <c r="AG9" s="115"/>
+      <c r="AH9" s="115"/>
+      <c r="AI9" s="115"/>
+      <c r="AJ9" s="116"/>
+      <c r="AK9" s="116"/>
+      <c r="AL9" s="117"/>
+      <c r="AW9" s="113"/>
     </row>
     <row r="11" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="117"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
     </row>
     <row r="12" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="143" t="s">
+      <c r="A12" s="140" t="s">
         <v>449</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="97" t="s">
+      <c r="B12" s="97"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="96" t="s">
         <v>414</v>
       </c>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="119"/>
-      <c r="M12" s="119"/>
-      <c r="N12" s="119"/>
-      <c r="O12" s="120"/>
-      <c r="P12" s="120"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="119"/>
-      <c r="S12" s="119"/>
-      <c r="T12" s="119"/>
-      <c r="U12" s="120"/>
-      <c r="V12" s="120"/>
-      <c r="W12" s="120"/>
-      <c r="X12" s="119"/>
-      <c r="Y12" s="119"/>
-      <c r="Z12" s="119"/>
-      <c r="AA12" s="120"/>
-      <c r="AB12" s="120"/>
-      <c r="AC12" s="121"/>
-      <c r="AD12" s="97" t="s">
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="119"/>
+      <c r="Q12" s="119"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="118"/>
+      <c r="U12" s="119"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="119"/>
+      <c r="X12" s="118"/>
+      <c r="Y12" s="118"/>
+      <c r="Z12" s="118"/>
+      <c r="AA12" s="119"/>
+      <c r="AB12" s="119"/>
+      <c r="AC12" s="120"/>
+      <c r="AD12" s="96" t="s">
         <v>414</v>
       </c>
-      <c r="AE12" s="98"/>
-      <c r="AF12" s="98"/>
-      <c r="AG12" s="95"/>
-      <c r="AH12" s="95"/>
-      <c r="AI12" s="95"/>
-      <c r="AJ12" s="119"/>
-      <c r="AK12" s="119"/>
-      <c r="AL12" s="119"/>
-      <c r="AM12" s="120"/>
-      <c r="AN12" s="120"/>
-      <c r="AO12" s="120"/>
-      <c r="AP12" s="119"/>
-      <c r="AQ12" s="119"/>
-      <c r="AR12" s="119"/>
-      <c r="AS12" s="120"/>
-      <c r="AT12" s="120"/>
-      <c r="AU12" s="120"/>
-      <c r="AV12" s="119"/>
-      <c r="AW12" s="119"/>
-      <c r="AX12" s="119"/>
-      <c r="AY12" s="120"/>
-      <c r="AZ12" s="120"/>
-      <c r="BA12" s="121"/>
+      <c r="AE12" s="97"/>
+      <c r="AF12" s="97"/>
+      <c r="AG12" s="94"/>
+      <c r="AH12" s="94"/>
+      <c r="AI12" s="94"/>
+      <c r="AJ12" s="118"/>
+      <c r="AK12" s="118"/>
+      <c r="AL12" s="118"/>
+      <c r="AM12" s="119"/>
+      <c r="AN12" s="119"/>
+      <c r="AO12" s="119"/>
+      <c r="AP12" s="118"/>
+      <c r="AQ12" s="118"/>
+      <c r="AR12" s="118"/>
+      <c r="AS12" s="119"/>
+      <c r="AT12" s="119"/>
+      <c r="AU12" s="119"/>
+      <c r="AV12" s="118"/>
+      <c r="AW12" s="118"/>
+      <c r="AX12" s="118"/>
+      <c r="AY12" s="119"/>
+      <c r="AZ12" s="119"/>
+      <c r="BA12" s="120"/>
     </row>
     <row r="13" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="143"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="99" t="s">
+      <c r="A13" s="140"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="98" t="s">
         <v>415</v>
       </c>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="98"/>
-      <c r="O13" s="95"/>
-      <c r="P13" s="95"/>
-      <c r="Q13" s="95"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="95"/>
-      <c r="V13" s="95"/>
-      <c r="W13" s="95"/>
-      <c r="X13" s="98"/>
-      <c r="Y13" s="98"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="95"/>
-      <c r="AB13" s="95"/>
-      <c r="AC13" s="95"/>
-      <c r="AD13" s="98"/>
-      <c r="AE13" s="98"/>
-      <c r="AF13" s="91"/>
-      <c r="AG13" s="99" t="s">
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="97"/>
+      <c r="S13" s="97"/>
+      <c r="T13" s="97"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="97"/>
+      <c r="Y13" s="97"/>
+      <c r="Z13" s="97"/>
+      <c r="AA13" s="94"/>
+      <c r="AB13" s="94"/>
+      <c r="AC13" s="94"/>
+      <c r="AD13" s="97"/>
+      <c r="AE13" s="97"/>
+      <c r="AF13" s="90"/>
+      <c r="AG13" s="98" t="s">
         <v>421</v>
       </c>
-      <c r="AH13" s="100"/>
-      <c r="AI13" s="100"/>
-      <c r="AJ13" s="106"/>
-      <c r="AK13" s="106"/>
-      <c r="AL13" s="106"/>
-      <c r="AM13" s="100"/>
-      <c r="AN13" s="100"/>
-      <c r="AO13" s="100"/>
-      <c r="AP13" s="106"/>
-      <c r="AQ13" s="106"/>
-      <c r="AR13" s="106"/>
-      <c r="AS13" s="100"/>
-      <c r="AT13" s="100"/>
-      <c r="AU13" s="100"/>
-      <c r="AV13" s="106"/>
-      <c r="AW13" s="106"/>
-      <c r="AX13" s="106"/>
-      <c r="AY13" s="100"/>
-      <c r="AZ13" s="100"/>
-      <c r="BA13" s="100"/>
-      <c r="BB13" s="106"/>
-      <c r="BC13" s="106"/>
-      <c r="BD13" s="107"/>
+      <c r="AH13" s="99"/>
+      <c r="AI13" s="99"/>
+      <c r="AJ13" s="105"/>
+      <c r="AK13" s="105"/>
+      <c r="AL13" s="105"/>
+      <c r="AM13" s="99"/>
+      <c r="AN13" s="99"/>
+      <c r="AO13" s="99"/>
+      <c r="AP13" s="105"/>
+      <c r="AQ13" s="105"/>
+      <c r="AR13" s="105"/>
+      <c r="AS13" s="99"/>
+      <c r="AT13" s="99"/>
+      <c r="AU13" s="99"/>
+      <c r="AV13" s="105"/>
+      <c r="AW13" s="105"/>
+      <c r="AX13" s="105"/>
+      <c r="AY13" s="99"/>
+      <c r="AZ13" s="99"/>
+      <c r="BA13" s="99"/>
+      <c r="BB13" s="105"/>
+      <c r="BC13" s="105"/>
+      <c r="BD13" s="106"/>
     </row>
     <row r="14" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="143"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="105" t="s">
+      <c r="A14" s="140"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="104" t="s">
         <v>416</v>
       </c>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="100"/>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
-      <c r="R14" s="106"/>
-      <c r="S14" s="106"/>
-      <c r="T14" s="106"/>
-      <c r="U14" s="100"/>
-      <c r="V14" s="100"/>
-      <c r="W14" s="100"/>
-      <c r="X14" s="106"/>
-      <c r="Y14" s="106"/>
-      <c r="Z14" s="106"/>
-      <c r="AA14" s="100"/>
-      <c r="AB14" s="100"/>
-      <c r="AC14" s="100"/>
-      <c r="AD14" s="106"/>
-      <c r="AE14" s="106"/>
-      <c r="AF14" s="106"/>
-      <c r="AG14" s="100"/>
-      <c r="AH14" s="100"/>
-      <c r="AI14" s="101"/>
-      <c r="AJ14" s="105" t="s">
+      <c r="M14" s="105"/>
+      <c r="N14" s="105"/>
+      <c r="O14" s="99"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="105"/>
+      <c r="S14" s="105"/>
+      <c r="T14" s="105"/>
+      <c r="U14" s="99"/>
+      <c r="V14" s="99"/>
+      <c r="W14" s="99"/>
+      <c r="X14" s="105"/>
+      <c r="Y14" s="105"/>
+      <c r="Z14" s="105"/>
+      <c r="AA14" s="99"/>
+      <c r="AB14" s="99"/>
+      <c r="AC14" s="99"/>
+      <c r="AD14" s="105"/>
+      <c r="AE14" s="105"/>
+      <c r="AF14" s="105"/>
+      <c r="AG14" s="99"/>
+      <c r="AH14" s="99"/>
+      <c r="AI14" s="100"/>
+      <c r="AJ14" s="104" t="s">
         <v>416</v>
       </c>
-      <c r="AK14" s="106"/>
-      <c r="AL14" s="106"/>
-      <c r="AM14" s="100"/>
-      <c r="AN14" s="100"/>
-      <c r="AO14" s="100"/>
-      <c r="AP14" s="106"/>
-      <c r="AQ14" s="106"/>
-      <c r="AR14" s="106"/>
-      <c r="AS14" s="100"/>
-      <c r="AT14" s="100"/>
-      <c r="AU14" s="100"/>
-      <c r="AV14" s="106"/>
-      <c r="AW14" s="106"/>
-      <c r="AX14" s="106"/>
-      <c r="AY14" s="100"/>
-      <c r="AZ14" s="100"/>
-      <c r="BA14" s="100"/>
-      <c r="BB14" s="106"/>
-      <c r="BC14" s="106"/>
-      <c r="BD14" s="106"/>
-      <c r="BE14" s="100"/>
-      <c r="BF14" s="100"/>
-      <c r="BG14" s="101"/>
+      <c r="AK14" s="105"/>
+      <c r="AL14" s="105"/>
+      <c r="AM14" s="99"/>
+      <c r="AN14" s="99"/>
+      <c r="AO14" s="99"/>
+      <c r="AP14" s="105"/>
+      <c r="AQ14" s="105"/>
+      <c r="AR14" s="105"/>
+      <c r="AS14" s="99"/>
+      <c r="AT14" s="99"/>
+      <c r="AU14" s="99"/>
+      <c r="AV14" s="105"/>
+      <c r="AW14" s="105"/>
+      <c r="AX14" s="105"/>
+      <c r="AY14" s="99"/>
+      <c r="AZ14" s="99"/>
+      <c r="BA14" s="99"/>
+      <c r="BB14" s="105"/>
+      <c r="BC14" s="105"/>
+      <c r="BD14" s="105"/>
+      <c r="BE14" s="99"/>
+      <c r="BF14" s="99"/>
+      <c r="BG14" s="100"/>
     </row>
     <row r="15" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="143"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="98"/>
-      <c r="O15" s="122" t="s">
+      <c r="A15" s="140"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="97"/>
+      <c r="O15" s="121" t="s">
         <v>417</v>
       </c>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="116"/>
-      <c r="V15" s="116"/>
-      <c r="W15" s="116"/>
-      <c r="X15" s="117"/>
-      <c r="Y15" s="117"/>
-      <c r="Z15" s="117"/>
-      <c r="AA15" s="116"/>
-      <c r="AB15" s="116"/>
-      <c r="AC15" s="116"/>
-      <c r="AD15" s="106"/>
-      <c r="AE15" s="106"/>
-      <c r="AF15" s="106"/>
-      <c r="AG15" s="100"/>
-      <c r="AH15" s="100"/>
-      <c r="AI15" s="100"/>
-      <c r="AJ15" s="106"/>
-      <c r="AK15" s="106"/>
-      <c r="AL15" s="107"/>
-      <c r="AM15" s="123" t="s">
+      <c r="R15" s="116"/>
+      <c r="S15" s="116"/>
+      <c r="T15" s="116"/>
+      <c r="U15" s="115"/>
+      <c r="V15" s="115"/>
+      <c r="W15" s="115"/>
+      <c r="X15" s="116"/>
+      <c r="Y15" s="116"/>
+      <c r="Z15" s="116"/>
+      <c r="AA15" s="115"/>
+      <c r="AB15" s="115"/>
+      <c r="AC15" s="115"/>
+      <c r="AD15" s="105"/>
+      <c r="AE15" s="105"/>
+      <c r="AF15" s="105"/>
+      <c r="AG15" s="99"/>
+      <c r="AH15" s="99"/>
+      <c r="AI15" s="99"/>
+      <c r="AJ15" s="105"/>
+      <c r="AK15" s="105"/>
+      <c r="AL15" s="106"/>
+      <c r="AM15" s="122" t="s">
         <v>423</v>
       </c>
-      <c r="AN15" s="124"/>
-      <c r="AO15" s="124"/>
-      <c r="AP15" s="125"/>
-      <c r="AQ15" s="125"/>
-      <c r="AR15" s="125"/>
-      <c r="AS15" s="124"/>
-      <c r="AT15" s="124"/>
-      <c r="AU15" s="124"/>
-      <c r="AV15" s="125"/>
-      <c r="AW15" s="125"/>
-      <c r="AX15" s="125"/>
-      <c r="AY15" s="124"/>
-      <c r="AZ15" s="124"/>
-      <c r="BA15" s="124"/>
-      <c r="BB15" s="106"/>
-      <c r="BC15" s="106"/>
-      <c r="BD15" s="106"/>
-      <c r="BE15" s="100"/>
-      <c r="BF15" s="100"/>
-      <c r="BG15" s="100"/>
-      <c r="BH15" s="106"/>
-      <c r="BI15" s="106"/>
-      <c r="BJ15" s="107"/>
+      <c r="AN15" s="123"/>
+      <c r="AO15" s="123"/>
+      <c r="AP15" s="124"/>
+      <c r="AQ15" s="124"/>
+      <c r="AR15" s="124"/>
+      <c r="AS15" s="123"/>
+      <c r="AT15" s="123"/>
+      <c r="AU15" s="123"/>
+      <c r="AV15" s="124"/>
+      <c r="AW15" s="124"/>
+      <c r="AX15" s="124"/>
+      <c r="AY15" s="123"/>
+      <c r="AZ15" s="123"/>
+      <c r="BA15" s="123"/>
+      <c r="BB15" s="105"/>
+      <c r="BC15" s="105"/>
+      <c r="BD15" s="105"/>
+      <c r="BE15" s="99"/>
+      <c r="BF15" s="99"/>
+      <c r="BG15" s="99"/>
+      <c r="BH15" s="105"/>
+      <c r="BI15" s="105"/>
+      <c r="BJ15" s="106"/>
     </row>
     <row r="16" spans="1:62" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>450</v>
       </c>
-      <c r="M16" s="126"/>
-      <c r="N16" s="127"/>
-      <c r="O16" s="127"/>
-      <c r="P16" s="127"/>
-      <c r="Q16" s="128"/>
-      <c r="R16" s="97" t="s">
+      <c r="M16" s="125"/>
+      <c r="N16" s="126"/>
+      <c r="O16" s="126"/>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="127"/>
+      <c r="R16" s="96" t="s">
         <v>418</v>
       </c>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="95"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="95"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
-      <c r="AA16" s="95"/>
-      <c r="AB16" s="95"/>
-      <c r="AC16" s="95"/>
-      <c r="AD16" s="98"/>
-      <c r="AE16" s="98"/>
-      <c r="AF16" s="98"/>
-      <c r="AG16" s="95"/>
-      <c r="AH16" s="95"/>
-      <c r="AI16" s="95"/>
-      <c r="AJ16" s="91"/>
-      <c r="AK16" s="129"/>
-      <c r="AL16" s="130"/>
-      <c r="AM16" s="130"/>
-      <c r="AN16" s="130"/>
-      <c r="AO16" s="131"/>
-      <c r="AP16" s="105" t="s">
+      <c r="S16" s="97"/>
+      <c r="T16" s="97"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="94"/>
+      <c r="W16" s="94"/>
+      <c r="X16" s="97"/>
+      <c r="Y16" s="97"/>
+      <c r="Z16" s="97"/>
+      <c r="AA16" s="94"/>
+      <c r="AB16" s="94"/>
+      <c r="AC16" s="94"/>
+      <c r="AD16" s="97"/>
+      <c r="AE16" s="97"/>
+      <c r="AF16" s="97"/>
+      <c r="AG16" s="94"/>
+      <c r="AH16" s="94"/>
+      <c r="AI16" s="94"/>
+      <c r="AJ16" s="90"/>
+      <c r="AK16" s="128"/>
+      <c r="AL16" s="129"/>
+      <c r="AM16" s="129"/>
+      <c r="AN16" s="129"/>
+      <c r="AO16" s="130"/>
+      <c r="AP16" s="104" t="s">
         <v>424</v>
       </c>
-      <c r="AQ16" s="106"/>
-      <c r="AR16" s="106"/>
-      <c r="AS16" s="100"/>
-      <c r="AT16" s="100"/>
-      <c r="AU16" s="100"/>
-      <c r="AV16" s="106"/>
-      <c r="AW16" s="106"/>
-      <c r="AX16" s="106"/>
+      <c r="AQ16" s="105"/>
+      <c r="AR16" s="105"/>
+      <c r="AS16" s="99"/>
+      <c r="AT16" s="99"/>
+      <c r="AU16" s="99"/>
+      <c r="AV16" s="105"/>
+      <c r="AW16" s="105"/>
+      <c r="AX16" s="105"/>
     </row>
     <row r="17" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>451</v>
       </c>
-      <c r="B17" s="132"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="128"/>
-      <c r="R17" s="97" t="s">
+      <c r="B17" s="131"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="96" t="s">
         <v>419</v>
       </c>
-      <c r="S17" s="91"/>
-      <c r="T17" s="133"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="134"/>
-      <c r="W17" s="134"/>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="134"/>
-      <c r="AE17" s="134"/>
-      <c r="AF17" s="134"/>
-      <c r="AG17" s="134"/>
-      <c r="AH17" s="134"/>
-      <c r="AI17" s="134"/>
-      <c r="AJ17" s="134"/>
-      <c r="AK17" s="134"/>
-      <c r="AL17" s="134"/>
-      <c r="AM17" s="134"/>
-      <c r="AN17" s="134"/>
-      <c r="AO17" s="135"/>
-      <c r="AP17" s="105" t="s">
+      <c r="S17" s="90"/>
+      <c r="T17" s="132"/>
+      <c r="U17" s="133"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="133"/>
+      <c r="X17" s="133"/>
+      <c r="Y17" s="133"/>
+      <c r="Z17" s="133"/>
+      <c r="AA17" s="133"/>
+      <c r="AB17" s="133"/>
+      <c r="AC17" s="133"/>
+      <c r="AD17" s="133"/>
+      <c r="AE17" s="133"/>
+      <c r="AF17" s="133"/>
+      <c r="AG17" s="133"/>
+      <c r="AH17" s="133"/>
+      <c r="AI17" s="133"/>
+      <c r="AJ17" s="133"/>
+      <c r="AK17" s="133"/>
+      <c r="AL17" s="133"/>
+      <c r="AM17" s="133"/>
+      <c r="AN17" s="133"/>
+      <c r="AO17" s="134"/>
+      <c r="AP17" s="104" t="s">
         <v>425</v>
       </c>
-      <c r="AQ17" s="107"/>
-      <c r="AR17" s="133"/>
-      <c r="AS17" s="134"/>
-      <c r="AT17" s="134"/>
-      <c r="AU17" s="134"/>
-      <c r="AV17" s="134"/>
-      <c r="AW17" s="134"/>
-      <c r="AX17" s="135"/>
+      <c r="AQ17" s="106"/>
+      <c r="AR17" s="132"/>
+      <c r="AS17" s="133"/>
+      <c r="AT17" s="133"/>
+      <c r="AU17" s="133"/>
+      <c r="AV17" s="133"/>
+      <c r="AW17" s="133"/>
+      <c r="AX17" s="134"/>
     </row>
     <row r="18" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>452</v>
       </c>
-      <c r="B18" s="126"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="127"/>
-      <c r="O18" s="127"/>
-      <c r="P18" s="127"/>
-      <c r="Q18" s="127"/>
-      <c r="R18" s="127"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="127"/>
-      <c r="U18" s="127"/>
-      <c r="V18" s="127"/>
-      <c r="W18" s="128"/>
-      <c r="X18" s="136" t="s">
+      <c r="B18" s="125"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="126"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="126"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="126"/>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="126"/>
+      <c r="S18" s="126"/>
+      <c r="T18" s="126"/>
+      <c r="U18" s="126"/>
+      <c r="V18" s="126"/>
+      <c r="W18" s="127"/>
+      <c r="X18" s="135" t="s">
         <v>419</v>
       </c>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="126"/>
-      <c r="AA18" s="127"/>
-      <c r="AB18" s="127"/>
-      <c r="AC18" s="127"/>
-      <c r="AD18" s="127"/>
-      <c r="AE18" s="127"/>
-      <c r="AF18" s="127"/>
-      <c r="AG18" s="127"/>
-      <c r="AH18" s="127"/>
-      <c r="AI18" s="127"/>
-      <c r="AJ18" s="127"/>
-      <c r="AK18" s="127"/>
-      <c r="AL18" s="127"/>
-      <c r="AM18" s="127"/>
-      <c r="AN18" s="127"/>
-      <c r="AO18" s="127"/>
-      <c r="AP18" s="127"/>
-      <c r="AQ18" s="127"/>
-      <c r="AR18" s="127"/>
-      <c r="AS18" s="127"/>
-      <c r="AT18" s="127"/>
-      <c r="AU18" s="128"/>
-      <c r="AV18" s="105" t="s">
+      <c r="Y18" s="117"/>
+      <c r="Z18" s="125"/>
+      <c r="AA18" s="126"/>
+      <c r="AB18" s="126"/>
+      <c r="AC18" s="126"/>
+      <c r="AD18" s="126"/>
+      <c r="AE18" s="126"/>
+      <c r="AF18" s="126"/>
+      <c r="AG18" s="126"/>
+      <c r="AH18" s="126"/>
+      <c r="AI18" s="126"/>
+      <c r="AJ18" s="126"/>
+      <c r="AK18" s="126"/>
+      <c r="AL18" s="126"/>
+      <c r="AM18" s="126"/>
+      <c r="AN18" s="126"/>
+      <c r="AO18" s="126"/>
+      <c r="AP18" s="126"/>
+      <c r="AQ18" s="126"/>
+      <c r="AR18" s="126"/>
+      <c r="AS18" s="126"/>
+      <c r="AT18" s="126"/>
+      <c r="AU18" s="127"/>
+      <c r="AV18" s="104" t="s">
         <v>425</v>
       </c>
-      <c r="AW18" s="107"/>
-      <c r="AX18" s="130"/>
-      <c r="AY18" s="130"/>
-      <c r="AZ18" s="130"/>
-      <c r="BA18" s="130"/>
-      <c r="BB18" s="130"/>
-      <c r="BC18" s="130"/>
-      <c r="BD18" s="130"/>
-      <c r="BE18" s="130"/>
-      <c r="BF18" s="130"/>
-      <c r="BG18" s="130"/>
-      <c r="BH18" s="130"/>
-      <c r="BI18" s="130"/>
-      <c r="BJ18" s="130"/>
-      <c r="BK18" s="130"/>
-      <c r="BL18" s="130"/>
-      <c r="BM18" s="130"/>
-      <c r="BN18" s="130"/>
-      <c r="BO18" s="130"/>
-      <c r="BP18" s="130"/>
-      <c r="BQ18" s="130"/>
-      <c r="BR18" s="130"/>
-      <c r="BS18" s="131"/>
+      <c r="AW18" s="106"/>
+      <c r="AX18" s="129"/>
+      <c r="AY18" s="129"/>
+      <c r="AZ18" s="129"/>
+      <c r="BA18" s="129"/>
+      <c r="BB18" s="129"/>
+      <c r="BC18" s="129"/>
+      <c r="BD18" s="129"/>
+      <c r="BE18" s="129"/>
+      <c r="BF18" s="129"/>
+      <c r="BG18" s="129"/>
+      <c r="BH18" s="129"/>
+      <c r="BI18" s="129"/>
+      <c r="BJ18" s="129"/>
+      <c r="BK18" s="129"/>
+      <c r="BL18" s="129"/>
+      <c r="BM18" s="129"/>
+      <c r="BN18" s="129"/>
+      <c r="BO18" s="129"/>
+      <c r="BP18" s="129"/>
+      <c r="BQ18" s="129"/>
+      <c r="BR18" s="129"/>
+      <c r="BS18" s="130"/>
     </row>
     <row r="19" spans="1:71" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>453</v>
       </c>
-      <c r="B19" s="126"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="127"/>
-      <c r="O19" s="127"/>
-      <c r="P19" s="127"/>
-      <c r="Q19" s="127"/>
-      <c r="R19" s="127"/>
-      <c r="S19" s="127"/>
-      <c r="T19" s="128"/>
-      <c r="U19" s="115" t="s">
+      <c r="B19" s="125"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="127"/>
+      <c r="U19" s="114" t="s">
         <v>419</v>
       </c>
-      <c r="V19" s="137"/>
-      <c r="W19" s="126"/>
-      <c r="X19" s="127"/>
-      <c r="Y19" s="127"/>
-      <c r="Z19" s="127"/>
-      <c r="AA19" s="127"/>
-      <c r="AB19" s="127"/>
-      <c r="AC19" s="127"/>
-      <c r="AD19" s="127"/>
-      <c r="AE19" s="127"/>
-      <c r="AF19" s="127"/>
-      <c r="AG19" s="127"/>
-      <c r="AH19" s="127"/>
-      <c r="AI19" s="127"/>
-      <c r="AJ19" s="127"/>
-      <c r="AK19" s="127"/>
-      <c r="AL19" s="127"/>
-      <c r="AM19" s="127"/>
-      <c r="AN19" s="127"/>
-      <c r="AO19" s="127"/>
-      <c r="AP19" s="127"/>
-      <c r="AQ19" s="127"/>
-      <c r="AR19" s="128"/>
-      <c r="AS19" s="123" t="s">
+      <c r="V19" s="136"/>
+      <c r="W19" s="125"/>
+      <c r="X19" s="126"/>
+      <c r="Y19" s="126"/>
+      <c r="Z19" s="126"/>
+      <c r="AA19" s="126"/>
+      <c r="AB19" s="126"/>
+      <c r="AC19" s="126"/>
+      <c r="AD19" s="126"/>
+      <c r="AE19" s="126"/>
+      <c r="AF19" s="126"/>
+      <c r="AG19" s="126"/>
+      <c r="AH19" s="126"/>
+      <c r="AI19" s="126"/>
+      <c r="AJ19" s="126"/>
+      <c r="AK19" s="126"/>
+      <c r="AL19" s="126"/>
+      <c r="AM19" s="126"/>
+      <c r="AN19" s="126"/>
+      <c r="AO19" s="126"/>
+      <c r="AP19" s="126"/>
+      <c r="AQ19" s="126"/>
+      <c r="AR19" s="127"/>
+      <c r="AS19" s="122" t="s">
         <v>425</v>
       </c>
-      <c r="AT19" s="138"/>
+      <c r="AT19" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="1">
